--- a/data/計画.xlsx
+++ b/data/計画.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\〇市道 南千反畑町第１号線舗装補修工事\１０測量と設計照査\そういち担当\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249B9F39-DC68-4D29-A245-E190C3CF5502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95C783A-FD16-4784-A306-F01A4E6CAF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{9B8B15DF-CC4A-4363-BE7A-E60876B7E9DD}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="縦断 (計画)" sheetId="12" r:id="rId2"/>
     <sheet name="横断(現況)" sheetId="8" r:id="rId3"/>
     <sheet name="横断(計画)" sheetId="7" r:id="rId4"/>
-    <sheet name="切削計算書" sheetId="6" r:id="rId5"/>
+    <sheet name="計画まとめ" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="59">
   <si>
     <t>No.0</t>
     <phoneticPr fontId="1"/>
@@ -1011,74 +1011,11 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1119,26 +1056,89 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2075,17 +2075,17 @@
       <c r="H34" s="2"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="56"/>
-      <c r="C35" s="56"/>
-      <c r="D35" s="56"/>
-      <c r="E35" s="56"/>
+      <c r="B35" s="76"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
       <c r="H35" s="2"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="56"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="76"/>
       <c r="H36" s="2"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.4">
@@ -3152,12 +3152,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
     </row>
     <row r="2" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B3" s="4"/>
@@ -3210,7 +3210,9 @@
       </c>
       <c r="J4" s="9"/>
       <c r="K4" s="11"/>
-      <c r="L4" s="14"/>
+      <c r="L4" s="14">
+        <v>10.669</v>
+      </c>
       <c r="M4" s="23"/>
     </row>
     <row r="5" spans="2:13" x14ac:dyDescent="0.4">
@@ -3244,7 +3246,9 @@
         <f>(I5-I4)/J5</f>
         <v>7.9999999999991189E-4</v>
       </c>
-      <c r="L5" s="14"/>
+      <c r="L5" s="14">
+        <v>10.691000000000001</v>
+      </c>
       <c r="M5" s="23"/>
     </row>
     <row r="6" spans="2:13" x14ac:dyDescent="0.4">
@@ -3278,7 +3282,9 @@
         <f t="shared" ref="K6:K8" si="2">(I6-I5)/J6</f>
         <v>4.9019607843137957E-3</v>
       </c>
-      <c r="L6" s="14"/>
+      <c r="L6" s="14">
+        <v>10.702</v>
+      </c>
       <c r="M6" s="23"/>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.4">
@@ -3312,7 +3318,9 @@
         <f t="shared" si="2"/>
         <v>-6.7346938775509129E-3</v>
       </c>
-      <c r="L7" s="14"/>
+      <c r="L7" s="14">
+        <v>10.679</v>
+      </c>
       <c r="M7" s="23"/>
     </row>
     <row r="8" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -3346,7 +3354,9 @@
         <f t="shared" si="2"/>
         <v>-3.6111111111110832E-3</v>
       </c>
-      <c r="L8" s="25"/>
+      <c r="L8" s="25">
+        <v>10.643000000000001</v>
+      </c>
       <c r="M8" s="26"/>
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.4">
@@ -3967,19 +3977,19 @@
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B36" s="56"/>
-      <c r="C36" s="56"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="59"/>
-      <c r="F36" s="59"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="76"/>
+      <c r="D36" s="76"/>
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
       <c r="I36" s="2"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B37" s="56"/>
-      <c r="C37" s="56"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="59"/>
-      <c r="F37" s="59"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="76"/>
+      <c r="E37" s="79"/>
+      <c r="F37" s="79"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.4">
@@ -5048,12 +5058,12 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B2" s="30"/>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="68"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="81"/>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.4">
@@ -5083,22 +5093,22 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B4" s="30"/>
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="66"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="84"/>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="60" t="s">
+      <c r="B5" s="85" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="44">
         <v>9.7159999999999993</v>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="87">
         <v>9.81</v>
       </c>
       <c r="E5" s="35"/>
@@ -5114,12 +5124,12 @@
       </c>
     </row>
     <row r="6" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="61"/>
+      <c r="B6" s="86"/>
       <c r="C6" s="45">
         <f>(D5-C5)/H5</f>
         <v>3.1438127090301402E-2</v>
       </c>
-      <c r="D6" s="63"/>
+      <c r="D6" s="88"/>
       <c r="E6" s="39"/>
       <c r="F6" s="50">
         <f>(D5-F5)/I5</f>
@@ -5130,13 +5140,13 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="85" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="46">
         <v>9.8249999999999993</v>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="87">
         <v>9.8550000000000004</v>
       </c>
       <c r="E7" s="35"/>
@@ -5152,12 +5162,12 @@
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B8" s="61"/>
+      <c r="B8" s="86"/>
       <c r="C8" s="45">
         <f>(D7-C7)/H7</f>
         <v>1.0101010101010484E-2</v>
       </c>
-      <c r="D8" s="63"/>
+      <c r="D8" s="88"/>
       <c r="E8" s="39"/>
       <c r="F8" s="50">
         <f>(D7-F7)/I7</f>
@@ -5168,13 +5178,13 @@
       <c r="I8" s="38"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="85" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="46">
         <v>9.8689999999999998</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="87">
         <v>9.9009999999999998</v>
       </c>
       <c r="E9" s="35"/>
@@ -5190,12 +5200,12 @@
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B10" s="61"/>
+      <c r="B10" s="86"/>
       <c r="C10" s="45">
         <f>(D9-C9)/H9</f>
         <v>1.0847457627118653E-2</v>
       </c>
-      <c r="D10" s="63"/>
+      <c r="D10" s="88"/>
       <c r="E10" s="39"/>
       <c r="F10" s="50">
         <f>(D9-F9)/I9</f>
@@ -5206,13 +5216,13 @@
       <c r="I10" s="38"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="85" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="46">
         <v>9.8829999999999991</v>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="87">
         <v>9.9350000000000005</v>
       </c>
       <c r="E11" s="35"/>
@@ -5228,12 +5238,12 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B12" s="61"/>
+      <c r="B12" s="86"/>
       <c r="C12" s="45">
         <f>(D11-C11)/H11</f>
         <v>1.7808219178082663E-2</v>
       </c>
-      <c r="D12" s="63"/>
+      <c r="D12" s="88"/>
       <c r="E12" s="39"/>
       <c r="F12" s="50">
         <f>(D11-F11)/I11</f>
@@ -5244,13 +5254,13 @@
       <c r="I12" s="38"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="89" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="46">
         <v>9.8719999999999999</v>
       </c>
-      <c r="D13" s="62">
+      <c r="D13" s="87">
         <v>9.9450000000000003</v>
       </c>
       <c r="E13" s="36">
@@ -5271,12 +5281,12 @@
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B14" s="70"/>
+      <c r="B14" s="90"/>
       <c r="C14" s="45">
         <f>(D13-C13)/H13</f>
         <v>2.4914675767918223E-2</v>
       </c>
-      <c r="D14" s="63"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="39"/>
       <c r="F14" s="50">
         <f>(D13-F13)/I13</f>
@@ -5287,13 +5297,13 @@
       <c r="I14" s="38"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B15" s="60" t="s">
+      <c r="B15" s="85" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="46">
         <v>9.9030000000000005</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="87">
         <v>9.9469999999999992</v>
       </c>
       <c r="E15" s="35"/>
@@ -5309,12 +5319,12 @@
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B16" s="61"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="45">
         <f>(D15-C15)/H15</f>
         <v>1.4666666666666236E-2</v>
       </c>
-      <c r="D16" s="63"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="39"/>
       <c r="F16" s="50">
         <f>(D15-F15)/I15</f>
@@ -5325,13 +5335,13 @@
       <c r="I16" s="38"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B17" s="60" t="s">
+      <c r="B17" s="85" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="46">
         <v>9.9260000000000002</v>
       </c>
-      <c r="D17" s="62">
+      <c r="D17" s="87">
         <v>9.9870000000000001</v>
       </c>
       <c r="E17" s="35"/>
@@ -5347,12 +5357,12 @@
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B18" s="61"/>
+      <c r="B18" s="86"/>
       <c r="C18" s="45">
         <f>(D17-C17)/H17</f>
         <v>1.9999999999999983E-2</v>
       </c>
-      <c r="D18" s="63"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="39"/>
       <c r="F18" s="50">
         <f>(D17-F17)/I17</f>
@@ -5363,13 +5373,13 @@
       <c r="I18" s="38"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="85" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="46">
         <v>10.038</v>
       </c>
-      <c r="D19" s="62">
+      <c r="D19" s="87">
         <v>10.050000000000001</v>
       </c>
       <c r="E19" s="35"/>
@@ -5385,12 +5395,12 @@
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B20" s="61"/>
+      <c r="B20" s="86"/>
       <c r="C20" s="45">
         <f>(D19-C19)/H19</f>
         <v>3.7500000000001421E-3</v>
       </c>
-      <c r="D20" s="63"/>
+      <c r="D20" s="88"/>
       <c r="E20" s="39"/>
       <c r="F20" s="50">
         <f>(D19-F19)/I19</f>
@@ -5401,13 +5411,13 @@
       <c r="I20" s="38"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="89" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="46">
         <v>10.052</v>
       </c>
-      <c r="D21" s="62">
+      <c r="D21" s="87">
         <v>10.054</v>
       </c>
       <c r="E21" s="36">
@@ -5428,12 +5438,12 @@
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B22" s="70"/>
+      <c r="B22" s="90"/>
       <c r="C22" s="45">
         <f>(D21-C21)/H21</f>
         <v>6.3694267515944836E-4</v>
       </c>
-      <c r="D22" s="63"/>
+      <c r="D22" s="88"/>
       <c r="E22" s="39"/>
       <c r="F22" s="50">
         <f>(D21-F21)/I21</f>
@@ -5444,13 +5454,13 @@
       <c r="I22" s="38"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B23" s="60" t="s">
+      <c r="B23" s="85" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="46">
         <v>10.002000000000001</v>
       </c>
-      <c r="D23" s="62">
+      <c r="D23" s="87">
         <v>10.045999999999999</v>
       </c>
       <c r="E23" s="35"/>
@@ -5466,12 +5476,12 @@
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B24" s="61"/>
+      <c r="B24" s="86"/>
       <c r="C24" s="45">
         <f>(D23-C23)/H23</f>
         <v>1.3836477987420976E-2</v>
       </c>
-      <c r="D24" s="63"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="39"/>
       <c r="F24" s="50">
         <f>(D23-F23)/I23</f>
@@ -5482,13 +5492,13 @@
       <c r="I24" s="38"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B25" s="60" t="s">
+      <c r="B25" s="85" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="46">
         <v>9.9960000000000004</v>
       </c>
-      <c r="D25" s="62">
+      <c r="D25" s="87">
         <v>10.048999999999999</v>
       </c>
       <c r="E25" s="35"/>
@@ -5504,12 +5514,12 @@
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B26" s="61"/>
+      <c r="B26" s="86"/>
       <c r="C26" s="45">
         <f>(D25-C25)/H25</f>
         <v>1.6562499999999702E-2</v>
       </c>
-      <c r="D26" s="63"/>
+      <c r="D26" s="88"/>
       <c r="E26" s="39"/>
       <c r="F26" s="50">
         <f>(D25-F25)/I25</f>
@@ -5520,13 +5530,13 @@
       <c r="I26" s="38"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B27" s="60" t="s">
+      <c r="B27" s="85" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="46">
         <v>10.002000000000001</v>
       </c>
-      <c r="D27" s="62">
+      <c r="D27" s="87">
         <v>10.068</v>
       </c>
       <c r="E27" s="35"/>
@@ -5542,12 +5552,12 @@
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B28" s="61"/>
+      <c r="B28" s="86"/>
       <c r="C28" s="45">
         <f>(D27-C27)/H27</f>
         <v>2.0689655172413463E-2</v>
       </c>
-      <c r="D28" s="63"/>
+      <c r="D28" s="88"/>
       <c r="E28" s="39"/>
       <c r="F28" s="50">
         <f>(D27-F27)/I27</f>
@@ -5558,13 +5568,13 @@
       <c r="I28" s="38"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="85" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="46">
         <v>10.019</v>
       </c>
-      <c r="D29" s="62">
+      <c r="D29" s="87">
         <v>10.087999999999999</v>
       </c>
       <c r="E29" s="35"/>
@@ -5580,12 +5590,12 @@
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B30" s="61"/>
+      <c r="B30" s="86"/>
       <c r="C30" s="45">
         <f>(D29-C29)/H29</f>
         <v>2.1562499999999707E-2</v>
       </c>
-      <c r="D30" s="63"/>
+      <c r="D30" s="88"/>
       <c r="E30" s="39"/>
       <c r="F30" s="50">
         <f>(D29-F29)/I29</f>
@@ -5596,13 +5606,13 @@
       <c r="I30" s="38"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="85" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="46">
         <v>10.037000000000001</v>
       </c>
-      <c r="D31" s="62">
+      <c r="D31" s="87">
         <v>10.089</v>
       </c>
       <c r="E31" s="35"/>
@@ -5618,12 +5628,12 @@
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B32" s="61"/>
+      <c r="B32" s="86"/>
       <c r="C32" s="45">
         <f>(D31-C31)/H31</f>
         <v>1.635220125786151E-2</v>
       </c>
-      <c r="D32" s="63"/>
+      <c r="D32" s="88"/>
       <c r="E32" s="39"/>
       <c r="F32" s="50">
         <f>(D31-F31)/I31</f>
@@ -5634,13 +5644,13 @@
       <c r="I32" s="38"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B33" s="60" t="s">
+      <c r="B33" s="85" t="s">
         <v>13</v>
       </c>
       <c r="C33" s="46">
         <v>10.103</v>
       </c>
-      <c r="D33" s="62">
+      <c r="D33" s="87">
         <v>10.138</v>
       </c>
       <c r="E33" s="35"/>
@@ -5656,12 +5666,12 @@
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B34" s="61"/>
+      <c r="B34" s="86"/>
       <c r="C34" s="45">
         <f>(D33-C33)/H33</f>
         <v>1.0937500000000044E-2</v>
       </c>
-      <c r="D34" s="63"/>
+      <c r="D34" s="88"/>
       <c r="E34" s="39"/>
       <c r="F34" s="50">
         <f>(D33-F33)/I33</f>
@@ -5672,13 +5682,13 @@
       <c r="I34" s="38"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="69" t="s">
+      <c r="B35" s="89" t="s">
         <v>44</v>
       </c>
       <c r="C35" s="46">
         <v>10.132</v>
       </c>
-      <c r="D35" s="62">
+      <c r="D35" s="87">
         <v>10.153</v>
       </c>
       <c r="E35" s="36">
@@ -5699,12 +5709,12 @@
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B36" s="70"/>
+      <c r="B36" s="90"/>
       <c r="C36" s="45">
         <f>(D35-C35)/H35</f>
         <v>6.6037735849059104E-3</v>
       </c>
-      <c r="D36" s="63"/>
+      <c r="D36" s="88"/>
       <c r="E36" s="39"/>
       <c r="F36" s="50">
         <f>(D35-F35)/I35</f>
@@ -5715,13 +5725,13 @@
       <c r="I36" s="38"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B37" s="60" t="s">
+      <c r="B37" s="85" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="46">
         <v>10.108000000000001</v>
       </c>
-      <c r="D37" s="62">
+      <c r="D37" s="87">
         <v>10.154</v>
       </c>
       <c r="E37" s="35"/>
@@ -5737,12 +5747,12 @@
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B38" s="61"/>
+      <c r="B38" s="86"/>
       <c r="C38" s="45">
         <f>(D37-C37)/H37</f>
         <v>1.4465408805031249E-2</v>
       </c>
-      <c r="D38" s="63"/>
+      <c r="D38" s="88"/>
       <c r="E38" s="39"/>
       <c r="F38" s="50">
         <f>(D37-F37)/I37</f>
@@ -5753,13 +5763,13 @@
       <c r="I38" s="38"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B39" s="60" t="s">
+      <c r="B39" s="85" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="46">
         <v>10.14</v>
       </c>
-      <c r="D39" s="62">
+      <c r="D39" s="87">
         <v>10.192</v>
       </c>
       <c r="E39" s="35"/>
@@ -5775,12 +5785,12 @@
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B40" s="61"/>
+      <c r="B40" s="86"/>
       <c r="C40" s="45">
         <f>(D39-C39)/H39</f>
         <v>1.635220125786151E-2</v>
       </c>
-      <c r="D40" s="63"/>
+      <c r="D40" s="88"/>
       <c r="E40" s="39"/>
       <c r="F40" s="50">
         <f>(D39-F39)/I39</f>
@@ -5791,13 +5801,13 @@
       <c r="I40" s="38"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B41" s="60" t="s">
+      <c r="B41" s="85" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="46">
         <v>10.196</v>
       </c>
-      <c r="D41" s="62">
+      <c r="D41" s="87">
         <v>10.228</v>
       </c>
       <c r="E41" s="35"/>
@@ -5813,12 +5823,12 @@
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B42" s="61"/>
+      <c r="B42" s="86"/>
       <c r="C42" s="45">
         <f>(D41-C41)/H41</f>
         <v>1.0062893081761014E-2</v>
       </c>
-      <c r="D42" s="63"/>
+      <c r="D42" s="88"/>
       <c r="E42" s="39"/>
       <c r="F42" s="50">
         <f>(D41-F41)/I41</f>
@@ -5829,13 +5839,13 @@
       <c r="I42" s="38"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="85" t="s">
         <v>17</v>
       </c>
       <c r="C43" s="46">
         <v>10.236000000000001</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="87">
         <v>10.298999999999999</v>
       </c>
       <c r="E43" s="35"/>
@@ -5851,12 +5861,12 @@
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B44" s="61"/>
+      <c r="B44" s="86"/>
       <c r="C44" s="45">
         <f>(D43-C43)/H43</f>
         <v>1.987381703469995E-2</v>
       </c>
-      <c r="D44" s="63"/>
+      <c r="D44" s="88"/>
       <c r="E44" s="39"/>
       <c r="F44" s="50">
         <f>(D43-F43)/I43</f>
@@ -5867,13 +5877,13 @@
       <c r="I44" s="38"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B45" s="60" t="s">
+      <c r="B45" s="85" t="s">
         <v>18</v>
       </c>
       <c r="C45" s="46">
         <v>10.359</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="87">
         <v>10.364000000000001</v>
       </c>
       <c r="E45" s="35"/>
@@ -5889,12 +5899,12 @@
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B46" s="61"/>
+      <c r="B46" s="86"/>
       <c r="C46" s="45">
         <f>(D45-C45)/H45</f>
         <v>1.5625000000002442E-3</v>
       </c>
-      <c r="D46" s="63"/>
+      <c r="D46" s="88"/>
       <c r="E46" s="39"/>
       <c r="F46" s="50">
         <f>(D45-F45)/I45</f>
@@ -5905,13 +5915,13 @@
       <c r="I46" s="38"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="89" t="s">
         <v>37</v>
       </c>
       <c r="C47" s="46">
         <v>10.372</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="87">
         <v>10.375999999999999</v>
       </c>
       <c r="E47" s="36">
@@ -5929,12 +5939,12 @@
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B48" s="70"/>
+      <c r="B48" s="90"/>
       <c r="C48" s="45">
         <f>(D47-C47)/H47</f>
         <v>1.2578616352199872E-3</v>
       </c>
-      <c r="D48" s="63"/>
+      <c r="D48" s="88"/>
       <c r="E48" s="39"/>
       <c r="F48" s="50">
         <f>(D47-F47)/I47</f>
@@ -5948,13 +5958,13 @@
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B49" s="60" t="s">
+      <c r="B49" s="85" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="46">
         <v>10.365</v>
       </c>
-      <c r="D49" s="62">
+      <c r="D49" s="87">
         <v>10.414</v>
       </c>
       <c r="E49" s="35"/>
@@ -5970,12 +5980,12 @@
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B50" s="61"/>
+      <c r="B50" s="86"/>
       <c r="C50" s="45">
         <f>(D49-C49)/H49</f>
         <v>1.5217391304347667E-2</v>
       </c>
-      <c r="D50" s="63"/>
+      <c r="D50" s="88"/>
       <c r="E50" s="39"/>
       <c r="F50" s="50">
         <f>(D49-F49)/I49</f>
@@ -5986,13 +5996,13 @@
       <c r="I50" s="38"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B51" s="60" t="s">
+      <c r="B51" s="85" t="s">
         <v>20</v>
       </c>
       <c r="C51" s="46">
         <v>10.404</v>
       </c>
-      <c r="D51" s="62">
+      <c r="D51" s="87">
         <v>10.465</v>
       </c>
       <c r="E51" s="35"/>
@@ -6008,12 +6018,12 @@
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B52" s="61"/>
+      <c r="B52" s="86"/>
       <c r="C52" s="45">
         <f>(D51-C51)/H51</f>
         <v>1.91823899371069E-2</v>
       </c>
-      <c r="D52" s="63"/>
+      <c r="D52" s="88"/>
       <c r="E52" s="39"/>
       <c r="F52" s="50">
         <f>(D51-F51)/I51</f>
@@ -6024,13 +6034,13 @@
       <c r="I52" s="38"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="85" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="46">
         <v>10.478</v>
       </c>
-      <c r="D53" s="62">
+      <c r="D53" s="87">
         <v>10.544</v>
       </c>
       <c r="E53" s="35"/>
@@ -6046,12 +6056,12 @@
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B54" s="61"/>
+      <c r="B54" s="86"/>
       <c r="C54" s="45">
         <f>(D53-C53)/H53</f>
         <v>2.0625000000000226E-2</v>
       </c>
-      <c r="D54" s="63"/>
+      <c r="D54" s="88"/>
       <c r="E54" s="39"/>
       <c r="F54" s="50">
         <f>(D53-F53)/I53</f>
@@ -6062,13 +6072,13 @@
       <c r="I54" s="38"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B55" s="69" t="s">
+      <c r="B55" s="89" t="s">
         <v>38</v>
       </c>
       <c r="C55" s="46">
         <v>10.510999999999999</v>
       </c>
-      <c r="D55" s="62">
+      <c r="D55" s="87">
         <v>10.589</v>
       </c>
       <c r="E55" s="36">
@@ -6086,12 +6096,12 @@
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B56" s="70"/>
+      <c r="B56" s="90"/>
       <c r="C56" s="45">
         <f>(D55-C55)/H55</f>
         <v>2.4528301886792822E-2</v>
       </c>
-      <c r="D56" s="63"/>
+      <c r="D56" s="88"/>
       <c r="E56" s="39"/>
       <c r="F56" s="50">
         <f>(D55-F55)/I55</f>
@@ -6105,13 +6115,13 @@
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B57" s="60" t="s">
+      <c r="B57" s="85" t="s">
         <v>22</v>
       </c>
       <c r="C57" s="46">
         <v>10.548999999999999</v>
       </c>
-      <c r="D57" s="62">
+      <c r="D57" s="87">
         <v>10.598000000000001</v>
       </c>
       <c r="E57" s="35"/>
@@ -6127,12 +6137,12 @@
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B58" s="61"/>
+      <c r="B58" s="86"/>
       <c r="C58" s="45">
         <f>(D57-C57)/H57</f>
         <v>1.5312500000000395E-2</v>
       </c>
-      <c r="D58" s="63"/>
+      <c r="D58" s="88"/>
       <c r="E58" s="39"/>
       <c r="F58" s="50">
         <f>(D57-F57)/I57</f>
@@ -6143,13 +6153,13 @@
       <c r="I58" s="38"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B59" s="60" t="s">
+      <c r="B59" s="85" t="s">
         <v>23</v>
       </c>
       <c r="C59" s="46">
         <v>10.606999999999999</v>
       </c>
-      <c r="D59" s="62">
+      <c r="D59" s="87">
         <v>10.669</v>
       </c>
       <c r="E59" s="35"/>
@@ -6165,12 +6175,12 @@
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B60" s="61"/>
+      <c r="B60" s="86"/>
       <c r="C60" s="45">
         <f>(D59-C59)/H59</f>
         <v>1.9375000000000364E-2</v>
       </c>
-      <c r="D60" s="63"/>
+      <c r="D60" s="88"/>
       <c r="E60" s="39"/>
       <c r="F60" s="50">
         <f>(D59-F59)/I59</f>
@@ -6181,13 +6191,13 @@
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B61" s="60" t="s">
+      <c r="B61" s="85" t="s">
         <v>39</v>
       </c>
       <c r="C61" s="46">
         <v>10.629</v>
       </c>
-      <c r="D61" s="62">
+      <c r="D61" s="87">
         <v>10.686</v>
       </c>
       <c r="E61" s="35"/>
@@ -6203,12 +6213,12 @@
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B62" s="61"/>
+      <c r="B62" s="86"/>
       <c r="C62" s="45">
         <f>(D61-C61)/H61</f>
         <v>1.786833855799385E-2</v>
       </c>
-      <c r="D62" s="63"/>
+      <c r="D62" s="88"/>
       <c r="E62" s="39"/>
       <c r="F62" s="50">
         <f>(D61-F61)/I61</f>
@@ -6219,13 +6229,13 @@
       <c r="I62" s="38"/>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B63" s="60" t="s">
+      <c r="B63" s="85" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="46">
         <v>10.673999999999999</v>
       </c>
-      <c r="D63" s="62">
+      <c r="D63" s="87">
         <v>10.734999999999999</v>
       </c>
       <c r="E63" s="35"/>
@@ -6237,9 +6247,9 @@
       <c r="I63" s="38"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B64" s="61"/>
+      <c r="B64" s="86"/>
       <c r="C64" s="45"/>
-      <c r="D64" s="63"/>
+      <c r="D64" s="88"/>
       <c r="E64" s="39"/>
       <c r="F64" s="50"/>
       <c r="G64" s="2"/>
@@ -6247,13 +6257,13 @@
       <c r="I64" s="38"/>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B65" s="60" t="s">
+      <c r="B65" s="85" t="s">
         <v>40</v>
       </c>
       <c r="C65" s="46">
         <v>10.631</v>
       </c>
-      <c r="D65" s="62">
+      <c r="D65" s="87">
         <v>10.693</v>
       </c>
       <c r="E65" s="35"/>
@@ -6265,9 +6275,9 @@
       <c r="I65" s="38"/>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B66" s="61"/>
+      <c r="B66" s="86"/>
       <c r="C66" s="45"/>
-      <c r="D66" s="63"/>
+      <c r="D66" s="88"/>
       <c r="E66" s="39"/>
       <c r="F66" s="50"/>
       <c r="G66" s="2"/>
@@ -6284,12 +6294,12 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B69" s="30"/>
-      <c r="C69" s="67" t="s">
+      <c r="C69" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="68"/>
+      <c r="D69" s="80"/>
+      <c r="E69" s="80"/>
+      <c r="F69" s="81"/>
       <c r="H69" s="38"/>
       <c r="I69" s="38"/>
     </row>
@@ -6314,23 +6324,23 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B71" s="30"/>
-      <c r="C71" s="64" t="s">
+      <c r="C71" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="D71" s="65"/>
-      <c r="E71" s="65"/>
-      <c r="F71" s="66"/>
+      <c r="D71" s="83"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="84"/>
       <c r="H71" s="38"/>
       <c r="I71" s="38"/>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B72" s="60" t="s">
+      <c r="B72" s="85" t="s">
         <v>0</v>
       </c>
       <c r="C72" s="44">
         <v>10.64</v>
       </c>
-      <c r="D72" s="62">
+      <c r="D72" s="87">
         <v>10.669</v>
       </c>
       <c r="E72" s="35"/>
@@ -6345,12 +6355,12 @@
       </c>
     </row>
     <row r="73" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B73" s="61"/>
+      <c r="B73" s="86"/>
       <c r="C73" s="45">
         <f>(D72-C72)/H72</f>
         <v>8.8957055214723673E-3</v>
       </c>
-      <c r="D73" s="63"/>
+      <c r="D73" s="88"/>
       <c r="E73" s="39"/>
       <c r="F73" s="50">
         <f>(D72-F72)/I72</f>
@@ -6360,13 +6370,13 @@
       <c r="I73" s="42"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B74" s="60" t="s">
+      <c r="B74" s="85" t="s">
         <v>1</v>
       </c>
       <c r="C74" s="46">
         <v>10.675000000000001</v>
       </c>
-      <c r="D74" s="62">
+      <c r="D74" s="87">
         <v>10.677</v>
       </c>
       <c r="E74" s="35"/>
@@ -6381,12 +6391,12 @@
       </c>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B75" s="61"/>
+      <c r="B75" s="86"/>
       <c r="C75" s="45">
         <f>(D74-C74)/H74</f>
         <v>6.4516129032222307E-4</v>
       </c>
-      <c r="D75" s="63"/>
+      <c r="D75" s="88"/>
       <c r="E75" s="39"/>
       <c r="F75" s="50">
         <f>(D74-F74)/I74</f>
@@ -6396,13 +6406,13 @@
       <c r="I75" s="38"/>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B76" s="60" t="s">
+      <c r="B76" s="85" t="s">
         <v>41</v>
       </c>
       <c r="C76" s="46">
         <v>10.688000000000001</v>
       </c>
-      <c r="D76" s="62">
+      <c r="D76" s="87">
         <v>10.702</v>
       </c>
       <c r="E76" s="35"/>
@@ -6417,12 +6427,12 @@
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B77" s="61"/>
+      <c r="B77" s="86"/>
       <c r="C77" s="45">
         <f>(D76-C76)/H76</f>
         <v>4.6357615894037571E-3</v>
       </c>
-      <c r="D77" s="63"/>
+      <c r="D77" s="88"/>
       <c r="E77" s="39"/>
       <c r="F77" s="50">
         <f>(D76-F76)/I76</f>
@@ -6432,13 +6442,13 @@
       <c r="I77" s="38"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B78" s="60" t="s">
+      <c r="B78" s="85" t="s">
         <v>2</v>
       </c>
       <c r="C78" s="46">
         <v>10.609</v>
       </c>
-      <c r="D78" s="62">
+      <c r="D78" s="87">
         <v>10.669</v>
       </c>
       <c r="E78" s="35"/>
@@ -6453,12 +6463,12 @@
       </c>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B79" s="61"/>
+      <c r="B79" s="86"/>
       <c r="C79" s="45">
         <f>(D78-C78)/H78</f>
         <v>1.857585139318901E-2</v>
       </c>
-      <c r="D79" s="63"/>
+      <c r="D79" s="88"/>
       <c r="E79" s="39"/>
       <c r="F79" s="50">
         <f>(D78-F78)/I78</f>
@@ -6468,13 +6478,13 @@
       <c r="I79" s="38"/>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B80" s="60" t="s">
+      <c r="B80" s="85" t="s">
         <v>42</v>
       </c>
       <c r="C80" s="46">
         <v>10.553000000000001</v>
       </c>
-      <c r="D80" s="62">
+      <c r="D80" s="87">
         <v>10.643000000000001</v>
       </c>
       <c r="E80" s="35"/>
@@ -6489,12 +6499,12 @@
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B81" s="61"/>
+      <c r="B81" s="86"/>
       <c r="C81" s="45">
         <f>(D80-C80)/H80</f>
         <v>2.8571428571428525E-2</v>
       </c>
-      <c r="D81" s="63"/>
+      <c r="D81" s="88"/>
       <c r="E81" s="39"/>
       <c r="F81" s="50">
         <f>(D80-F80)/I80</f>
@@ -6505,60 +6515,16 @@
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D76:D77"/>
     <mergeCell ref="C71:F71"/>
     <mergeCell ref="B57:B58"/>
     <mergeCell ref="D57:D58"/>
@@ -6571,16 +6537,60 @@
     <mergeCell ref="B65:B66"/>
     <mergeCell ref="D65:D66"/>
     <mergeCell ref="C69:F69"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D7:D8"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6605,12 +6615,12 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B2" s="30"/>
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="68"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="81"/>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.4">
@@ -6640,22 +6650,22 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B4" s="30"/>
-      <c r="C4" s="64" t="s">
+      <c r="C4" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="65"/>
-      <c r="E4" s="65"/>
-      <c r="F4" s="66"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="84"/>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="60" t="s">
+      <c r="B5" s="85" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="44">
         <v>9.7159999999999993</v>
       </c>
-      <c r="D5" s="62">
+      <c r="D5" s="87">
         <v>9.81</v>
       </c>
       <c r="E5" s="35"/>
@@ -6671,12 +6681,12 @@
       </c>
     </row>
     <row r="6" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="61"/>
+      <c r="B6" s="86"/>
       <c r="C6" s="45">
         <f>(D5-C5)/H5</f>
         <v>3.1438127090301402E-2</v>
       </c>
-      <c r="D6" s="63"/>
+      <c r="D6" s="88"/>
       <c r="E6" s="39"/>
       <c r="F6" s="50">
         <f>(D5-F5)/I5</f>
@@ -6687,13 +6697,13 @@
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="85" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="46">
         <v>9.8249999999999993</v>
       </c>
-      <c r="D7" s="62">
+      <c r="D7" s="87">
         <v>9.8510000000000009</v>
       </c>
       <c r="E7" s="35"/>
@@ -6709,12 +6719,12 @@
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B8" s="61"/>
+      <c r="B8" s="86"/>
       <c r="C8" s="45">
         <f>(D7-C7)/H7</f>
         <v>8.7542087542092847E-3</v>
       </c>
-      <c r="D8" s="63"/>
+      <c r="D8" s="88"/>
       <c r="E8" s="39"/>
       <c r="F8" s="50">
         <f>(D7-F7)/I7</f>
@@ -6725,13 +6735,13 @@
       <c r="I8" s="38"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="85" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="46">
         <v>9.8689999999999998</v>
       </c>
-      <c r="D9" s="62">
+      <c r="D9" s="87">
         <v>9.8919999999999995</v>
       </c>
       <c r="E9" s="35"/>
@@ -6747,12 +6757,12 @@
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B10" s="61"/>
+      <c r="B10" s="86"/>
       <c r="C10" s="45">
         <f>(D9-C9)/H9</f>
         <v>7.796610169491419E-3</v>
       </c>
-      <c r="D10" s="63"/>
+      <c r="D10" s="88"/>
       <c r="E10" s="39"/>
       <c r="F10" s="50">
         <f>(D9-F9)/I9</f>
@@ -6763,13 +6773,13 @@
       <c r="I10" s="38"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B11" s="60" t="s">
+      <c r="B11" s="85" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="46">
         <v>9.8829999999999991</v>
       </c>
-      <c r="D11" s="62">
+      <c r="D11" s="87">
         <v>9.9329999999999998</v>
       </c>
       <c r="E11" s="35"/>
@@ -6785,12 +6795,12 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B12" s="61"/>
+      <c r="B12" s="86"/>
       <c r="C12" s="45">
         <f>(D11-C11)/H11</f>
         <v>1.7123287671233122E-2</v>
       </c>
-      <c r="D12" s="63"/>
+      <c r="D12" s="88"/>
       <c r="E12" s="39"/>
       <c r="F12" s="50">
         <f>(D11-F11)/I11</f>
@@ -6801,13 +6811,13 @@
       <c r="I12" s="38"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="89" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="46">
         <v>9.8719999999999999</v>
       </c>
-      <c r="D13" s="62">
+      <c r="D13" s="87">
         <v>9.9559999999999995</v>
       </c>
       <c r="E13" s="36">
@@ -6828,12 +6838,12 @@
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B14" s="70"/>
+      <c r="B14" s="90"/>
       <c r="C14" s="45">
         <f>(D13-C13)/H13</f>
         <v>2.8668941979522057E-2</v>
       </c>
-      <c r="D14" s="63"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="39">
         <f>D13-(F14*J13)</f>
         <v>9.9333489278752438</v>
@@ -6847,13 +6857,13 @@
       <c r="I14" s="38"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B15" s="60" t="s">
+      <c r="B15" s="85" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="46">
         <v>9.9030000000000005</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="87">
         <v>9.9740000000000002</v>
       </c>
       <c r="E15" s="35"/>
@@ -6869,12 +6879,12 @@
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B16" s="61"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="45">
         <f>(D15-C15)/H15</f>
         <v>2.3666666666666576E-2</v>
       </c>
-      <c r="D16" s="63"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="39"/>
       <c r="F16" s="50">
         <f>(D15-F15)/I15</f>
@@ -6885,13 +6895,13 @@
       <c r="I16" s="38"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B17" s="60" t="s">
+      <c r="B17" s="85" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="46">
         <v>9.9260000000000002</v>
       </c>
-      <c r="D17" s="62">
+      <c r="D17" s="87">
         <v>10.015000000000001</v>
       </c>
       <c r="E17" s="35"/>
@@ -6907,12 +6917,12 @@
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B18" s="61"/>
+      <c r="B18" s="86"/>
       <c r="C18" s="45">
         <f>(D17-C17)/H17</f>
         <v>2.9180327868852596E-2</v>
       </c>
-      <c r="D18" s="63"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="39"/>
       <c r="F18" s="50">
         <f>(D17-F17)/I17</f>
@@ -6923,13 +6933,13 @@
       <c r="I18" s="38"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="85" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="46">
         <v>10.038</v>
       </c>
-      <c r="D19" s="62">
+      <c r="D19" s="87">
         <v>10.055</v>
       </c>
       <c r="E19" s="35"/>
@@ -6945,12 +6955,12 @@
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B20" s="61"/>
+      <c r="B20" s="86"/>
       <c r="C20" s="45">
         <f>(D19-C19)/H19</f>
         <v>5.3124999999998312E-3</v>
       </c>
-      <c r="D20" s="63"/>
+      <c r="D20" s="88"/>
       <c r="E20" s="39"/>
       <c r="F20" s="50">
         <f>(D19-F19)/I19</f>
@@ -6961,13 +6971,13 @@
       <c r="I20" s="38"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B21" s="69" t="s">
+      <c r="B21" s="89" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="46">
         <v>10.052</v>
       </c>
-      <c r="D21" s="62">
+      <c r="D21" s="87">
         <v>10.055</v>
       </c>
       <c r="E21" s="36">
@@ -6988,12 +6998,12 @@
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B22" s="70"/>
+      <c r="B22" s="90"/>
       <c r="C22" s="45">
         <f>(D21-C21)/H21</f>
         <v>9.5541401273888972E-4</v>
       </c>
-      <c r="D22" s="63"/>
+      <c r="D22" s="88"/>
       <c r="E22" s="39">
         <f>D21-(F22*J21)</f>
         <v>10.02967018469657</v>
@@ -7007,13 +7017,13 @@
       <c r="I22" s="38"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B23" s="60" t="s">
+      <c r="B23" s="85" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="46">
         <v>10.002000000000001</v>
       </c>
-      <c r="D23" s="62">
+      <c r="D23" s="87">
         <v>10.055</v>
       </c>
       <c r="E23" s="35"/>
@@ -7029,12 +7039,12 @@
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B24" s="61"/>
+      <c r="B24" s="86"/>
       <c r="C24" s="45">
         <f>(D23-C23)/H23</f>
         <v>1.6666666666666368E-2</v>
       </c>
-      <c r="D24" s="63"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="39"/>
       <c r="F24" s="50">
         <f>(D23-F23)/I23</f>
@@ -7045,13 +7055,13 @@
       <c r="I24" s="38"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B25" s="60" t="s">
+      <c r="B25" s="85" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="46">
         <v>9.9960000000000004</v>
       </c>
-      <c r="D25" s="62">
+      <c r="D25" s="87">
         <v>10.055</v>
       </c>
       <c r="E25" s="35"/>
@@ -7067,12 +7077,12 @@
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B26" s="61"/>
+      <c r="B26" s="86"/>
       <c r="C26" s="45">
         <f>(D25-C25)/H25</f>
         <v>1.8437499999999774E-2</v>
       </c>
-      <c r="D26" s="63"/>
+      <c r="D26" s="88"/>
       <c r="E26" s="39"/>
       <c r="F26" s="50">
         <f>(D25-F25)/I25</f>
@@ -7083,13 +7093,13 @@
       <c r="I26" s="38"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B27" s="60" t="s">
+      <c r="B27" s="85" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="46">
         <v>10.002000000000001</v>
       </c>
-      <c r="D27" s="62">
+      <c r="D27" s="87">
         <v>10.076000000000001</v>
       </c>
       <c r="E27" s="35"/>
@@ -7105,12 +7115,12 @@
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B28" s="61"/>
+      <c r="B28" s="86"/>
       <c r="C28" s="45">
         <f>(D27-C27)/H27</f>
         <v>2.3197492163009356E-2</v>
       </c>
-      <c r="D28" s="63"/>
+      <c r="D28" s="88"/>
       <c r="E28" s="39"/>
       <c r="F28" s="50">
         <f>(D27-F27)/I27</f>
@@ -7121,13 +7131,13 @@
       <c r="I28" s="38"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B29" s="60" t="s">
+      <c r="B29" s="85" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="46">
         <v>10.019</v>
       </c>
-      <c r="D29" s="62">
+      <c r="D29" s="87">
         <v>10.097</v>
       </c>
       <c r="E29" s="35"/>
@@ -7143,12 +7153,12 @@
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B30" s="61"/>
+      <c r="B30" s="86"/>
       <c r="C30" s="45">
         <f>(D29-C29)/H29</f>
         <v>2.4374999999999813E-2</v>
       </c>
-      <c r="D30" s="63"/>
+      <c r="D30" s="88"/>
       <c r="E30" s="39"/>
       <c r="F30" s="50">
         <f>(D29-F29)/I29</f>
@@ -7159,13 +7169,13 @@
       <c r="I30" s="38"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B31" s="60" t="s">
+      <c r="B31" s="85" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="46">
         <v>10.037000000000001</v>
       </c>
-      <c r="D31" s="62">
+      <c r="D31" s="87">
         <v>10.118</v>
       </c>
       <c r="E31" s="35"/>
@@ -7181,12 +7191,12 @@
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B32" s="61"/>
+      <c r="B32" s="86"/>
       <c r="C32" s="45">
         <f>(D31-C31)/H31</f>
         <v>2.5471698113207392E-2</v>
       </c>
-      <c r="D32" s="63"/>
+      <c r="D32" s="88"/>
       <c r="E32" s="39"/>
       <c r="F32" s="50">
         <f>(D31-F31)/I31</f>
@@ -7197,13 +7207,13 @@
       <c r="I32" s="38"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B33" s="60" t="s">
+      <c r="B33" s="85" t="s">
         <v>13</v>
       </c>
       <c r="C33" s="46">
         <v>10.103</v>
       </c>
-      <c r="D33" s="62">
+      <c r="D33" s="87">
         <v>10.138999999999999</v>
       </c>
       <c r="E33" s="35"/>
@@ -7219,12 +7229,12 @@
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B34" s="61"/>
+      <c r="B34" s="86"/>
       <c r="C34" s="45">
         <f>(D33-C33)/H33</f>
         <v>1.1249999999999871E-2</v>
       </c>
-      <c r="D34" s="63"/>
+      <c r="D34" s="88"/>
       <c r="E34" s="39"/>
       <c r="F34" s="50">
         <f>(D33-F33)/I33</f>
@@ -7235,13 +7245,13 @@
       <c r="I34" s="38"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="69" t="s">
+      <c r="B35" s="89" t="s">
         <v>36</v>
       </c>
       <c r="C35" s="46">
         <v>10.132</v>
       </c>
-      <c r="D35" s="62">
+      <c r="D35" s="87">
         <v>10.15</v>
       </c>
       <c r="E35" s="36">
@@ -7262,12 +7272,12 @@
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B36" s="70"/>
+      <c r="B36" s="90"/>
       <c r="C36" s="45">
         <f>(D35-C35)/H35</f>
         <v>5.6603773584907799E-3</v>
       </c>
-      <c r="D36" s="63"/>
+      <c r="D36" s="88"/>
       <c r="E36" s="39">
         <f>D35-(F36*J35)</f>
         <v>10.130000000000001</v>
@@ -7281,13 +7291,13 @@
       <c r="I36" s="38"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B37" s="60" t="s">
+      <c r="B37" s="85" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="46">
         <v>10.108000000000001</v>
       </c>
-      <c r="D37" s="62">
+      <c r="D37" s="87">
         <v>10.166</v>
       </c>
       <c r="E37" s="35"/>
@@ -7303,12 +7313,12 @@
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B38" s="61"/>
+      <c r="B38" s="86"/>
       <c r="C38" s="45">
         <f>(D37-C37)/H37</f>
         <v>1.8238993710691768E-2</v>
       </c>
-      <c r="D38" s="63"/>
+      <c r="D38" s="88"/>
       <c r="E38" s="39"/>
       <c r="F38" s="50">
         <f>(D37-F37)/I37</f>
@@ -7319,13 +7329,13 @@
       <c r="I38" s="38"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B39" s="60" t="s">
+      <c r="B39" s="85" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="46">
         <v>10.14</v>
       </c>
-      <c r="D39" s="62">
+      <c r="D39" s="87">
         <v>10.193</v>
       </c>
       <c r="E39" s="35"/>
@@ -7341,12 +7351,12 @@
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B40" s="61"/>
+      <c r="B40" s="86"/>
       <c r="C40" s="45">
         <f>(D39-C39)/H39</f>
         <v>1.6666666666666368E-2</v>
       </c>
-      <c r="D40" s="63"/>
+      <c r="D40" s="88"/>
       <c r="E40" s="39"/>
       <c r="F40" s="50">
         <f>(D39-F39)/I39</f>
@@ -7357,13 +7367,13 @@
       <c r="I40" s="38"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B41" s="60" t="s">
+      <c r="B41" s="85" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="46">
         <v>10.196</v>
       </c>
-      <c r="D41" s="62">
+      <c r="D41" s="87">
         <v>10.25</v>
       </c>
       <c r="E41" s="35"/>
@@ -7379,12 +7389,12 @@
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B42" s="61"/>
+      <c r="B42" s="86"/>
       <c r="C42" s="45">
         <f>(D41-C41)/H41</f>
         <v>1.6981132075471781E-2</v>
       </c>
-      <c r="D42" s="63"/>
+      <c r="D42" s="88"/>
       <c r="E42" s="39"/>
       <c r="F42" s="50">
         <f>(D41-F41)/I41</f>
@@ -7395,13 +7405,13 @@
       <c r="I42" s="38"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B43" s="60" t="s">
+      <c r="B43" s="85" t="s">
         <v>17</v>
       </c>
       <c r="C43" s="46">
         <v>10.236000000000001</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="87">
         <v>10.307</v>
       </c>
       <c r="E43" s="35"/>
@@ -7417,12 +7427,12 @@
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B44" s="61"/>
+      <c r="B44" s="86"/>
       <c r="C44" s="45">
         <f>(D43-C43)/H43</f>
         <v>2.239747634069392E-2</v>
       </c>
-      <c r="D44" s="63"/>
+      <c r="D44" s="88"/>
       <c r="E44" s="39"/>
       <c r="F44" s="50">
         <f>(D43-F43)/I43</f>
@@ -7433,13 +7443,13 @@
       <c r="I44" s="38"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B45" s="60" t="s">
+      <c r="B45" s="85" t="s">
         <v>18</v>
       </c>
       <c r="C45" s="46">
         <v>10.359</v>
       </c>
-      <c r="D45" s="62">
+      <c r="D45" s="87">
         <v>10.364000000000001</v>
       </c>
       <c r="E45" s="35"/>
@@ -7455,12 +7465,12 @@
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B46" s="61"/>
+      <c r="B46" s="86"/>
       <c r="C46" s="45">
         <f>(D45-C45)/H45</f>
         <v>1.5625000000002442E-3</v>
       </c>
-      <c r="D46" s="63"/>
+      <c r="D46" s="88"/>
       <c r="E46" s="39"/>
       <c r="F46" s="50">
         <f>(D45-F45)/I45</f>
@@ -7471,13 +7481,13 @@
       <c r="I46" s="38"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B47" s="69" t="s">
+      <c r="B47" s="89" t="s">
         <v>37</v>
       </c>
       <c r="C47" s="46">
         <v>10.372</v>
       </c>
-      <c r="D47" s="62">
+      <c r="D47" s="87">
         <v>10.379</v>
       </c>
       <c r="E47" s="36">
@@ -7498,12 +7508,12 @@
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B48" s="70"/>
+      <c r="B48" s="90"/>
       <c r="C48" s="45">
         <f>(D47-C47)/H47</f>
         <v>2.2012578616351173E-3</v>
       </c>
-      <c r="D48" s="63"/>
+      <c r="D48" s="88"/>
       <c r="E48" s="39">
         <f>D47-(F48*J47)</f>
         <v>10.380749999999999</v>
@@ -7517,13 +7527,13 @@
       <c r="I48" s="38"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B49" s="60" t="s">
+      <c r="B49" s="85" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="46">
         <v>10.365</v>
       </c>
-      <c r="D49" s="62">
+      <c r="D49" s="87">
         <v>10.426</v>
       </c>
       <c r="E49" s="35"/>
@@ -7539,12 +7549,12 @@
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B50" s="61"/>
+      <c r="B50" s="86"/>
       <c r="C50" s="45">
         <f>(D49-C49)/H49</f>
         <v>1.894409937888197E-2</v>
       </c>
-      <c r="D50" s="63"/>
+      <c r="D50" s="88"/>
       <c r="E50" s="39"/>
       <c r="F50" s="50">
         <f>(D49-F49)/I49</f>
@@ -7555,13 +7565,13 @@
       <c r="I50" s="38"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B51" s="60" t="s">
+      <c r="B51" s="85" t="s">
         <v>20</v>
       </c>
       <c r="C51" s="46">
         <v>10.404</v>
       </c>
-      <c r="D51" s="62">
+      <c r="D51" s="87">
         <v>10.488</v>
       </c>
       <c r="E51" s="35"/>
@@ -7577,12 +7587,12 @@
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B52" s="61"/>
+      <c r="B52" s="86"/>
       <c r="C52" s="45">
         <f>(D51-C51)/H51</f>
         <v>2.6415094339622525E-2</v>
       </c>
-      <c r="D52" s="63"/>
+      <c r="D52" s="88"/>
       <c r="E52" s="39"/>
       <c r="F52" s="50">
         <f>(D51-F51)/I51</f>
@@ -7593,13 +7603,13 @@
       <c r="I52" s="38"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B53" s="60" t="s">
+      <c r="B53" s="85" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="46">
         <v>10.478</v>
       </c>
-      <c r="D53" s="62">
+      <c r="D53" s="87">
         <v>10.55</v>
       </c>
       <c r="E53" s="35"/>
@@ -7615,12 +7625,12 @@
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B54" s="61"/>
+      <c r="B54" s="86"/>
       <c r="C54" s="45">
         <f>(D53-C53)/H53</f>
         <v>2.2500000000000298E-2</v>
       </c>
-      <c r="D54" s="63"/>
+      <c r="D54" s="88"/>
       <c r="E54" s="39"/>
       <c r="F54" s="50">
         <f>(D53-F53)/I53</f>
@@ -7631,13 +7641,13 @@
       <c r="I54" s="38"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B55" s="69" t="s">
+      <c r="B55" s="89" t="s">
         <v>38</v>
       </c>
       <c r="C55" s="46">
         <v>10.510999999999999</v>
       </c>
-      <c r="D55" s="62">
+      <c r="D55" s="87">
         <v>10.58</v>
       </c>
       <c r="E55" s="36">
@@ -7658,12 +7668,12 @@
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B56" s="70"/>
+      <c r="B56" s="90"/>
       <c r="C56" s="45">
         <f>(D55-C55)/H55</f>
         <v>2.1698113207547432E-2</v>
       </c>
-      <c r="D56" s="63"/>
+      <c r="D56" s="88"/>
       <c r="E56" s="39">
         <f>D55-(F56*J55)</f>
         <v>10.56490625</v>
@@ -7677,13 +7687,13 @@
       <c r="I56" s="38"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B57" s="60" t="s">
+      <c r="B57" s="85" t="s">
         <v>22</v>
       </c>
       <c r="C57" s="46">
         <v>10.548999999999999</v>
       </c>
-      <c r="D57" s="62">
+      <c r="D57" s="87">
         <v>10.612</v>
       </c>
       <c r="E57" s="35"/>
@@ -7699,12 +7709,12 @@
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B58" s="61"/>
+      <c r="B58" s="86"/>
       <c r="C58" s="45">
         <f>(D57-C57)/H57</f>
         <v>1.9687500000000191E-2</v>
       </c>
-      <c r="D58" s="63"/>
+      <c r="D58" s="88"/>
       <c r="E58" s="39"/>
       <c r="F58" s="50">
         <f>(D57-F57)/I57</f>
@@ -7715,13 +7725,13 @@
       <c r="I58" s="38"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B59" s="60" t="s">
+      <c r="B59" s="85" t="s">
         <v>23</v>
       </c>
       <c r="C59" s="46">
         <v>10.606999999999999</v>
       </c>
-      <c r="D59" s="62">
+      <c r="D59" s="87">
         <v>10.673999999999999</v>
       </c>
       <c r="E59" s="35"/>
@@ -7737,12 +7747,12 @@
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B60" s="61"/>
+      <c r="B60" s="86"/>
       <c r="C60" s="45">
         <f>(D59-C59)/H59</f>
         <v>2.0937500000000053E-2</v>
       </c>
-      <c r="D60" s="63"/>
+      <c r="D60" s="88"/>
       <c r="E60" s="39"/>
       <c r="F60" s="50">
         <f>(D59-F59)/I59</f>
@@ -7753,13 +7763,13 @@
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B61" s="60" t="s">
+      <c r="B61" s="85" t="s">
         <v>39</v>
       </c>
       <c r="C61" s="46">
         <v>10.629</v>
       </c>
-      <c r="D61" s="62">
+      <c r="D61" s="87">
         <v>10.686</v>
       </c>
       <c r="E61" s="35"/>
@@ -7775,12 +7785,12 @@
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B62" s="61"/>
+      <c r="B62" s="86"/>
       <c r="C62" s="45">
         <f>(D61-C61)/H61</f>
         <v>1.786833855799385E-2</v>
       </c>
-      <c r="D62" s="63"/>
+      <c r="D62" s="88"/>
       <c r="E62" s="39"/>
       <c r="F62" s="50">
         <f>(D61-F61)/I61</f>
@@ -7791,13 +7801,13 @@
       <c r="I62" s="38"/>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B63" s="60" t="s">
+      <c r="B63" s="85" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="46">
         <v>10.673999999999999</v>
       </c>
-      <c r="D63" s="62">
+      <c r="D63" s="87">
         <v>10.734999999999999</v>
       </c>
       <c r="E63" s="35"/>
@@ -7805,43 +7815,63 @@
         <v>10.643000000000001</v>
       </c>
       <c r="G63" s="2"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="38"/>
+      <c r="H63" s="38">
+        <v>3.1</v>
+      </c>
+      <c r="I63" s="38">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B64" s="61"/>
-      <c r="C64" s="45"/>
-      <c r="D64" s="63"/>
+      <c r="B64" s="86"/>
+      <c r="C64" s="45">
+        <f>(D63-C63)/H63</f>
+        <v>1.9677419354838691E-2</v>
+      </c>
+      <c r="D64" s="88"/>
       <c r="E64" s="39"/>
-      <c r="F64" s="50"/>
+      <c r="F64" s="50">
+        <f>(D63-F63)/I63</f>
+        <v>1.0697674418604506E-2</v>
+      </c>
       <c r="G64" s="2"/>
       <c r="H64" s="38"/>
       <c r="I64" s="38"/>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B65" s="60" t="s">
+      <c r="B65" s="85" t="s">
         <v>40</v>
       </c>
       <c r="C65" s="46">
         <v>10.631</v>
       </c>
-      <c r="D65" s="62">
-        <v>10.693</v>
+      <c r="D65" s="87">
+        <v>10.721</v>
       </c>
       <c r="E65" s="35"/>
       <c r="F65" s="51">
         <v>10.643000000000001</v>
       </c>
       <c r="G65" s="2"/>
-      <c r="H65" s="38"/>
-      <c r="I65" s="38"/>
+      <c r="H65" s="38">
+        <v>5</v>
+      </c>
+      <c r="I65" s="38">
+        <v>9</v>
+      </c>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B66" s="61"/>
-      <c r="C66" s="45"/>
-      <c r="D66" s="63"/>
+      <c r="B66" s="86"/>
+      <c r="C66" s="45">
+        <f>(D65-C65)/H65</f>
+        <v>1.7999999999999971E-2</v>
+      </c>
+      <c r="D66" s="88"/>
       <c r="E66" s="39"/>
-      <c r="F66" s="50"/>
+      <c r="F66" s="50">
+        <f>(D65-F65)/I65</f>
+        <v>8.6666666666666003E-3</v>
+      </c>
       <c r="G66" s="2"/>
       <c r="H66" s="38"/>
       <c r="I66" s="38"/>
@@ -7856,12 +7886,12 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B69" s="30"/>
-      <c r="C69" s="67" t="s">
+      <c r="C69" s="80" t="s">
         <v>30</v>
       </c>
-      <c r="D69" s="67"/>
-      <c r="E69" s="67"/>
-      <c r="F69" s="68"/>
+      <c r="D69" s="80"/>
+      <c r="E69" s="80"/>
+      <c r="F69" s="81"/>
       <c r="H69" s="38"/>
       <c r="I69" s="38"/>
     </row>
@@ -7886,23 +7916,23 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B71" s="30"/>
-      <c r="C71" s="64" t="s">
+      <c r="C71" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="D71" s="65"/>
-      <c r="E71" s="65"/>
-      <c r="F71" s="66"/>
+      <c r="D71" s="83"/>
+      <c r="E71" s="83"/>
+      <c r="F71" s="84"/>
       <c r="H71" s="38"/>
       <c r="I71" s="38"/>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B72" s="60" t="s">
+      <c r="B72" s="85" t="s">
         <v>0</v>
       </c>
       <c r="C72" s="44">
         <v>10.64</v>
       </c>
-      <c r="D72" s="62">
+      <c r="D72" s="87">
         <v>10.669</v>
       </c>
       <c r="E72" s="35"/>
@@ -7917,12 +7947,12 @@
       </c>
     </row>
     <row r="73" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B73" s="61"/>
+      <c r="B73" s="86"/>
       <c r="C73" s="45">
         <f>(D72-C72)/H72</f>
         <v>8.8957055214723673E-3</v>
       </c>
-      <c r="D73" s="63"/>
+      <c r="D73" s="88"/>
       <c r="E73" s="39"/>
       <c r="F73" s="50">
         <f>(D72-F72)/I72</f>
@@ -7932,14 +7962,14 @@
       <c r="I73" s="42"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B74" s="60" t="s">
+      <c r="B74" s="85" t="s">
         <v>1</v>
       </c>
       <c r="C74" s="46">
         <v>10.675000000000001</v>
       </c>
-      <c r="D74" s="62">
-        <v>10.677</v>
+      <c r="D74" s="87">
+        <v>10.691000000000001</v>
       </c>
       <c r="E74" s="35"/>
       <c r="F74" s="51">
@@ -7953,28 +7983,28 @@
       </c>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B75" s="61"/>
+      <c r="B75" s="86"/>
       <c r="C75" s="45">
         <f>(D74-C74)/H74</f>
-        <v>6.4516129032222307E-4</v>
-      </c>
-      <c r="D75" s="63"/>
+        <v>5.1612903225806495E-3</v>
+      </c>
+      <c r="D75" s="88"/>
       <c r="E75" s="39"/>
       <c r="F75" s="50">
         <f>(D74-F74)/I74</f>
-        <v>2.7812500000000129E-2</v>
+        <v>3.218750000000048E-2</v>
       </c>
       <c r="H75" s="38"/>
       <c r="I75" s="38"/>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B76" s="60" t="s">
+      <c r="B76" s="85" t="s">
         <v>41</v>
       </c>
       <c r="C76" s="46">
         <v>10.688000000000001</v>
       </c>
-      <c r="D76" s="62">
+      <c r="D76" s="87">
         <v>10.702</v>
       </c>
       <c r="E76" s="35"/>
@@ -7989,12 +8019,12 @@
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B77" s="61"/>
+      <c r="B77" s="86"/>
       <c r="C77" s="45">
         <f>(D76-C76)/H76</f>
         <v>4.6357615894037571E-3</v>
       </c>
-      <c r="D77" s="63"/>
+      <c r="D77" s="88"/>
       <c r="E77" s="39"/>
       <c r="F77" s="50">
         <f>(D76-F76)/I76</f>
@@ -8004,14 +8034,14 @@
       <c r="I77" s="38"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B78" s="60" t="s">
+      <c r="B78" s="85" t="s">
         <v>2</v>
       </c>
       <c r="C78" s="46">
         <v>10.609</v>
       </c>
-      <c r="D78" s="62">
-        <v>10.669</v>
+      <c r="D78" s="87">
+        <v>10.678000000000001</v>
       </c>
       <c r="E78" s="35"/>
       <c r="F78" s="51">
@@ -8025,28 +8055,28 @@
       </c>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B79" s="61"/>
+      <c r="B79" s="86"/>
       <c r="C79" s="45">
         <f>(D78-C78)/H78</f>
-        <v>1.857585139318901E-2</v>
-      </c>
-      <c r="D79" s="63"/>
+        <v>2.1362229102167441E-2</v>
+      </c>
+      <c r="D79" s="88"/>
       <c r="E79" s="39"/>
       <c r="F79" s="50">
         <f>(D78-F78)/I78</f>
-        <v>2.0317460317460335E-2</v>
+        <v>2.3174603174603303E-2</v>
       </c>
       <c r="H79" s="38"/>
       <c r="I79" s="38"/>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B80" s="60" t="s">
+      <c r="B80" s="85" t="s">
         <v>42</v>
       </c>
       <c r="C80" s="46">
         <v>10.553000000000001</v>
       </c>
-      <c r="D80" s="62">
+      <c r="D80" s="87">
         <v>10.643000000000001</v>
       </c>
       <c r="E80" s="35"/>
@@ -8061,12 +8091,12 @@
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B81" s="61"/>
+      <c r="B81" s="86"/>
       <c r="C81" s="45">
         <f>(D80-C80)/H80</f>
         <v>2.8571428571428525E-2</v>
       </c>
-      <c r="D81" s="63"/>
+      <c r="D81" s="88"/>
       <c r="E81" s="39"/>
       <c r="F81" s="50">
         <f>(D80-F80)/I80</f>
@@ -8077,6 +8107,66 @@
     </row>
   </sheetData>
   <mergeCells count="76">
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="D63:D64"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
     <mergeCell ref="B23:B24"/>
     <mergeCell ref="C2:F2"/>
     <mergeCell ref="C4:F4"/>
@@ -8093,66 +8183,6 @@
     <mergeCell ref="D5:D6"/>
     <mergeCell ref="D7:D8"/>
     <mergeCell ref="D9:D10"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="D63:D64"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -8162,7 +8192,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FADC482F-24F7-4F5C-B8D7-C1D9AEF4234E}">
-  <dimension ref="B1:R155"/>
+  <sheetPr>
+    <tabColor theme="9"/>
+  </sheetPr>
+  <dimension ref="B1:R181"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="22.375" style="31" customWidth="1"/>
@@ -8171,9 +8204,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:18" s="1" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="79"/>
-      <c r="C1" s="80"/>
-      <c r="D1" s="72" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="57" t="s">
         <v>26</v>
       </c>
       <c r="E1" s="29">
@@ -8182,7 +8215,7 @@
       <c r="F1" s="29">
         <v>2</v>
       </c>
-      <c r="G1" s="71" t="s">
+      <c r="G1" s="56" t="s">
         <v>28</v>
       </c>
       <c r="H1" s="29">
@@ -8197,7 +8230,7 @@
       <c r="K1" s="29">
         <v>8</v>
       </c>
-      <c r="L1" s="72" t="s">
+      <c r="L1" s="57" t="s">
         <v>27</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -8214,31 +8247,31 @@
       </c>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B2" s="73" t="s">
+      <c r="B2" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="82">
+      <c r="D2" s="61">
         <v>9.7159999999999993</v>
       </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="82">
+      <c r="E2" s="61"/>
+      <c r="F2" s="61">
         <v>9.7609999999999992</v>
       </c>
-      <c r="G2" s="82">
+      <c r="G2" s="61">
         <v>9.81</v>
       </c>
-      <c r="H2" s="82">
+      <c r="H2" s="61">
         <v>9.827</v>
       </c>
-      <c r="I2" s="82">
+      <c r="I2" s="61">
         <v>9.7420000000000009</v>
       </c>
-      <c r="J2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82">
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+      <c r="L2" s="61">
         <v>9.6809999999999992</v>
       </c>
       <c r="N2" s="38">
@@ -8255,63 +8288,63 @@
       </c>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B3" s="73"/>
-      <c r="C3" s="86" t="s">
+      <c r="B3" s="92"/>
+      <c r="C3" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="87">
+      <c r="D3" s="66">
         <v>9.7159999999999993</v>
       </c>
-      <c r="E3" s="88"/>
-      <c r="F3" s="87">
+      <c r="E3" s="67"/>
+      <c r="F3" s="66">
         <v>9.7609999999999992</v>
       </c>
-      <c r="G3" s="87">
+      <c r="G3" s="66">
         <v>9.81</v>
       </c>
-      <c r="H3" s="88">
+      <c r="H3" s="67">
         <v>9.827</v>
       </c>
-      <c r="I3" s="88">
+      <c r="I3" s="67">
         <v>9.7420000000000009</v>
       </c>
-      <c r="J3" s="88"/>
-      <c r="K3" s="88"/>
-      <c r="L3" s="88">
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67">
         <v>9.6809999999999992</v>
       </c>
       <c r="Q3" s="32"/>
       <c r="R3" s="32"/>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B4" s="73"/>
-      <c r="C4" s="89" t="s">
+      <c r="B4" s="92"/>
+      <c r="C4" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="90">
+      <c r="D4" s="69">
         <f>D3-0.05</f>
         <v>9.6659999999999986</v>
       </c>
-      <c r="E4" s="91"/>
-      <c r="F4" s="90">
+      <c r="E4" s="70"/>
+      <c r="F4" s="69">
         <f>F3-0.05</f>
         <v>9.7109999999999985</v>
       </c>
-      <c r="G4" s="90">
+      <c r="G4" s="69">
         <f>G3-0.05</f>
         <v>9.76</v>
       </c>
-      <c r="H4" s="90">
+      <c r="H4" s="69">
         <f>H3-0.05</f>
         <v>9.7769999999999992</v>
       </c>
-      <c r="I4" s="90">
+      <c r="I4" s="69">
         <f>I3-0.05</f>
         <v>9.6920000000000002</v>
       </c>
-      <c r="J4" s="91"/>
-      <c r="K4" s="91"/>
-      <c r="L4" s="90">
+      <c r="J4" s="70"/>
+      <c r="K4" s="70"/>
+      <c r="L4" s="69">
         <f>L3-0.05</f>
         <v>9.6309999999999985</v>
       </c>
@@ -8321,79 +8354,79 @@
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B5" s="74"/>
-      <c r="C5" s="83" t="s">
+      <c r="B5" s="93"/>
+      <c r="C5" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D5" s="84">
+      <c r="D5" s="63">
         <v>0.05</v>
       </c>
-      <c r="E5" s="85"/>
-      <c r="F5" s="84">
+      <c r="E5" s="64"/>
+      <c r="F5" s="63">
         <f>F2-F4</f>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="G5" s="84">
+      <c r="G5" s="63">
         <f>G2-G4</f>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="H5" s="84">
+      <c r="H5" s="63">
         <f>H2-H4</f>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="I5" s="84">
+      <c r="I5" s="63">
         <f>I2-I4</f>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="84">
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="63">
         <v>0.05</v>
       </c>
       <c r="Q5" s="32"/>
       <c r="R5" s="32"/>
     </row>
-    <row r="6" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="94"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="97"/>
-      <c r="H6" s="97"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
-      <c r="L6" s="95"/>
-      <c r="Q6" s="93"/>
-      <c r="R6" s="93"/>
+    <row r="6" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B6" s="71"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="75"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="74"/>
+      <c r="I6" s="74"/>
+      <c r="J6" s="75"/>
+      <c r="K6" s="75"/>
+      <c r="L6" s="72"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="81" t="s">
+      <c r="C7" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="82">
+      <c r="D7" s="61">
         <v>9.8249999999999993</v>
       </c>
-      <c r="E7" s="80"/>
-      <c r="F7" s="82">
+      <c r="E7" s="59"/>
+      <c r="F7" s="61">
         <v>9.8469999999999995</v>
       </c>
-      <c r="G7" s="82">
+      <c r="G7" s="61">
         <v>9.8550000000000004</v>
       </c>
-      <c r="H7" s="80">
+      <c r="H7" s="59">
         <v>9.8119999999999994</v>
       </c>
-      <c r="I7" s="80">
+      <c r="I7" s="59">
         <v>9.7829999999999995</v>
       </c>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80">
+      <c r="J7" s="59"/>
+      <c r="K7" s="59"/>
+      <c r="L7" s="59">
         <v>9.7430000000000003</v>
       </c>
       <c r="N7" s="38">
@@ -8410,66 +8443,66 @@
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B8" s="73"/>
-      <c r="C8" s="86" t="s">
+      <c r="B8" s="92"/>
+      <c r="C8" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="87">
+      <c r="D8" s="66">
         <v>9.8249999999999993</v>
       </c>
-      <c r="E8" s="88"/>
-      <c r="F8" s="87">
+      <c r="E8" s="67"/>
+      <c r="F8" s="66">
         <f>G8-($F$1*Q7)</f>
         <v>9.8330000000000002</v>
       </c>
-      <c r="G8" s="87">
+      <c r="G8" s="66">
         <v>9.8510000000000009</v>
       </c>
-      <c r="H8" s="88">
+      <c r="H8" s="67">
         <f>G8-($H$1*R7)</f>
         <v>9.8110000000000017</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="67">
         <f>G8-($I$1*R7)</f>
         <v>9.7710000000000008</v>
       </c>
-      <c r="J8" s="88"/>
-      <c r="K8" s="88"/>
-      <c r="L8" s="88">
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67">
         <v>9.7430000000000003</v>
       </c>
       <c r="Q8" s="32"/>
       <c r="R8" s="32"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B9" s="73"/>
-      <c r="C9" s="89" t="s">
+      <c r="B9" s="92"/>
+      <c r="C9" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D9" s="90">
+      <c r="D9" s="69">
         <f>D8-0.05</f>
         <v>9.7749999999999986</v>
       </c>
-      <c r="E9" s="91"/>
-      <c r="F9" s="90">
+      <c r="E9" s="70"/>
+      <c r="F9" s="69">
         <f>F8-0.05</f>
         <v>9.7829999999999995</v>
       </c>
-      <c r="G9" s="90">
+      <c r="G9" s="69">
         <f>G8-0.05</f>
         <v>9.8010000000000002</v>
       </c>
-      <c r="H9" s="90">
+      <c r="H9" s="69">
         <f>H8-0.05</f>
         <v>9.761000000000001</v>
       </c>
-      <c r="I9" s="90">
+      <c r="I9" s="69">
         <f>I8-0.05</f>
         <v>9.7210000000000001</v>
       </c>
-      <c r="J9" s="91"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="90">
+      <c r="J9" s="70"/>
+      <c r="K9" s="70"/>
+      <c r="L9" s="69">
         <f>L8-0.05</f>
         <v>9.6929999999999996</v>
       </c>
@@ -8477,79 +8510,79 @@
       <c r="R9" s="32"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B10" s="74"/>
-      <c r="C10" s="83" t="s">
+      <c r="B10" s="93"/>
+      <c r="C10" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D10" s="84">
+      <c r="D10" s="63">
         <v>0.05</v>
       </c>
-      <c r="E10" s="85"/>
-      <c r="F10" s="84">
+      <c r="E10" s="64"/>
+      <c r="F10" s="63">
         <f>F7-F9</f>
         <v>6.4000000000000057E-2</v>
       </c>
-      <c r="G10" s="84">
+      <c r="G10" s="63">
         <f>G7-G9</f>
         <v>5.400000000000027E-2</v>
       </c>
-      <c r="H10" s="84">
+      <c r="H10" s="63">
         <f>H7-H9</f>
         <v>5.099999999999838E-2</v>
       </c>
-      <c r="I10" s="84">
+      <c r="I10" s="63">
         <f>I7-I9</f>
         <v>6.1999999999999389E-2</v>
       </c>
-      <c r="J10" s="85"/>
-      <c r="K10" s="85"/>
-      <c r="L10" s="84">
+      <c r="J10" s="64"/>
+      <c r="K10" s="64"/>
+      <c r="L10" s="63">
         <v>0.05</v>
       </c>
       <c r="Q10" s="32"/>
       <c r="R10" s="32"/>
     </row>
-    <row r="11" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="94"/>
-      <c r="C11" s="96"/>
-      <c r="D11" s="97"/>
-      <c r="E11" s="98"/>
-      <c r="F11" s="97"/>
-      <c r="G11" s="97"/>
-      <c r="H11" s="97"/>
-      <c r="I11" s="97"/>
-      <c r="J11" s="98"/>
-      <c r="K11" s="98"/>
-      <c r="L11" s="95"/>
-      <c r="Q11" s="93"/>
-      <c r="R11" s="93"/>
+    <row r="11" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B11" s="71"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="74"/>
+      <c r="J11" s="75"/>
+      <c r="K11" s="75"/>
+      <c r="L11" s="72"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="91" t="s">
         <v>2</v>
       </c>
-      <c r="C12" s="81" t="s">
+      <c r="C12" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="82">
+      <c r="D12" s="61">
         <v>9.8689999999999998</v>
       </c>
-      <c r="E12" s="80"/>
-      <c r="F12" s="82">
+      <c r="E12" s="59"/>
+      <c r="F12" s="61">
         <v>9.8740000000000006</v>
       </c>
-      <c r="G12" s="82">
+      <c r="G12" s="61">
         <v>9.9009999999999998</v>
       </c>
-      <c r="H12" s="80">
+      <c r="H12" s="59">
         <v>9.8789999999999996</v>
       </c>
-      <c r="I12" s="80">
+      <c r="I12" s="59">
         <v>9.8650000000000002</v>
       </c>
-      <c r="J12" s="80"/>
-      <c r="K12" s="80"/>
-      <c r="L12" s="80">
+      <c r="J12" s="59"/>
+      <c r="K12" s="59"/>
+      <c r="L12" s="59">
         <v>9.8350000000000009</v>
       </c>
       <c r="N12" s="38">
@@ -8566,66 +8599,66 @@
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B13" s="73"/>
-      <c r="C13" s="86" t="s">
+      <c r="B13" s="92"/>
+      <c r="C13" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="87">
+      <c r="D13" s="66">
         <v>9.8689999999999998</v>
       </c>
-      <c r="E13" s="88"/>
-      <c r="F13" s="87">
+      <c r="E13" s="67"/>
+      <c r="F13" s="66">
         <f>G13-($F$1*Q12)</f>
         <v>9.8759999999999994</v>
       </c>
-      <c r="G13" s="87">
+      <c r="G13" s="66">
         <v>9.8919999999999995</v>
       </c>
-      <c r="H13" s="88">
+      <c r="H13" s="67">
         <f>G13-($H$1*R12)</f>
         <v>9.8699999999999992</v>
       </c>
-      <c r="I13" s="88">
+      <c r="I13" s="67">
         <f>G13-($I$1*R12)</f>
         <v>9.847999999999999</v>
       </c>
-      <c r="J13" s="88"/>
-      <c r="K13" s="88"/>
-      <c r="L13" s="88">
+      <c r="J13" s="67"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="67">
         <v>9.8350000000000009</v>
       </c>
       <c r="Q13" s="32"/>
       <c r="R13" s="32"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B14" s="73"/>
-      <c r="C14" s="89" t="s">
+      <c r="B14" s="92"/>
+      <c r="C14" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="90">
+      <c r="D14" s="69">
         <f>D13-0.05</f>
         <v>9.8189999999999991</v>
       </c>
-      <c r="E14" s="91"/>
-      <c r="F14" s="90">
+      <c r="E14" s="70"/>
+      <c r="F14" s="69">
         <f>F13-0.05</f>
         <v>9.8259999999999987</v>
       </c>
-      <c r="G14" s="90">
+      <c r="G14" s="69">
         <f>G13-0.05</f>
         <v>9.8419999999999987</v>
       </c>
-      <c r="H14" s="90">
+      <c r="H14" s="69">
         <f>H13-0.05</f>
         <v>9.8199999999999985</v>
       </c>
-      <c r="I14" s="90">
+      <c r="I14" s="69">
         <f>I13-0.05</f>
         <v>9.7979999999999983</v>
       </c>
-      <c r="J14" s="91"/>
-      <c r="K14" s="91"/>
-      <c r="L14" s="90">
+      <c r="J14" s="70"/>
+      <c r="K14" s="70"/>
+      <c r="L14" s="69">
         <f>L13-0.05</f>
         <v>9.7850000000000001</v>
       </c>
@@ -8633,79 +8666,79 @@
       <c r="R14" s="32"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B15" s="74"/>
-      <c r="C15" s="83" t="s">
+      <c r="B15" s="93"/>
+      <c r="C15" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="84">
+      <c r="D15" s="63">
         <v>0.05</v>
       </c>
-      <c r="E15" s="85"/>
-      <c r="F15" s="84">
+      <c r="E15" s="64"/>
+      <c r="F15" s="63">
         <f>F12-F14</f>
         <v>4.8000000000001819E-2</v>
       </c>
-      <c r="G15" s="84">
+      <c r="G15" s="63">
         <f>G12-G14</f>
         <v>5.9000000000001052E-2</v>
       </c>
-      <c r="H15" s="84">
+      <c r="H15" s="63">
         <f>H12-H14</f>
         <v>5.9000000000001052E-2</v>
       </c>
-      <c r="I15" s="84">
+      <c r="I15" s="63">
         <f>I12-I14</f>
         <v>6.7000000000001947E-2</v>
       </c>
-      <c r="J15" s="85"/>
-      <c r="K15" s="85"/>
-      <c r="L15" s="84">
+      <c r="J15" s="64"/>
+      <c r="K15" s="64"/>
+      <c r="L15" s="63">
         <v>0.05</v>
       </c>
       <c r="Q15" s="32"/>
       <c r="R15" s="32"/>
     </row>
-    <row r="16" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B16" s="94"/>
-      <c r="C16" s="96"/>
-      <c r="D16" s="97"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="97"/>
-      <c r="G16" s="97"/>
-      <c r="H16" s="97"/>
-      <c r="I16" s="97"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="95"/>
-      <c r="Q16" s="93"/>
-      <c r="R16" s="93"/>
+    <row r="16" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B16" s="71"/>
+      <c r="C16" s="73"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="75"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
+      <c r="J16" s="75"/>
+      <c r="K16" s="75"/>
+      <c r="L16" s="72"/>
+      <c r="Q16" s="32"/>
+      <c r="R16" s="32"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="91" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="81" t="s">
+      <c r="C17" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="82">
+      <c r="D17" s="61">
         <v>9.8829999999999991</v>
       </c>
-      <c r="E17" s="80"/>
-      <c r="F17" s="82">
+      <c r="E17" s="59"/>
+      <c r="F17" s="61">
         <v>9.9019999999999992</v>
       </c>
-      <c r="G17" s="82">
+      <c r="G17" s="61">
         <v>9.9350000000000005</v>
       </c>
-      <c r="H17" s="80">
+      <c r="H17" s="59">
         <v>9.9190000000000005</v>
       </c>
-      <c r="I17" s="80">
+      <c r="I17" s="59">
         <v>9.9019999999999992</v>
       </c>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80"/>
-      <c r="L17" s="80">
+      <c r="J17" s="59"/>
+      <c r="K17" s="59"/>
+      <c r="L17" s="59">
         <v>9.8780000000000001</v>
       </c>
       <c r="N17" s="38">
@@ -8722,66 +8755,66 @@
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B18" s="73"/>
-      <c r="C18" s="86" t="s">
+      <c r="B18" s="92"/>
+      <c r="C18" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="87">
+      <c r="D18" s="66">
         <v>9.8829999999999991</v>
       </c>
-      <c r="E18" s="88"/>
-      <c r="F18" s="87">
+      <c r="E18" s="67"/>
+      <c r="F18" s="66">
         <f>G18-($F$1*Q17)</f>
         <v>9.8989999999999991</v>
       </c>
-      <c r="G18" s="87">
+      <c r="G18" s="66">
         <v>9.9329999999999998</v>
       </c>
-      <c r="H18" s="88">
+      <c r="H18" s="67">
         <f>G18-($H$1*R17)</f>
         <v>9.9130000000000003</v>
       </c>
-      <c r="I18" s="88">
+      <c r="I18" s="67">
         <f>G18-($I$1*R17)</f>
         <v>9.8930000000000007</v>
       </c>
-      <c r="J18" s="88"/>
-      <c r="K18" s="88"/>
-      <c r="L18" s="88">
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="67">
         <v>9.8780000000000001</v>
       </c>
       <c r="Q18" s="32"/>
       <c r="R18" s="32"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B19" s="73"/>
-      <c r="C19" s="89" t="s">
+      <c r="B19" s="92"/>
+      <c r="C19" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="90">
+      <c r="D19" s="69">
         <f>D18-0.05</f>
         <v>9.8329999999999984</v>
       </c>
-      <c r="E19" s="91"/>
-      <c r="F19" s="90">
+      <c r="E19" s="70"/>
+      <c r="F19" s="69">
         <f>F18-0.05</f>
         <v>9.8489999999999984</v>
       </c>
-      <c r="G19" s="90">
+      <c r="G19" s="69">
         <f>G18-0.05</f>
         <v>9.8829999999999991</v>
       </c>
-      <c r="H19" s="90">
+      <c r="H19" s="69">
         <f>H18-0.05</f>
         <v>9.8629999999999995</v>
       </c>
-      <c r="I19" s="90">
+      <c r="I19" s="69">
         <f>I18-0.05</f>
         <v>9.843</v>
       </c>
-      <c r="J19" s="91"/>
-      <c r="K19" s="91"/>
-      <c r="L19" s="90">
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="69">
         <f>L18-0.05</f>
         <v>9.8279999999999994</v>
       </c>
@@ -8789,79 +8822,79 @@
       <c r="R19" s="32"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B20" s="74"/>
-      <c r="C20" s="83" t="s">
+      <c r="B20" s="93"/>
+      <c r="C20" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="84">
+      <c r="D20" s="63">
         <v>0.05</v>
       </c>
-      <c r="E20" s="85"/>
-      <c r="F20" s="84">
+      <c r="E20" s="64"/>
+      <c r="F20" s="63">
         <f>F17-F19</f>
         <v>5.3000000000000824E-2</v>
       </c>
-      <c r="G20" s="84">
+      <c r="G20" s="63">
         <f>G17-G19</f>
         <v>5.2000000000001378E-2</v>
       </c>
-      <c r="H20" s="84">
+      <c r="H20" s="63">
         <f>H17-H19</f>
         <v>5.6000000000000938E-2</v>
       </c>
-      <c r="I20" s="84">
+      <c r="I20" s="63">
         <f>I17-I19</f>
         <v>5.8999999999999275E-2</v>
       </c>
-      <c r="J20" s="85"/>
-      <c r="K20" s="85"/>
-      <c r="L20" s="84">
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="63">
         <v>0.05</v>
       </c>
       <c r="Q20" s="32"/>
       <c r="R20" s="32"/>
     </row>
-    <row r="21" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B21" s="94"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="98"/>
-      <c r="F21" s="97"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="98"/>
-      <c r="L21" s="95"/>
-      <c r="Q21" s="93"/>
-      <c r="R21" s="93"/>
+    <row r="21" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B21" s="71"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="75"/>
+      <c r="L21" s="72"/>
+      <c r="Q21" s="32"/>
+      <c r="R21" s="32"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B22" s="76" t="s">
+      <c r="B22" s="94" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="81" t="s">
+      <c r="C22" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="82">
+      <c r="D22" s="61">
         <v>9.8719999999999999</v>
       </c>
-      <c r="E22" s="80"/>
-      <c r="F22" s="82">
+      <c r="E22" s="59"/>
+      <c r="F22" s="61">
         <v>9.8930000000000007</v>
       </c>
-      <c r="G22" s="82">
+      <c r="G22" s="61">
         <v>9.9450000000000003</v>
       </c>
-      <c r="H22" s="80">
+      <c r="H22" s="59">
         <v>9.9160000000000004</v>
       </c>
-      <c r="I22" s="80">
+      <c r="I22" s="59">
         <v>9.8960000000000008</v>
       </c>
-      <c r="J22" s="80"/>
-      <c r="K22" s="80"/>
-      <c r="L22" s="80">
+      <c r="J22" s="59"/>
+      <c r="K22" s="59"/>
+      <c r="L22" s="59">
         <v>9.8729999999999993</v>
       </c>
       <c r="N22" s="38">
@@ -8878,66 +8911,66 @@
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B23" s="77"/>
-      <c r="C23" s="86" t="s">
+      <c r="B23" s="95"/>
+      <c r="C23" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D23" s="87">
+      <c r="D23" s="66">
         <v>9.8719999999999999</v>
       </c>
-      <c r="E23" s="88"/>
-      <c r="F23" s="87">
+      <c r="E23" s="67"/>
+      <c r="F23" s="66">
         <f>G23-($F$1*Q22)</f>
         <v>9.8979999999999997</v>
       </c>
-      <c r="G23" s="87">
+      <c r="G23" s="66">
         <v>9.9559999999999995</v>
       </c>
-      <c r="H23" s="88">
+      <c r="H23" s="67">
         <f>G23-($H$1*R22)</f>
         <v>9.9239999999999995</v>
       </c>
-      <c r="I23" s="88">
+      <c r="I23" s="67">
         <f>G23-($I$1*R22)</f>
         <v>9.8919999999999995</v>
       </c>
-      <c r="J23" s="88"/>
-      <c r="K23" s="88"/>
-      <c r="L23" s="88">
+      <c r="J23" s="67"/>
+      <c r="K23" s="67"/>
+      <c r="L23" s="67">
         <v>9.8729999999999993</v>
       </c>
       <c r="Q23" s="32"/>
       <c r="R23" s="32"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B24" s="77"/>
-      <c r="C24" s="89" t="s">
+      <c r="B24" s="95"/>
+      <c r="C24" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D24" s="90">
+      <c r="D24" s="69">
         <f>D23-0.05</f>
         <v>9.8219999999999992</v>
       </c>
-      <c r="E24" s="91"/>
-      <c r="F24" s="90">
+      <c r="E24" s="70"/>
+      <c r="F24" s="69">
         <f>F23-0.05</f>
         <v>9.847999999999999</v>
       </c>
-      <c r="G24" s="90">
+      <c r="G24" s="69">
         <f>G23-0.05</f>
         <v>9.9059999999999988</v>
       </c>
-      <c r="H24" s="90">
+      <c r="H24" s="69">
         <f>H23-0.05</f>
         <v>9.8739999999999988</v>
       </c>
-      <c r="I24" s="90">
+      <c r="I24" s="69">
         <f>I23-0.05</f>
         <v>9.8419999999999987</v>
       </c>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="90">
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="69">
         <f>L23-0.05</f>
         <v>9.8229999999999986</v>
       </c>
@@ -8945,79 +8978,79 @@
       <c r="R24" s="32"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B25" s="78"/>
-      <c r="C25" s="83" t="s">
+      <c r="B25" s="96"/>
+      <c r="C25" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D25" s="84">
+      <c r="D25" s="63">
         <v>0.05</v>
       </c>
-      <c r="E25" s="85"/>
-      <c r="F25" s="84">
+      <c r="E25" s="64"/>
+      <c r="F25" s="63">
         <f>F22-F24</f>
         <v>4.5000000000001705E-2</v>
       </c>
-      <c r="G25" s="84">
+      <c r="G25" s="63">
         <f>G22-G24</f>
         <v>3.9000000000001478E-2</v>
       </c>
-      <c r="H25" s="84">
+      <c r="H25" s="63">
         <f>H22-H24</f>
         <v>4.2000000000001592E-2</v>
       </c>
-      <c r="I25" s="84">
+      <c r="I25" s="63">
         <f>I22-I24</f>
         <v>5.4000000000002046E-2</v>
       </c>
-      <c r="J25" s="85"/>
-      <c r="K25" s="85"/>
-      <c r="L25" s="84">
+      <c r="J25" s="64"/>
+      <c r="K25" s="64"/>
+      <c r="L25" s="63">
         <v>0.05</v>
       </c>
       <c r="Q25" s="32"/>
       <c r="R25" s="32"/>
     </row>
-    <row r="26" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B26" s="94"/>
-      <c r="C26" s="96"/>
-      <c r="D26" s="97"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="97"/>
-      <c r="G26" s="97"/>
-      <c r="H26" s="97"/>
-      <c r="I26" s="97"/>
-      <c r="J26" s="98"/>
-      <c r="K26" s="98"/>
-      <c r="L26" s="95"/>
-      <c r="Q26" s="93"/>
-      <c r="R26" s="93"/>
+    <row r="26" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B26" s="71"/>
+      <c r="C26" s="73"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="75"/>
+      <c r="L26" s="72"/>
+      <c r="Q26" s="32"/>
+      <c r="R26" s="32"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="C27" s="81" t="s">
+      <c r="C27" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D27" s="82">
+      <c r="D27" s="61">
         <v>9.9030000000000005</v>
       </c>
-      <c r="E27" s="80"/>
-      <c r="F27" s="82">
+      <c r="E27" s="59"/>
+      <c r="F27" s="61">
         <v>9.9169999999999998</v>
       </c>
-      <c r="G27" s="82">
+      <c r="G27" s="61">
         <v>9.9469999999999992</v>
       </c>
-      <c r="H27" s="80">
+      <c r="H27" s="59">
         <v>9.9469999999999992</v>
       </c>
-      <c r="I27" s="80">
+      <c r="I27" s="59">
         <v>9.9149999999999991</v>
       </c>
-      <c r="J27" s="80"/>
-      <c r="K27" s="80"/>
-      <c r="L27" s="80">
+      <c r="J27" s="59"/>
+      <c r="K27" s="59"/>
+      <c r="L27" s="59">
         <v>9.8839999999999986</v>
       </c>
       <c r="N27" s="38">
@@ -9034,66 +9067,66 @@
       </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B28" s="73"/>
-      <c r="C28" s="86" t="s">
+      <c r="B28" s="92"/>
+      <c r="C28" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D28" s="87">
+      <c r="D28" s="66">
         <v>9.9030000000000005</v>
       </c>
-      <c r="E28" s="88"/>
-      <c r="F28" s="87">
+      <c r="E28" s="67"/>
+      <c r="F28" s="66">
         <f>G28-($F$1*Q27)</f>
         <v>9.9260000000000002</v>
       </c>
-      <c r="G28" s="87">
+      <c r="G28" s="66">
         <v>9.9740000000000002</v>
       </c>
-      <c r="H28" s="88">
+      <c r="H28" s="67">
         <f>G28-($H$1*R27)</f>
         <v>9.9380000000000006</v>
       </c>
-      <c r="I28" s="88">
+      <c r="I28" s="67">
         <f>G28-($I$1*R27)</f>
         <v>9.902000000000001</v>
       </c>
-      <c r="J28" s="88"/>
-      <c r="K28" s="88"/>
-      <c r="L28" s="88">
+      <c r="J28" s="67"/>
+      <c r="K28" s="67"/>
+      <c r="L28" s="67">
         <v>9.8839999999999986</v>
       </c>
       <c r="Q28" s="32"/>
       <c r="R28" s="32"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B29" s="73"/>
-      <c r="C29" s="89" t="s">
+      <c r="B29" s="92"/>
+      <c r="C29" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D29" s="90">
+      <c r="D29" s="69">
         <f>D28-0.05</f>
         <v>9.8529999999999998</v>
       </c>
-      <c r="E29" s="91"/>
-      <c r="F29" s="90">
+      <c r="E29" s="70"/>
+      <c r="F29" s="69">
         <f>F28-0.05</f>
         <v>9.8759999999999994</v>
       </c>
-      <c r="G29" s="90">
+      <c r="G29" s="69">
         <f>G28-0.05</f>
         <v>9.9239999999999995</v>
       </c>
-      <c r="H29" s="90">
+      <c r="H29" s="69">
         <f>H28-0.05</f>
         <v>9.8879999999999999</v>
       </c>
-      <c r="I29" s="90">
+      <c r="I29" s="69">
         <f>I28-0.05</f>
         <v>9.8520000000000003</v>
       </c>
-      <c r="J29" s="91"/>
-      <c r="K29" s="91"/>
-      <c r="L29" s="90">
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="69">
         <f>L28-0.05</f>
         <v>9.8339999999999979</v>
       </c>
@@ -9101,79 +9134,79 @@
       <c r="R29" s="32"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B30" s="74"/>
-      <c r="C30" s="83" t="s">
+      <c r="B30" s="93"/>
+      <c r="C30" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D30" s="84">
+      <c r="D30" s="63">
         <v>0.05</v>
       </c>
-      <c r="E30" s="85"/>
-      <c r="F30" s="84">
+      <c r="E30" s="64"/>
+      <c r="F30" s="63">
         <f>F27-F29</f>
         <v>4.1000000000000369E-2</v>
       </c>
-      <c r="G30" s="84">
+      <c r="G30" s="63">
         <f>G27-G29</f>
         <v>2.2999999999999687E-2</v>
       </c>
-      <c r="H30" s="84">
+      <c r="H30" s="63">
         <f>H27-H29</f>
         <v>5.8999999999999275E-2</v>
       </c>
-      <c r="I30" s="84">
+      <c r="I30" s="63">
         <f>I27-I29</f>
         <v>6.2999999999998835E-2</v>
       </c>
-      <c r="J30" s="85"/>
-      <c r="K30" s="85"/>
-      <c r="L30" s="84">
+      <c r="J30" s="64"/>
+      <c r="K30" s="64"/>
+      <c r="L30" s="63">
         <v>0.05</v>
       </c>
       <c r="Q30" s="32"/>
       <c r="R30" s="32"/>
     </row>
-    <row r="31" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B31" s="94"/>
-      <c r="C31" s="96"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="97"/>
-      <c r="H31" s="97"/>
-      <c r="I31" s="97"/>
-      <c r="J31" s="98"/>
-      <c r="K31" s="98"/>
-      <c r="L31" s="95"/>
-      <c r="Q31" s="93"/>
-      <c r="R31" s="93"/>
+    <row r="31" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B31" s="71"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="75"/>
+      <c r="L31" s="72"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B32" s="75" t="s">
+      <c r="B32" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="C32" s="81" t="s">
+      <c r="C32" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D32" s="82">
+      <c r="D32" s="61">
         <v>9.9260000000000002</v>
       </c>
-      <c r="E32" s="80"/>
-      <c r="F32" s="82">
+      <c r="E32" s="59"/>
+      <c r="F32" s="61">
         <v>9.9440000000000008</v>
       </c>
-      <c r="G32" s="82">
+      <c r="G32" s="61">
         <v>9.9870000000000001</v>
       </c>
-      <c r="H32" s="82">
+      <c r="H32" s="61">
         <v>9.9600000000000009</v>
       </c>
-      <c r="I32" s="80">
+      <c r="I32" s="59">
         <v>9.9280000000000008</v>
       </c>
-      <c r="J32" s="80"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="80">
+      <c r="J32" s="59"/>
+      <c r="K32" s="59"/>
+      <c r="L32" s="59">
         <v>9.9120000000000008</v>
       </c>
       <c r="N32" s="38">
@@ -9190,66 +9223,66 @@
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B33" s="73"/>
-      <c r="C33" s="86" t="s">
+      <c r="B33" s="92"/>
+      <c r="C33" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D33" s="87">
+      <c r="D33" s="66">
         <v>9.9260000000000002</v>
       </c>
-      <c r="E33" s="88"/>
-      <c r="F33" s="87">
+      <c r="E33" s="67"/>
+      <c r="F33" s="66">
         <f>G33-($F$1*Q32)</f>
         <v>9.9570000000000007</v>
       </c>
-      <c r="G33" s="87">
+      <c r="G33" s="66">
         <v>10.015000000000001</v>
       </c>
-      <c r="H33" s="88">
+      <c r="H33" s="67">
         <f>G33-($H$1*R32)</f>
         <v>9.9690000000000012</v>
       </c>
-      <c r="I33" s="88">
+      <c r="I33" s="67">
         <f>G33-($I$1*R32)</f>
         <v>9.923</v>
       </c>
-      <c r="J33" s="88"/>
-      <c r="K33" s="88"/>
-      <c r="L33" s="88">
+      <c r="J33" s="67"/>
+      <c r="K33" s="67"/>
+      <c r="L33" s="67">
         <v>9.9120000000000008</v>
       </c>
       <c r="Q33" s="32"/>
       <c r="R33" s="32"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B34" s="73"/>
-      <c r="C34" s="89" t="s">
+      <c r="B34" s="92"/>
+      <c r="C34" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D34" s="90">
+      <c r="D34" s="69">
         <f>D33-0.05</f>
         <v>9.8759999999999994</v>
       </c>
-      <c r="E34" s="91"/>
-      <c r="F34" s="90">
+      <c r="E34" s="70"/>
+      <c r="F34" s="69">
         <f>F33-0.05</f>
         <v>9.907</v>
       </c>
-      <c r="G34" s="90">
+      <c r="G34" s="69">
         <f>G33-0.05</f>
         <v>9.9649999999999999</v>
       </c>
-      <c r="H34" s="90">
+      <c r="H34" s="69">
         <f>H33-0.05</f>
         <v>9.9190000000000005</v>
       </c>
-      <c r="I34" s="90">
+      <c r="I34" s="69">
         <f>I33-0.05</f>
         <v>9.8729999999999993</v>
       </c>
-      <c r="J34" s="91"/>
-      <c r="K34" s="91"/>
-      <c r="L34" s="90">
+      <c r="J34" s="70"/>
+      <c r="K34" s="70"/>
+      <c r="L34" s="69">
         <f>L33-0.05</f>
         <v>9.8620000000000001</v>
       </c>
@@ -9257,77 +9290,77 @@
       <c r="R34" s="32"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B35" s="74"/>
-      <c r="C35" s="83" t="s">
+      <c r="B35" s="93"/>
+      <c r="C35" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D35" s="84">
+      <c r="D35" s="63">
         <v>0.05</v>
       </c>
-      <c r="E35" s="85"/>
-      <c r="F35" s="84">
+      <c r="E35" s="64"/>
+      <c r="F35" s="63">
         <f>F32-F34</f>
         <v>3.700000000000081E-2</v>
       </c>
-      <c r="G35" s="84">
+      <c r="G35" s="63">
         <f>G32-G34</f>
         <v>2.2000000000000242E-2</v>
       </c>
-      <c r="H35" s="84">
+      <c r="H35" s="63">
         <f>H32-H34</f>
         <v>4.1000000000000369E-2</v>
       </c>
-      <c r="I35" s="84">
+      <c r="I35" s="63">
         <f>I32-I34</f>
         <v>5.5000000000001492E-2</v>
       </c>
-      <c r="J35" s="85"/>
-      <c r="K35" s="85"/>
-      <c r="L35" s="84">
+      <c r="J35" s="64"/>
+      <c r="K35" s="64"/>
+      <c r="L35" s="63">
         <v>0.05</v>
       </c>
       <c r="Q35" s="32"/>
       <c r="R35" s="32"/>
     </row>
-    <row r="36" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B36" s="94"/>
-      <c r="C36" s="96"/>
-      <c r="D36" s="97"/>
-      <c r="E36" s="98"/>
-      <c r="F36" s="97"/>
-      <c r="G36" s="97"/>
-      <c r="H36" s="97"/>
-      <c r="I36" s="97"/>
-      <c r="J36" s="98"/>
-      <c r="K36" s="98"/>
-      <c r="L36" s="95"/>
-      <c r="Q36" s="93"/>
-      <c r="R36" s="93"/>
+    <row r="36" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="71"/>
+      <c r="C36" s="73"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="75"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="74"/>
+      <c r="I36" s="74"/>
+      <c r="J36" s="75"/>
+      <c r="K36" s="75"/>
+      <c r="L36" s="72"/>
+      <c r="Q36" s="32"/>
+      <c r="R36" s="32"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B37" s="75" t="s">
+      <c r="B37" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="81" t="s">
+      <c r="C37" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D37" s="82">
+      <c r="D37" s="61">
         <v>10.038</v>
       </c>
-      <c r="E37" s="80"/>
-      <c r="F37" s="82">
+      <c r="E37" s="59"/>
+      <c r="F37" s="61">
         <v>10.036</v>
       </c>
-      <c r="G37" s="82">
+      <c r="G37" s="61">
         <v>10.026</v>
       </c>
-      <c r="H37" s="80">
+      <c r="H37" s="59">
         <v>9.9969999999999999</v>
       </c>
-      <c r="I37" s="80"/>
-      <c r="J37" s="80"/>
-      <c r="K37" s="80"/>
-      <c r="L37" s="80">
+      <c r="I37" s="59"/>
+      <c r="J37" s="59"/>
+      <c r="K37" s="59"/>
+      <c r="L37" s="59">
         <v>9.9559999999999995</v>
       </c>
       <c r="N37" s="38">
@@ -9344,60 +9377,60 @@
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B38" s="73"/>
-      <c r="C38" s="86" t="s">
+      <c r="B38" s="92"/>
+      <c r="C38" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D38" s="87">
+      <c r="D38" s="66">
         <v>10.038</v>
       </c>
-      <c r="E38" s="88"/>
-      <c r="F38" s="87">
+      <c r="E38" s="67"/>
+      <c r="F38" s="66">
         <f>G38-($F$1*Q37)</f>
         <v>10.045</v>
       </c>
-      <c r="G38" s="87">
+      <c r="G38" s="66">
         <v>10.055</v>
       </c>
-      <c r="H38" s="88">
+      <c r="H38" s="67">
         <f>G38-($H$1*R37)</f>
         <v>10.004999999999999</v>
       </c>
-      <c r="I38" s="88"/>
-      <c r="J38" s="88"/>
-      <c r="K38" s="88"/>
-      <c r="L38" s="88">
+      <c r="I38" s="67"/>
+      <c r="J38" s="67"/>
+      <c r="K38" s="67"/>
+      <c r="L38" s="67">
         <v>9.9559999999999995</v>
       </c>
       <c r="Q38" s="32"/>
       <c r="R38" s="32"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B39" s="73"/>
-      <c r="C39" s="89" t="s">
+      <c r="B39" s="92"/>
+      <c r="C39" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D39" s="90">
+      <c r="D39" s="69">
         <f>D38-0.05</f>
         <v>9.9879999999999995</v>
       </c>
-      <c r="E39" s="91"/>
-      <c r="F39" s="90">
+      <c r="E39" s="70"/>
+      <c r="F39" s="69">
         <f>F38-0.05</f>
         <v>9.9949999999999992</v>
       </c>
-      <c r="G39" s="90">
+      <c r="G39" s="69">
         <f>G38-0.05</f>
         <v>10.004999999999999</v>
       </c>
-      <c r="H39" s="90">
+      <c r="H39" s="69">
         <f>H38-0.05</f>
         <v>9.9549999999999983</v>
       </c>
-      <c r="I39" s="91"/>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="90">
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="69">
         <f>L38-0.05</f>
         <v>9.9059999999999988</v>
       </c>
@@ -9405,74 +9438,74 @@
       <c r="R39" s="32"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B40" s="74"/>
-      <c r="C40" s="83" t="s">
+      <c r="B40" s="93"/>
+      <c r="C40" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D40" s="84">
+      <c r="D40" s="63">
         <v>0.05</v>
       </c>
-      <c r="E40" s="85"/>
-      <c r="F40" s="84">
+      <c r="E40" s="64"/>
+      <c r="F40" s="63">
         <f>F37-F39</f>
         <v>4.1000000000000369E-2</v>
       </c>
-      <c r="G40" s="84">
+      <c r="G40" s="63">
         <f>G37-G39</f>
         <v>2.1000000000000796E-2</v>
       </c>
-      <c r="H40" s="84">
+      <c r="H40" s="63">
         <f>H37-H39</f>
         <v>4.2000000000001592E-2</v>
       </c>
-      <c r="I40" s="85"/>
-      <c r="J40" s="85"/>
-      <c r="K40" s="85"/>
-      <c r="L40" s="84">
+      <c r="I40" s="64"/>
+      <c r="J40" s="64"/>
+      <c r="K40" s="64"/>
+      <c r="L40" s="63">
         <v>0.05</v>
       </c>
       <c r="Q40" s="32"/>
       <c r="R40" s="32"/>
     </row>
-    <row r="41" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B41" s="94"/>
-      <c r="C41" s="96"/>
-      <c r="D41" s="97"/>
-      <c r="E41" s="98"/>
-      <c r="F41" s="97"/>
-      <c r="G41" s="97"/>
-      <c r="H41" s="97"/>
-      <c r="I41" s="97"/>
-      <c r="J41" s="98"/>
-      <c r="K41" s="98"/>
-      <c r="L41" s="95"/>
-      <c r="Q41" s="93"/>
-      <c r="R41" s="93"/>
+    <row r="41" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B41" s="71"/>
+      <c r="C41" s="73"/>
+      <c r="D41" s="74"/>
+      <c r="E41" s="75"/>
+      <c r="F41" s="74"/>
+      <c r="G41" s="74"/>
+      <c r="H41" s="74"/>
+      <c r="I41" s="74"/>
+      <c r="J41" s="75"/>
+      <c r="K41" s="75"/>
+      <c r="L41" s="72"/>
+      <c r="Q41" s="32"/>
+      <c r="R41" s="32"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B42" s="76" t="s">
+      <c r="B42" s="94" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="81" t="s">
+      <c r="C42" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D42" s="82">
+      <c r="D42" s="61">
         <v>10.052</v>
       </c>
-      <c r="E42" s="80"/>
-      <c r="F42" s="82">
+      <c r="E42" s="59"/>
+      <c r="F42" s="61">
         <v>10.055999999999999</v>
       </c>
-      <c r="G42" s="82">
+      <c r="G42" s="61">
         <v>10.054</v>
       </c>
-      <c r="H42" s="80">
+      <c r="H42" s="59">
         <v>10.007999999999999</v>
       </c>
-      <c r="I42" s="80"/>
-      <c r="J42" s="80"/>
-      <c r="K42" s="80"/>
-      <c r="L42" s="80">
+      <c r="I42" s="59"/>
+      <c r="J42" s="59"/>
+      <c r="K42" s="59"/>
+      <c r="L42" s="59">
         <v>9.9589999999999996</v>
       </c>
       <c r="N42" s="38">
@@ -9489,60 +9522,60 @@
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B43" s="77"/>
-      <c r="C43" s="86" t="s">
+      <c r="B43" s="95"/>
+      <c r="C43" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D43" s="87">
+      <c r="D43" s="66">
         <v>10.052</v>
       </c>
-      <c r="E43" s="88"/>
-      <c r="F43" s="87">
+      <c r="E43" s="67"/>
+      <c r="F43" s="66">
         <f>G43-($F$1*Q42)</f>
         <v>10.052999999999999</v>
       </c>
-      <c r="G43" s="87">
+      <c r="G43" s="66">
         <v>10.055</v>
       </c>
-      <c r="H43" s="88">
+      <c r="H43" s="67">
         <f>G43-($H$1*R42)</f>
         <v>10.004999999999999</v>
       </c>
-      <c r="I43" s="88"/>
-      <c r="J43" s="88"/>
-      <c r="K43" s="88"/>
-      <c r="L43" s="88">
+      <c r="I43" s="67"/>
+      <c r="J43" s="67"/>
+      <c r="K43" s="67"/>
+      <c r="L43" s="67">
         <v>9.9589999999999996</v>
       </c>
       <c r="Q43" s="32"/>
       <c r="R43" s="32"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B44" s="77"/>
-      <c r="C44" s="89" t="s">
+      <c r="B44" s="95"/>
+      <c r="C44" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D44" s="90">
+      <c r="D44" s="69">
         <f>D43-0.05</f>
         <v>10.001999999999999</v>
       </c>
-      <c r="E44" s="91"/>
-      <c r="F44" s="90">
+      <c r="E44" s="70"/>
+      <c r="F44" s="69">
         <f>F43-0.05</f>
         <v>10.002999999999998</v>
       </c>
-      <c r="G44" s="90">
+      <c r="G44" s="69">
         <f>G43-0.05</f>
         <v>10.004999999999999</v>
       </c>
-      <c r="H44" s="90">
+      <c r="H44" s="69">
         <f>H43-0.05</f>
         <v>9.9549999999999983</v>
       </c>
-      <c r="I44" s="91"/>
-      <c r="J44" s="91"/>
-      <c r="K44" s="91"/>
-      <c r="L44" s="90">
+      <c r="I44" s="70"/>
+      <c r="J44" s="70"/>
+      <c r="K44" s="70"/>
+      <c r="L44" s="69">
         <f>L43-0.05</f>
         <v>9.9089999999999989</v>
       </c>
@@ -9550,74 +9583,74 @@
       <c r="R44" s="32"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B45" s="78"/>
-      <c r="C45" s="83" t="s">
+      <c r="B45" s="96"/>
+      <c r="C45" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D45" s="84">
+      <c r="D45" s="63">
         <v>0.05</v>
       </c>
-      <c r="E45" s="85"/>
-      <c r="F45" s="84">
+      <c r="E45" s="64"/>
+      <c r="F45" s="63">
         <f>F42-F44</f>
         <v>5.3000000000000824E-2</v>
       </c>
-      <c r="G45" s="84">
+      <c r="G45" s="63">
         <f>G42-G44</f>
         <v>4.9000000000001265E-2</v>
       </c>
-      <c r="H45" s="84">
+      <c r="H45" s="63">
         <f>H42-H44</f>
         <v>5.3000000000000824E-2</v>
       </c>
-      <c r="I45" s="85"/>
-      <c r="J45" s="85"/>
-      <c r="K45" s="85"/>
-      <c r="L45" s="84">
+      <c r="I45" s="64"/>
+      <c r="J45" s="64"/>
+      <c r="K45" s="64"/>
+      <c r="L45" s="63">
         <v>0.05</v>
       </c>
       <c r="Q45" s="32"/>
       <c r="R45" s="32"/>
     </row>
-    <row r="46" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B46" s="94"/>
-      <c r="C46" s="96"/>
-      <c r="D46" s="97"/>
-      <c r="E46" s="98"/>
-      <c r="F46" s="97"/>
-      <c r="G46" s="97"/>
-      <c r="H46" s="97"/>
-      <c r="I46" s="97"/>
-      <c r="J46" s="98"/>
-      <c r="K46" s="98"/>
-      <c r="L46" s="95"/>
-      <c r="Q46" s="93"/>
-      <c r="R46" s="93"/>
+    <row r="46" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B46" s="71"/>
+      <c r="C46" s="73"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="75"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="74"/>
+      <c r="H46" s="74"/>
+      <c r="I46" s="74"/>
+      <c r="J46" s="75"/>
+      <c r="K46" s="75"/>
+      <c r="L46" s="72"/>
+      <c r="Q46" s="32"/>
+      <c r="R46" s="32"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B47" s="75" t="s">
+      <c r="B47" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="81" t="s">
+      <c r="C47" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D47" s="82">
+      <c r="D47" s="61">
         <v>10.002000000000001</v>
       </c>
-      <c r="E47" s="80"/>
-      <c r="F47" s="82">
+      <c r="E47" s="59"/>
+      <c r="F47" s="61">
         <v>10.013999999999999</v>
       </c>
-      <c r="G47" s="82">
+      <c r="G47" s="61">
         <v>10.045999999999999</v>
       </c>
-      <c r="H47" s="80">
+      <c r="H47" s="59">
         <v>10.006</v>
       </c>
-      <c r="I47" s="80"/>
-      <c r="J47" s="80"/>
-      <c r="K47" s="80"/>
-      <c r="L47" s="80">
+      <c r="I47" s="59"/>
+      <c r="J47" s="59"/>
+      <c r="K47" s="59"/>
+      <c r="L47" s="59">
         <v>9.968</v>
       </c>
       <c r="N47" s="38">
@@ -9634,60 +9667,60 @@
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B48" s="73"/>
-      <c r="C48" s="86" t="s">
+      <c r="B48" s="92"/>
+      <c r="C48" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D48" s="87">
+      <c r="D48" s="66">
         <v>10.002000000000001</v>
       </c>
-      <c r="E48" s="88"/>
-      <c r="F48" s="87">
+      <c r="E48" s="67"/>
+      <c r="F48" s="66">
         <f>G48-($F$1*Q47)</f>
         <v>10.020999999999999</v>
       </c>
-      <c r="G48" s="87">
+      <c r="G48" s="66">
         <v>10.055</v>
       </c>
-      <c r="H48" s="88">
+      <c r="H48" s="67">
         <f>G48-($H$1*R47)</f>
         <v>10.004999999999999</v>
       </c>
-      <c r="I48" s="88"/>
-      <c r="J48" s="88"/>
-      <c r="K48" s="88"/>
-      <c r="L48" s="88">
+      <c r="I48" s="67"/>
+      <c r="J48" s="67"/>
+      <c r="K48" s="67"/>
+      <c r="L48" s="67">
         <v>9.968</v>
       </c>
       <c r="Q48" s="32"/>
       <c r="R48" s="32"/>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B49" s="73"/>
-      <c r="C49" s="89" t="s">
+      <c r="B49" s="92"/>
+      <c r="C49" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D49" s="90">
+      <c r="D49" s="69">
         <f>D48-0.05</f>
         <v>9.952</v>
       </c>
-      <c r="E49" s="91"/>
-      <c r="F49" s="90">
+      <c r="E49" s="70"/>
+      <c r="F49" s="69">
         <f>F48-0.05</f>
         <v>9.9709999999999983</v>
       </c>
-      <c r="G49" s="90">
+      <c r="G49" s="69">
         <f>G48-0.05</f>
         <v>10.004999999999999</v>
       </c>
-      <c r="H49" s="90">
+      <c r="H49" s="69">
         <f>H48-0.05</f>
         <v>9.9549999999999983</v>
       </c>
-      <c r="I49" s="91"/>
-      <c r="J49" s="91"/>
-      <c r="K49" s="91"/>
-      <c r="L49" s="90">
+      <c r="I49" s="70"/>
+      <c r="J49" s="70"/>
+      <c r="K49" s="70"/>
+      <c r="L49" s="69">
         <f>L48-0.05</f>
         <v>9.9179999999999993</v>
       </c>
@@ -9695,74 +9728,74 @@
       <c r="R49" s="32"/>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B50" s="74"/>
-      <c r="C50" s="83" t="s">
+      <c r="B50" s="93"/>
+      <c r="C50" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D50" s="84">
+      <c r="D50" s="63">
         <v>0.05</v>
       </c>
-      <c r="E50" s="85"/>
-      <c r="F50" s="84">
+      <c r="E50" s="64"/>
+      <c r="F50" s="63">
         <f>F47-F49</f>
         <v>4.3000000000001037E-2</v>
       </c>
-      <c r="G50" s="84">
+      <c r="G50" s="63">
         <f>G47-G49</f>
         <v>4.1000000000000369E-2</v>
       </c>
-      <c r="H50" s="84">
+      <c r="H50" s="63">
         <f>H47-H49</f>
         <v>5.1000000000001933E-2</v>
       </c>
-      <c r="I50" s="85"/>
-      <c r="J50" s="85"/>
-      <c r="K50" s="85"/>
-      <c r="L50" s="84">
+      <c r="I50" s="64"/>
+      <c r="J50" s="64"/>
+      <c r="K50" s="64"/>
+      <c r="L50" s="63">
         <v>0.05</v>
       </c>
       <c r="Q50" s="32"/>
       <c r="R50" s="32"/>
     </row>
-    <row r="51" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B51" s="94"/>
-      <c r="C51" s="96"/>
-      <c r="D51" s="97"/>
-      <c r="E51" s="98"/>
-      <c r="F51" s="97"/>
-      <c r="G51" s="97"/>
-      <c r="H51" s="97"/>
-      <c r="I51" s="97"/>
-      <c r="J51" s="98"/>
-      <c r="K51" s="98"/>
-      <c r="L51" s="95"/>
-      <c r="Q51" s="93"/>
-      <c r="R51" s="93"/>
+    <row r="51" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B51" s="71"/>
+      <c r="C51" s="73"/>
+      <c r="D51" s="74"/>
+      <c r="E51" s="75"/>
+      <c r="F51" s="74"/>
+      <c r="G51" s="74"/>
+      <c r="H51" s="74"/>
+      <c r="I51" s="74"/>
+      <c r="J51" s="75"/>
+      <c r="K51" s="75"/>
+      <c r="L51" s="72"/>
+      <c r="Q51" s="32"/>
+      <c r="R51" s="32"/>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B52" s="75" t="s">
+      <c r="B52" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="81" t="s">
+      <c r="C52" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D52" s="82">
+      <c r="D52" s="61">
         <v>9.9960000000000004</v>
       </c>
-      <c r="E52" s="80"/>
-      <c r="F52" s="82">
+      <c r="E52" s="59"/>
+      <c r="F52" s="61">
         <v>10.016999999999999</v>
       </c>
-      <c r="G52" s="82">
+      <c r="G52" s="61">
         <v>10.048999999999999</v>
       </c>
-      <c r="H52" s="80">
+      <c r="H52" s="59">
         <v>10.015000000000001</v>
       </c>
-      <c r="I52" s="80"/>
-      <c r="J52" s="80"/>
-      <c r="K52" s="80"/>
-      <c r="L52" s="80">
+      <c r="I52" s="59"/>
+      <c r="J52" s="59"/>
+      <c r="K52" s="59"/>
+      <c r="L52" s="59">
         <v>9.9920000000000009</v>
       </c>
       <c r="N52" s="38">
@@ -9779,60 +9812,60 @@
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B53" s="73"/>
-      <c r="C53" s="86" t="s">
+      <c r="B53" s="92"/>
+      <c r="C53" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D53" s="87">
+      <c r="D53" s="66">
         <v>9.9960000000000004</v>
       </c>
-      <c r="E53" s="88"/>
-      <c r="F53" s="87">
+      <c r="E53" s="67"/>
+      <c r="F53" s="66">
         <f>G53-($F$1*Q52)</f>
         <v>10.019</v>
       </c>
-      <c r="G53" s="87">
+      <c r="G53" s="66">
         <v>10.055</v>
       </c>
-      <c r="H53" s="88">
+      <c r="H53" s="67">
         <f>G53-($H$1*R52)</f>
         <v>10.015000000000001</v>
       </c>
-      <c r="I53" s="88"/>
-      <c r="J53" s="88"/>
-      <c r="K53" s="88"/>
-      <c r="L53" s="88">
+      <c r="I53" s="67"/>
+      <c r="J53" s="67"/>
+      <c r="K53" s="67"/>
+      <c r="L53" s="67">
         <v>9.9920000000000009</v>
       </c>
       <c r="Q53" s="32"/>
       <c r="R53" s="32"/>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B54" s="73"/>
-      <c r="C54" s="89" t="s">
+      <c r="B54" s="92"/>
+      <c r="C54" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D54" s="90">
+      <c r="D54" s="69">
         <f>D53-0.05</f>
         <v>9.9459999999999997</v>
       </c>
-      <c r="E54" s="91"/>
-      <c r="F54" s="90">
+      <c r="E54" s="70"/>
+      <c r="F54" s="69">
         <f>F53-0.05</f>
         <v>9.9689999999999994</v>
       </c>
-      <c r="G54" s="90">
+      <c r="G54" s="69">
         <f>G53-0.05</f>
         <v>10.004999999999999</v>
       </c>
-      <c r="H54" s="90">
+      <c r="H54" s="69">
         <f>H53-0.05</f>
         <v>9.9649999999999999</v>
       </c>
-      <c r="I54" s="91"/>
-      <c r="J54" s="91"/>
-      <c r="K54" s="91"/>
-      <c r="L54" s="90">
+      <c r="I54" s="70"/>
+      <c r="J54" s="70"/>
+      <c r="K54" s="70"/>
+      <c r="L54" s="69">
         <f>L53-0.05</f>
         <v>9.9420000000000002</v>
       </c>
@@ -9840,74 +9873,74 @@
       <c r="R54" s="32"/>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B55" s="74"/>
-      <c r="C55" s="83" t="s">
+      <c r="B55" s="93"/>
+      <c r="C55" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D55" s="84">
+      <c r="D55" s="63">
         <v>0.05</v>
       </c>
-      <c r="E55" s="85"/>
-      <c r="F55" s="84">
+      <c r="E55" s="64"/>
+      <c r="F55" s="63">
         <f>F52-F54</f>
         <v>4.8000000000000043E-2</v>
       </c>
-      <c r="G55" s="84">
+      <c r="G55" s="63">
         <f>G52-G54</f>
         <v>4.4000000000000483E-2</v>
       </c>
-      <c r="H55" s="84">
+      <c r="H55" s="63">
         <f>H52-H54</f>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="I55" s="85"/>
-      <c r="J55" s="85"/>
-      <c r="K55" s="85"/>
-      <c r="L55" s="84">
+      <c r="I55" s="64"/>
+      <c r="J55" s="64"/>
+      <c r="K55" s="64"/>
+      <c r="L55" s="63">
         <v>0.05</v>
       </c>
       <c r="Q55" s="32"/>
       <c r="R55" s="32"/>
     </row>
-    <row r="56" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B56" s="94"/>
-      <c r="C56" s="96"/>
-      <c r="D56" s="97"/>
-      <c r="E56" s="98"/>
-      <c r="F56" s="97"/>
-      <c r="G56" s="97"/>
-      <c r="H56" s="97"/>
-      <c r="I56" s="97"/>
-      <c r="J56" s="98"/>
-      <c r="K56" s="98"/>
-      <c r="L56" s="95"/>
-      <c r="Q56" s="93"/>
-      <c r="R56" s="93"/>
+    <row r="56" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B56" s="71"/>
+      <c r="C56" s="73"/>
+      <c r="D56" s="74"/>
+      <c r="E56" s="75"/>
+      <c r="F56" s="74"/>
+      <c r="G56" s="74"/>
+      <c r="H56" s="74"/>
+      <c r="I56" s="74"/>
+      <c r="J56" s="75"/>
+      <c r="K56" s="75"/>
+      <c r="L56" s="72"/>
+      <c r="Q56" s="32"/>
+      <c r="R56" s="32"/>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B57" s="75" t="s">
+      <c r="B57" s="91" t="s">
         <v>31</v>
       </c>
-      <c r="C57" s="81" t="s">
+      <c r="C57" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D57" s="82">
+      <c r="D57" s="61">
         <v>10.002000000000001</v>
       </c>
-      <c r="E57" s="80"/>
-      <c r="F57" s="82">
+      <c r="E57" s="59"/>
+      <c r="F57" s="61">
         <v>10.029</v>
       </c>
-      <c r="G57" s="82">
+      <c r="G57" s="61">
         <v>10.068</v>
       </c>
-      <c r="H57" s="80">
+      <c r="H57" s="59">
         <v>10.026999999999999</v>
       </c>
-      <c r="I57" s="80"/>
-      <c r="J57" s="80"/>
-      <c r="K57" s="80"/>
-      <c r="L57" s="80">
+      <c r="I57" s="59"/>
+      <c r="J57" s="59"/>
+      <c r="K57" s="59"/>
+      <c r="L57" s="59">
         <v>9.9990000000000006</v>
       </c>
       <c r="N57" s="38">
@@ -9924,60 +9957,60 @@
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B58" s="73"/>
-      <c r="C58" s="86" t="s">
+      <c r="B58" s="92"/>
+      <c r="C58" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D58" s="87">
+      <c r="D58" s="66">
         <v>10.002000000000001</v>
       </c>
-      <c r="E58" s="88"/>
-      <c r="F58" s="87">
+      <c r="E58" s="67"/>
+      <c r="F58" s="66">
         <f>G58-($F$1*Q57)</f>
         <v>10.030000000000001</v>
       </c>
-      <c r="G58" s="87">
+      <c r="G58" s="66">
         <v>10.076000000000001</v>
       </c>
-      <c r="H58" s="88">
+      <c r="H58" s="67">
         <f>G58-($H$1*R57)</f>
         <v>10.028</v>
       </c>
-      <c r="I58" s="87"/>
-      <c r="J58" s="88"/>
-      <c r="K58" s="88"/>
-      <c r="L58" s="88">
+      <c r="I58" s="66"/>
+      <c r="J58" s="67"/>
+      <c r="K58" s="67"/>
+      <c r="L58" s="67">
         <v>9.9990000000000006</v>
       </c>
       <c r="Q58" s="32"/>
       <c r="R58" s="32"/>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B59" s="73"/>
-      <c r="C59" s="89" t="s">
+      <c r="B59" s="92"/>
+      <c r="C59" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D59" s="90">
+      <c r="D59" s="69">
         <f>D58-0.05</f>
         <v>9.952</v>
       </c>
-      <c r="E59" s="91"/>
-      <c r="F59" s="90">
+      <c r="E59" s="70"/>
+      <c r="F59" s="69">
         <f>F58-0.05</f>
         <v>9.98</v>
       </c>
-      <c r="G59" s="90">
+      <c r="G59" s="69">
         <f>G58-0.05</f>
         <v>10.026</v>
       </c>
-      <c r="H59" s="90">
+      <c r="H59" s="69">
         <f>H58-0.05</f>
         <v>9.9779999999999998</v>
       </c>
-      <c r="I59" s="91"/>
-      <c r="J59" s="91"/>
-      <c r="K59" s="91"/>
-      <c r="L59" s="90">
+      <c r="I59" s="70"/>
+      <c r="J59" s="70"/>
+      <c r="K59" s="70"/>
+      <c r="L59" s="69">
         <f>L58-0.05</f>
         <v>9.9489999999999998</v>
       </c>
@@ -9985,74 +10018,74 @@
       <c r="R59" s="32"/>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B60" s="74"/>
-      <c r="C60" s="83" t="s">
+      <c r="B60" s="93"/>
+      <c r="C60" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D60" s="84">
+      <c r="D60" s="63">
         <v>0.05</v>
       </c>
-      <c r="E60" s="85"/>
-      <c r="F60" s="84">
+      <c r="E60" s="64"/>
+      <c r="F60" s="63">
         <f>F57-F59</f>
         <v>4.8999999999999488E-2</v>
       </c>
-      <c r="G60" s="84">
+      <c r="G60" s="63">
         <f>G57-G59</f>
         <v>4.1999999999999815E-2</v>
       </c>
-      <c r="H60" s="84">
+      <c r="H60" s="63">
         <f>H57-H59</f>
         <v>4.8999999999999488E-2</v>
       </c>
-      <c r="I60" s="85"/>
-      <c r="J60" s="85"/>
-      <c r="K60" s="85"/>
-      <c r="L60" s="84">
+      <c r="I60" s="64"/>
+      <c r="J60" s="64"/>
+      <c r="K60" s="64"/>
+      <c r="L60" s="63">
         <v>0.05</v>
       </c>
       <c r="Q60" s="32"/>
       <c r="R60" s="32"/>
     </row>
-    <row r="61" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B61" s="94"/>
-      <c r="C61" s="96"/>
-      <c r="D61" s="97"/>
-      <c r="E61" s="98"/>
-      <c r="F61" s="97"/>
-      <c r="G61" s="97"/>
-      <c r="H61" s="97"/>
-      <c r="I61" s="97"/>
-      <c r="J61" s="98"/>
-      <c r="K61" s="98"/>
-      <c r="L61" s="95"/>
-      <c r="Q61" s="93"/>
-      <c r="R61" s="93"/>
+    <row r="61" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B61" s="71"/>
+      <c r="C61" s="73"/>
+      <c r="D61" s="74"/>
+      <c r="E61" s="75"/>
+      <c r="F61" s="74"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="74"/>
+      <c r="I61" s="74"/>
+      <c r="J61" s="75"/>
+      <c r="K61" s="75"/>
+      <c r="L61" s="72"/>
+      <c r="Q61" s="32"/>
+      <c r="R61" s="32"/>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B62" s="75" t="s">
+      <c r="B62" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="C62" s="81" t="s">
+      <c r="C62" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D62" s="82">
+      <c r="D62" s="61">
         <v>10.019</v>
       </c>
-      <c r="E62" s="80"/>
-      <c r="F62" s="82">
+      <c r="E62" s="59"/>
+      <c r="F62" s="61">
         <v>10.047000000000001</v>
       </c>
-      <c r="G62" s="82">
+      <c r="G62" s="61">
         <v>10.087999999999999</v>
       </c>
-      <c r="H62" s="80">
+      <c r="H62" s="59">
         <v>10.048</v>
       </c>
-      <c r="I62" s="80"/>
-      <c r="J62" s="80"/>
-      <c r="K62" s="80"/>
-      <c r="L62" s="80">
+      <c r="I62" s="59"/>
+      <c r="J62" s="59"/>
+      <c r="K62" s="59"/>
+      <c r="L62" s="59">
         <v>10.023999999999999</v>
       </c>
       <c r="N62" s="38">
@@ -10069,60 +10102,60 @@
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B63" s="73"/>
-      <c r="C63" s="86" t="s">
+      <c r="B63" s="92"/>
+      <c r="C63" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D63" s="87">
+      <c r="D63" s="66">
         <v>10.019</v>
       </c>
-      <c r="E63" s="88"/>
-      <c r="F63" s="87">
+      <c r="E63" s="67"/>
+      <c r="F63" s="66">
         <f>G63-($F$1*Q62)</f>
         <v>10.048999999999999</v>
       </c>
-      <c r="G63" s="87">
+      <c r="G63" s="66">
         <v>10.097</v>
       </c>
-      <c r="H63" s="88">
+      <c r="H63" s="67">
         <f>G63-($H$1*R62)</f>
         <v>10.051</v>
       </c>
-      <c r="I63" s="88"/>
-      <c r="J63" s="88"/>
-      <c r="K63" s="88"/>
-      <c r="L63" s="88">
+      <c r="I63" s="67"/>
+      <c r="J63" s="67"/>
+      <c r="K63" s="67"/>
+      <c r="L63" s="67">
         <v>10.023999999999999</v>
       </c>
       <c r="Q63" s="32"/>
       <c r="R63" s="32"/>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B64" s="73"/>
-      <c r="C64" s="89" t="s">
+      <c r="B64" s="92"/>
+      <c r="C64" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D64" s="90">
+      <c r="D64" s="69">
         <f>D63-0.05</f>
         <v>9.9689999999999994</v>
       </c>
-      <c r="E64" s="91"/>
-      <c r="F64" s="90">
+      <c r="E64" s="70"/>
+      <c r="F64" s="69">
         <f>F63-0.05</f>
         <v>9.9989999999999988</v>
       </c>
-      <c r="G64" s="90">
+      <c r="G64" s="69">
         <f>G63-0.05</f>
         <v>10.046999999999999</v>
       </c>
-      <c r="H64" s="90">
+      <c r="H64" s="69">
         <f>H63-0.05</f>
         <v>10.000999999999999</v>
       </c>
-      <c r="I64" s="91"/>
-      <c r="J64" s="91"/>
-      <c r="K64" s="91"/>
-      <c r="L64" s="90">
+      <c r="I64" s="70"/>
+      <c r="J64" s="70"/>
+      <c r="K64" s="70"/>
+      <c r="L64" s="69">
         <f>L63-0.05</f>
         <v>9.9739999999999984</v>
       </c>
@@ -10130,74 +10163,74 @@
       <c r="R64" s="32"/>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B65" s="74"/>
-      <c r="C65" s="83" t="s">
+      <c r="B65" s="93"/>
+      <c r="C65" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D65" s="84">
+      <c r="D65" s="63">
         <v>0.05</v>
       </c>
-      <c r="E65" s="85"/>
-      <c r="F65" s="84">
+      <c r="E65" s="64"/>
+      <c r="F65" s="63">
         <f>F62-F64</f>
         <v>4.8000000000001819E-2</v>
       </c>
-      <c r="G65" s="84">
+      <c r="G65" s="63">
         <f>G62-G64</f>
         <v>4.1000000000000369E-2</v>
       </c>
-      <c r="H65" s="84">
+      <c r="H65" s="63">
         <f>H62-H64</f>
         <v>4.7000000000000597E-2</v>
       </c>
-      <c r="I65" s="85"/>
-      <c r="J65" s="85"/>
-      <c r="K65" s="85"/>
-      <c r="L65" s="84">
+      <c r="I65" s="64"/>
+      <c r="J65" s="64"/>
+      <c r="K65" s="64"/>
+      <c r="L65" s="63">
         <v>0.05</v>
       </c>
       <c r="Q65" s="32"/>
       <c r="R65" s="32"/>
     </row>
-    <row r="66" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B66" s="94"/>
-      <c r="C66" s="96"/>
-      <c r="D66" s="97"/>
-      <c r="E66" s="98"/>
-      <c r="F66" s="97"/>
-      <c r="G66" s="97"/>
-      <c r="H66" s="97"/>
-      <c r="I66" s="97"/>
-      <c r="J66" s="98"/>
-      <c r="K66" s="98"/>
-      <c r="L66" s="95"/>
-      <c r="Q66" s="93"/>
-      <c r="R66" s="93"/>
+    <row r="66" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B66" s="71"/>
+      <c r="C66" s="73"/>
+      <c r="D66" s="74"/>
+      <c r="E66" s="75"/>
+      <c r="F66" s="74"/>
+      <c r="G66" s="74"/>
+      <c r="H66" s="74"/>
+      <c r="I66" s="74"/>
+      <c r="J66" s="75"/>
+      <c r="K66" s="75"/>
+      <c r="L66" s="72"/>
+      <c r="Q66" s="32"/>
+      <c r="R66" s="32"/>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B67" s="75" t="s">
+      <c r="B67" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="C67" s="81" t="s">
+      <c r="C67" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D67" s="82">
+      <c r="D67" s="61">
         <v>10.037000000000001</v>
       </c>
-      <c r="E67" s="80"/>
-      <c r="F67" s="82">
+      <c r="E67" s="59"/>
+      <c r="F67" s="61">
         <v>10.055</v>
       </c>
-      <c r="G67" s="82">
+      <c r="G67" s="61">
         <v>10.089</v>
       </c>
-      <c r="H67" s="82">
+      <c r="H67" s="61">
         <v>10.06</v>
       </c>
-      <c r="I67" s="80"/>
-      <c r="J67" s="80"/>
-      <c r="K67" s="80"/>
-      <c r="L67" s="80">
+      <c r="I67" s="59"/>
+      <c r="J67" s="59"/>
+      <c r="K67" s="59"/>
+      <c r="L67" s="59">
         <v>10.035</v>
       </c>
       <c r="N67" s="38">
@@ -10214,60 +10247,60 @@
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B68" s="73"/>
-      <c r="C68" s="86" t="s">
+      <c r="B68" s="92"/>
+      <c r="C68" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D68" s="87">
+      <c r="D68" s="66">
         <v>10.037000000000001</v>
       </c>
-      <c r="E68" s="88"/>
-      <c r="F68" s="87">
+      <c r="E68" s="67"/>
+      <c r="F68" s="66">
         <f>G68-($F$1*Q67)</f>
         <v>10.068</v>
       </c>
-      <c r="G68" s="87">
+      <c r="G68" s="66">
         <v>10.118</v>
       </c>
-      <c r="H68" s="88">
+      <c r="H68" s="67">
         <f>G68-($H$1*R67)</f>
         <v>10.066000000000001</v>
       </c>
-      <c r="I68" s="88"/>
-      <c r="J68" s="88"/>
-      <c r="K68" s="88"/>
-      <c r="L68" s="88">
+      <c r="I68" s="67"/>
+      <c r="J68" s="67"/>
+      <c r="K68" s="67"/>
+      <c r="L68" s="67">
         <v>10.035</v>
       </c>
       <c r="Q68" s="32"/>
       <c r="R68" s="32"/>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B69" s="73"/>
-      <c r="C69" s="89" t="s">
+      <c r="B69" s="92"/>
+      <c r="C69" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D69" s="90">
+      <c r="D69" s="69">
         <f>D68-0.05</f>
         <v>9.9870000000000001</v>
       </c>
-      <c r="E69" s="91"/>
-      <c r="F69" s="90">
+      <c r="E69" s="70"/>
+      <c r="F69" s="69">
         <f>F68-0.05</f>
         <v>10.017999999999999</v>
       </c>
-      <c r="G69" s="90">
+      <c r="G69" s="69">
         <f>G68-0.05</f>
         <v>10.068</v>
       </c>
-      <c r="H69" s="90">
+      <c r="H69" s="69">
         <f>H68-0.05</f>
         <v>10.016</v>
       </c>
-      <c r="I69" s="91"/>
-      <c r="J69" s="91"/>
-      <c r="K69" s="91"/>
-      <c r="L69" s="90">
+      <c r="I69" s="70"/>
+      <c r="J69" s="70"/>
+      <c r="K69" s="70"/>
+      <c r="L69" s="69">
         <f>L68-0.05</f>
         <v>9.9849999999999994</v>
       </c>
@@ -10275,74 +10308,74 @@
       <c r="R69" s="32"/>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B70" s="74"/>
-      <c r="C70" s="83" t="s">
+      <c r="B70" s="93"/>
+      <c r="C70" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D70" s="84">
+      <c r="D70" s="63">
         <v>0.05</v>
       </c>
-      <c r="E70" s="85"/>
-      <c r="F70" s="84">
+      <c r="E70" s="64"/>
+      <c r="F70" s="63">
         <f>F67-F69</f>
         <v>3.700000000000081E-2</v>
       </c>
-      <c r="G70" s="84">
+      <c r="G70" s="63">
         <f>G67-G69</f>
         <v>2.1000000000000796E-2</v>
       </c>
-      <c r="H70" s="84">
+      <c r="H70" s="63">
         <f>H67-H69</f>
         <v>4.4000000000000483E-2</v>
       </c>
-      <c r="I70" s="85"/>
-      <c r="J70" s="85"/>
-      <c r="K70" s="85"/>
-      <c r="L70" s="84">
+      <c r="I70" s="64"/>
+      <c r="J70" s="64"/>
+      <c r="K70" s="64"/>
+      <c r="L70" s="63">
         <v>0.05</v>
       </c>
       <c r="Q70" s="32"/>
       <c r="R70" s="32"/>
     </row>
-    <row r="71" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B71" s="94"/>
-      <c r="C71" s="96"/>
-      <c r="D71" s="97"/>
-      <c r="E71" s="98"/>
-      <c r="F71" s="97"/>
-      <c r="G71" s="97"/>
-      <c r="H71" s="97"/>
-      <c r="I71" s="97"/>
-      <c r="J71" s="98"/>
-      <c r="K71" s="98"/>
-      <c r="L71" s="95"/>
-      <c r="Q71" s="93"/>
-      <c r="R71" s="93"/>
+    <row r="71" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B71" s="71"/>
+      <c r="C71" s="73"/>
+      <c r="D71" s="74"/>
+      <c r="E71" s="75"/>
+      <c r="F71" s="74"/>
+      <c r="G71" s="74"/>
+      <c r="H71" s="74"/>
+      <c r="I71" s="74"/>
+      <c r="J71" s="75"/>
+      <c r="K71" s="75"/>
+      <c r="L71" s="72"/>
+      <c r="Q71" s="32"/>
+      <c r="R71" s="32"/>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B72" s="75" t="s">
+      <c r="B72" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="C72" s="81" t="s">
+      <c r="C72" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D72" s="82">
+      <c r="D72" s="61">
         <v>10.103</v>
       </c>
-      <c r="E72" s="80"/>
-      <c r="F72" s="82">
+      <c r="E72" s="59"/>
+      <c r="F72" s="61">
         <v>10.106</v>
       </c>
-      <c r="G72" s="82">
+      <c r="G72" s="61">
         <v>10.138</v>
       </c>
-      <c r="H72" s="80">
+      <c r="H72" s="59">
         <v>10.105</v>
       </c>
-      <c r="I72" s="80"/>
-      <c r="J72" s="80"/>
-      <c r="K72" s="80"/>
-      <c r="L72" s="80">
+      <c r="I72" s="59"/>
+      <c r="J72" s="59"/>
+      <c r="K72" s="59"/>
+      <c r="L72" s="59">
         <v>10.071999999999999</v>
       </c>
       <c r="N72" s="38">
@@ -10359,60 +10392,60 @@
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B73" s="73"/>
-      <c r="C73" s="86" t="s">
+      <c r="B73" s="92"/>
+      <c r="C73" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D73" s="87">
+      <c r="D73" s="66">
         <v>10.103</v>
       </c>
-      <c r="E73" s="88"/>
-      <c r="F73" s="87">
+      <c r="E73" s="67"/>
+      <c r="F73" s="66">
         <f>G73-($F$1*Q72)</f>
         <v>10.116999999999999</v>
       </c>
-      <c r="G73" s="87">
+      <c r="G73" s="66">
         <v>10.138999999999999</v>
       </c>
-      <c r="H73" s="88">
+      <c r="H73" s="67">
         <f>G73-($H$1*R72)</f>
         <v>10.097</v>
       </c>
-      <c r="I73" s="88"/>
-      <c r="J73" s="88"/>
-      <c r="K73" s="88"/>
-      <c r="L73" s="88">
+      <c r="I73" s="67"/>
+      <c r="J73" s="67"/>
+      <c r="K73" s="67"/>
+      <c r="L73" s="67">
         <v>10.071999999999999</v>
       </c>
       <c r="Q73" s="32"/>
       <c r="R73" s="32"/>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B74" s="73"/>
-      <c r="C74" s="89" t="s">
+      <c r="B74" s="92"/>
+      <c r="C74" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D74" s="90">
+      <c r="D74" s="69">
         <f>D73-0.05</f>
         <v>10.052999999999999</v>
       </c>
-      <c r="E74" s="91"/>
-      <c r="F74" s="90">
+      <c r="E74" s="70"/>
+      <c r="F74" s="69">
         <f>F73-0.05</f>
         <v>10.066999999999998</v>
       </c>
-      <c r="G74" s="90">
+      <c r="G74" s="69">
         <f>G73-0.05</f>
         <v>10.088999999999999</v>
       </c>
-      <c r="H74" s="90">
+      <c r="H74" s="69">
         <f>H73-0.05</f>
         <v>10.046999999999999</v>
       </c>
-      <c r="I74" s="91"/>
-      <c r="J74" s="91"/>
-      <c r="K74" s="91"/>
-      <c r="L74" s="90">
+      <c r="I74" s="70"/>
+      <c r="J74" s="70"/>
+      <c r="K74" s="70"/>
+      <c r="L74" s="69">
         <f>L73-0.05</f>
         <v>10.021999999999998</v>
       </c>
@@ -10420,74 +10453,74 @@
       <c r="R74" s="32"/>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B75" s="74"/>
-      <c r="C75" s="83" t="s">
+      <c r="B75" s="93"/>
+      <c r="C75" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D75" s="84">
+      <c r="D75" s="63">
         <v>0.05</v>
       </c>
-      <c r="E75" s="85"/>
-      <c r="F75" s="84">
+      <c r="E75" s="64"/>
+      <c r="F75" s="63">
         <f>F72-F74</f>
         <v>3.9000000000001478E-2</v>
       </c>
-      <c r="G75" s="84">
+      <c r="G75" s="63">
         <f>G72-G74</f>
         <v>4.9000000000001265E-2</v>
       </c>
-      <c r="H75" s="84">
+      <c r="H75" s="63">
         <f>H72-H74</f>
         <v>5.8000000000001606E-2</v>
       </c>
-      <c r="I75" s="85"/>
-      <c r="J75" s="85"/>
-      <c r="K75" s="85"/>
-      <c r="L75" s="84">
+      <c r="I75" s="64"/>
+      <c r="J75" s="64"/>
+      <c r="K75" s="64"/>
+      <c r="L75" s="63">
         <v>0.05</v>
       </c>
       <c r="Q75" s="32"/>
       <c r="R75" s="32"/>
     </row>
-    <row r="76" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B76" s="94"/>
-      <c r="C76" s="96"/>
-      <c r="D76" s="97"/>
-      <c r="E76" s="98"/>
-      <c r="F76" s="97"/>
-      <c r="G76" s="97"/>
-      <c r="H76" s="97"/>
-      <c r="I76" s="97"/>
-      <c r="J76" s="98"/>
-      <c r="K76" s="98"/>
-      <c r="L76" s="95"/>
-      <c r="Q76" s="93"/>
-      <c r="R76" s="93"/>
+    <row r="76" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B76" s="71"/>
+      <c r="C76" s="73"/>
+      <c r="D76" s="74"/>
+      <c r="E76" s="75"/>
+      <c r="F76" s="74"/>
+      <c r="G76" s="74"/>
+      <c r="H76" s="74"/>
+      <c r="I76" s="74"/>
+      <c r="J76" s="75"/>
+      <c r="K76" s="75"/>
+      <c r="L76" s="72"/>
+      <c r="Q76" s="32"/>
+      <c r="R76" s="32"/>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B77" s="76" t="s">
+      <c r="B77" s="94" t="s">
         <v>44</v>
       </c>
-      <c r="C77" s="81" t="s">
+      <c r="C77" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D77" s="82">
+      <c r="D77" s="61">
         <v>10.132</v>
       </c>
-      <c r="E77" s="80"/>
-      <c r="F77" s="82">
+      <c r="E77" s="59"/>
+      <c r="F77" s="61">
         <v>10.128</v>
       </c>
-      <c r="G77" s="82">
+      <c r="G77" s="61">
         <v>10.153</v>
       </c>
-      <c r="H77" s="80">
+      <c r="H77" s="59">
         <v>10.112</v>
       </c>
-      <c r="I77" s="80"/>
-      <c r="J77" s="80"/>
-      <c r="K77" s="80"/>
-      <c r="L77" s="82">
+      <c r="I77" s="59"/>
+      <c r="J77" s="59"/>
+      <c r="K77" s="59"/>
+      <c r="L77" s="61">
         <v>10.07</v>
       </c>
       <c r="N77" s="38">
@@ -10504,60 +10537,60 @@
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B78" s="77"/>
-      <c r="C78" s="86" t="s">
+      <c r="B78" s="95"/>
+      <c r="C78" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D78" s="87">
+      <c r="D78" s="66">
         <v>10.132</v>
       </c>
-      <c r="E78" s="88"/>
-      <c r="F78" s="87">
+      <c r="E78" s="67"/>
+      <c r="F78" s="66">
         <f>G78-($F$1*Q77)</f>
         <v>10.138</v>
       </c>
-      <c r="G78" s="87">
+      <c r="G78" s="66">
         <v>10.15</v>
       </c>
-      <c r="H78" s="87">
+      <c r="H78" s="66">
         <f>G78-($H$1*R77)</f>
         <v>10.1</v>
       </c>
-      <c r="I78" s="88"/>
-      <c r="J78" s="88"/>
-      <c r="K78" s="88"/>
-      <c r="L78" s="87">
+      <c r="I78" s="67"/>
+      <c r="J78" s="67"/>
+      <c r="K78" s="67"/>
+      <c r="L78" s="66">
         <v>10.07</v>
       </c>
       <c r="Q78" s="32"/>
       <c r="R78" s="32"/>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B79" s="77"/>
-      <c r="C79" s="89" t="s">
+      <c r="B79" s="95"/>
+      <c r="C79" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D79" s="90">
+      <c r="D79" s="69">
         <f>D78-0.05</f>
         <v>10.081999999999999</v>
       </c>
-      <c r="E79" s="91"/>
-      <c r="F79" s="90">
+      <c r="E79" s="70"/>
+      <c r="F79" s="69">
         <f>F78-0.05</f>
         <v>10.087999999999999</v>
       </c>
-      <c r="G79" s="90">
+      <c r="G79" s="69">
         <f>G78-0.05</f>
         <v>10.1</v>
       </c>
-      <c r="H79" s="90">
+      <c r="H79" s="69">
         <f>H78-0.05</f>
         <v>10.049999999999999</v>
       </c>
-      <c r="I79" s="91"/>
-      <c r="J79" s="91"/>
-      <c r="K79" s="91"/>
-      <c r="L79" s="90">
+      <c r="I79" s="70"/>
+      <c r="J79" s="70"/>
+      <c r="K79" s="70"/>
+      <c r="L79" s="69">
         <f>L78-0.05</f>
         <v>10.02</v>
       </c>
@@ -10565,74 +10598,74 @@
       <c r="R79" s="32"/>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B80" s="78"/>
-      <c r="C80" s="83" t="s">
+      <c r="B80" s="96"/>
+      <c r="C80" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D80" s="84">
+      <c r="D80" s="63">
         <v>0.05</v>
       </c>
-      <c r="E80" s="85"/>
-      <c r="F80" s="84">
+      <c r="E80" s="64"/>
+      <c r="F80" s="63">
         <f>F77-F79</f>
         <v>4.0000000000000924E-2</v>
       </c>
-      <c r="G80" s="84">
+      <c r="G80" s="63">
         <f>G77-G79</f>
         <v>5.3000000000000824E-2</v>
       </c>
-      <c r="H80" s="84">
+      <c r="H80" s="63">
         <f>H77-H79</f>
         <v>6.2000000000001165E-2</v>
       </c>
-      <c r="I80" s="85"/>
-      <c r="J80" s="85"/>
-      <c r="K80" s="85"/>
-      <c r="L80" s="84">
+      <c r="I80" s="64"/>
+      <c r="J80" s="64"/>
+      <c r="K80" s="64"/>
+      <c r="L80" s="63">
         <v>0.05</v>
       </c>
       <c r="Q80" s="32"/>
       <c r="R80" s="32"/>
     </row>
-    <row r="81" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B81" s="94"/>
-      <c r="C81" s="96"/>
-      <c r="D81" s="97"/>
-      <c r="E81" s="98"/>
-      <c r="F81" s="97"/>
-      <c r="G81" s="97"/>
-      <c r="H81" s="97"/>
-      <c r="I81" s="97"/>
-      <c r="J81" s="98"/>
-      <c r="K81" s="98"/>
-      <c r="L81" s="95"/>
-      <c r="Q81" s="93"/>
-      <c r="R81" s="93"/>
+    <row r="81" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B81" s="71"/>
+      <c r="C81" s="73"/>
+      <c r="D81" s="74"/>
+      <c r="E81" s="75"/>
+      <c r="F81" s="74"/>
+      <c r="G81" s="74"/>
+      <c r="H81" s="74"/>
+      <c r="I81" s="74"/>
+      <c r="J81" s="75"/>
+      <c r="K81" s="75"/>
+      <c r="L81" s="72"/>
+      <c r="Q81" s="32"/>
+      <c r="R81" s="32"/>
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B82" s="75" t="s">
+      <c r="B82" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="C82" s="81" t="s">
+      <c r="C82" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D82" s="82">
+      <c r="D82" s="61">
         <v>10.108000000000001</v>
       </c>
-      <c r="E82" s="80"/>
-      <c r="F82" s="82">
+      <c r="E82" s="59"/>
+      <c r="F82" s="61">
         <v>10.122999999999999</v>
       </c>
-      <c r="G82" s="82">
+      <c r="G82" s="61">
         <v>10.154</v>
       </c>
-      <c r="H82" s="80">
+      <c r="H82" s="59">
         <v>10.135</v>
       </c>
-      <c r="I82" s="80"/>
-      <c r="J82" s="80"/>
-      <c r="K82" s="80"/>
-      <c r="L82" s="80">
+      <c r="I82" s="59"/>
+      <c r="J82" s="59"/>
+      <c r="K82" s="59"/>
+      <c r="L82" s="59">
         <v>10.098000000000001</v>
       </c>
       <c r="N82" s="38">
@@ -10649,60 +10682,60 @@
       </c>
     </row>
     <row r="83" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B83" s="73"/>
-      <c r="C83" s="86" t="s">
+      <c r="B83" s="92"/>
+      <c r="C83" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D83" s="87">
+      <c r="D83" s="66">
         <v>10.108000000000001</v>
       </c>
-      <c r="E83" s="88"/>
-      <c r="F83" s="87">
+      <c r="E83" s="67"/>
+      <c r="F83" s="66">
         <f>G83-($F$1*Q82)</f>
         <v>10.130000000000001</v>
       </c>
-      <c r="G83" s="87">
+      <c r="G83" s="66">
         <v>10.166</v>
       </c>
-      <c r="H83" s="88">
+      <c r="H83" s="67">
         <f>G83-($H$1*R82)</f>
         <v>10.124000000000001</v>
       </c>
-      <c r="I83" s="88"/>
-      <c r="J83" s="88"/>
-      <c r="K83" s="88"/>
-      <c r="L83" s="88">
+      <c r="I83" s="67"/>
+      <c r="J83" s="67"/>
+      <c r="K83" s="67"/>
+      <c r="L83" s="67">
         <v>10.098000000000001</v>
       </c>
       <c r="Q83" s="32"/>
       <c r="R83" s="32"/>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B84" s="73"/>
-      <c r="C84" s="89" t="s">
+      <c r="B84" s="92"/>
+      <c r="C84" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D84" s="90">
+      <c r="D84" s="69">
         <f>D83-0.05</f>
         <v>10.058</v>
       </c>
-      <c r="E84" s="91"/>
-      <c r="F84" s="90">
+      <c r="E84" s="70"/>
+      <c r="F84" s="69">
         <f>F83-0.05</f>
         <v>10.08</v>
       </c>
-      <c r="G84" s="90">
+      <c r="G84" s="69">
         <f>G83-0.05</f>
         <v>10.116</v>
       </c>
-      <c r="H84" s="90">
+      <c r="H84" s="69">
         <f>H83-0.05</f>
         <v>10.074</v>
       </c>
-      <c r="I84" s="91"/>
-      <c r="J84" s="91"/>
-      <c r="K84" s="91"/>
-      <c r="L84" s="90">
+      <c r="I84" s="70"/>
+      <c r="J84" s="70"/>
+      <c r="K84" s="70"/>
+      <c r="L84" s="69">
         <f>L83-0.05</f>
         <v>10.048</v>
       </c>
@@ -10710,74 +10743,74 @@
       <c r="R84" s="32"/>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B85" s="74"/>
-      <c r="C85" s="83" t="s">
+      <c r="B85" s="93"/>
+      <c r="C85" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D85" s="84">
+      <c r="D85" s="63">
         <v>0.05</v>
       </c>
-      <c r="E85" s="85"/>
-      <c r="F85" s="84">
+      <c r="E85" s="64"/>
+      <c r="F85" s="63">
         <f>F82-F84</f>
         <v>4.2999999999999261E-2</v>
       </c>
-      <c r="G85" s="84">
+      <c r="G85" s="63">
         <f>G82-G84</f>
         <v>3.8000000000000256E-2</v>
       </c>
-      <c r="H85" s="84">
+      <c r="H85" s="63">
         <f>H82-H84</f>
         <v>6.0999999999999943E-2</v>
       </c>
-      <c r="I85" s="85"/>
-      <c r="J85" s="85"/>
-      <c r="K85" s="85"/>
-      <c r="L85" s="84">
+      <c r="I85" s="64"/>
+      <c r="J85" s="64"/>
+      <c r="K85" s="64"/>
+      <c r="L85" s="63">
         <v>0.05</v>
       </c>
       <c r="Q85" s="32"/>
       <c r="R85" s="32"/>
     </row>
-    <row r="86" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B86" s="94"/>
-      <c r="C86" s="96"/>
-      <c r="D86" s="97"/>
-      <c r="E86" s="98"/>
-      <c r="F86" s="97"/>
-      <c r="G86" s="97"/>
-      <c r="H86" s="97"/>
-      <c r="I86" s="97"/>
-      <c r="J86" s="98"/>
-      <c r="K86" s="98"/>
-      <c r="L86" s="95"/>
-      <c r="Q86" s="93"/>
-      <c r="R86" s="93"/>
+    <row r="86" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B86" s="71"/>
+      <c r="C86" s="73"/>
+      <c r="D86" s="74"/>
+      <c r="E86" s="75"/>
+      <c r="F86" s="74"/>
+      <c r="G86" s="74"/>
+      <c r="H86" s="74"/>
+      <c r="I86" s="74"/>
+      <c r="J86" s="75"/>
+      <c r="K86" s="75"/>
+      <c r="L86" s="72"/>
+      <c r="Q86" s="32"/>
+      <c r="R86" s="32"/>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B87" s="75" t="s">
+      <c r="B87" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="C87" s="81" t="s">
+      <c r="C87" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D87" s="82">
+      <c r="D87" s="61">
         <v>10.14</v>
       </c>
-      <c r="E87" s="80"/>
-      <c r="F87" s="82">
+      <c r="E87" s="59"/>
+      <c r="F87" s="61">
         <v>10.157999999999999</v>
       </c>
-      <c r="G87" s="82">
+      <c r="G87" s="61">
         <v>10.192</v>
       </c>
-      <c r="H87" s="80">
+      <c r="H87" s="59">
         <v>10.172000000000001</v>
       </c>
-      <c r="I87" s="80"/>
-      <c r="J87" s="80"/>
-      <c r="K87" s="80"/>
-      <c r="L87" s="80">
+      <c r="I87" s="59"/>
+      <c r="J87" s="59"/>
+      <c r="K87" s="59"/>
+      <c r="L87" s="59">
         <v>10.141999999999999</v>
       </c>
       <c r="N87" s="38">
@@ -10794,60 +10827,60 @@
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B88" s="73"/>
-      <c r="C88" s="86" t="s">
+      <c r="B88" s="92"/>
+      <c r="C88" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D88" s="87">
+      <c r="D88" s="66">
         <v>10.14</v>
       </c>
-      <c r="E88" s="88"/>
-      <c r="F88" s="87">
+      <c r="E88" s="67"/>
+      <c r="F88" s="66">
         <f>G88-($F$1*Q87)</f>
         <v>10.158999999999999</v>
       </c>
-      <c r="G88" s="87">
+      <c r="G88" s="66">
         <v>10.193</v>
       </c>
-      <c r="H88" s="88">
+      <c r="H88" s="67">
         <f>G88-($H$1*R87)</f>
         <v>10.161</v>
       </c>
-      <c r="I88" s="88"/>
-      <c r="J88" s="88"/>
-      <c r="K88" s="88"/>
-      <c r="L88" s="88">
+      <c r="I88" s="67"/>
+      <c r="J88" s="67"/>
+      <c r="K88" s="67"/>
+      <c r="L88" s="67">
         <v>10.141999999999999</v>
       </c>
       <c r="Q88" s="32"/>
       <c r="R88" s="32"/>
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B89" s="73"/>
-      <c r="C89" s="89" t="s">
+      <c r="B89" s="92"/>
+      <c r="C89" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D89" s="90">
+      <c r="D89" s="69">
         <f>D88-0.05</f>
         <v>10.09</v>
       </c>
-      <c r="E89" s="91"/>
-      <c r="F89" s="90">
+      <c r="E89" s="70"/>
+      <c r="F89" s="69">
         <f>F88-0.05</f>
         <v>10.108999999999998</v>
       </c>
-      <c r="G89" s="90">
+      <c r="G89" s="69">
         <f>G88-0.05</f>
         <v>10.142999999999999</v>
       </c>
-      <c r="H89" s="90">
+      <c r="H89" s="69">
         <f>H88-0.05</f>
         <v>10.110999999999999</v>
       </c>
-      <c r="I89" s="91"/>
-      <c r="J89" s="91"/>
-      <c r="K89" s="91"/>
-      <c r="L89" s="90">
+      <c r="I89" s="70"/>
+      <c r="J89" s="70"/>
+      <c r="K89" s="70"/>
+      <c r="L89" s="69">
         <f>L88-0.05</f>
         <v>10.091999999999999</v>
       </c>
@@ -10855,74 +10888,74 @@
       <c r="R89" s="32"/>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B90" s="74"/>
-      <c r="C90" s="83" t="s">
+      <c r="B90" s="93"/>
+      <c r="C90" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D90" s="84">
+      <c r="D90" s="63">
         <v>0.05</v>
       </c>
-      <c r="E90" s="85"/>
-      <c r="F90" s="84">
+      <c r="E90" s="64"/>
+      <c r="F90" s="63">
         <f>F87-F89</f>
         <v>4.9000000000001265E-2</v>
       </c>
-      <c r="G90" s="84">
+      <c r="G90" s="63">
         <f>G87-G89</f>
         <v>4.9000000000001265E-2</v>
       </c>
-      <c r="H90" s="84">
+      <c r="H90" s="63">
         <f>H87-H89</f>
         <v>6.100000000000172E-2</v>
       </c>
-      <c r="I90" s="85"/>
-      <c r="J90" s="85"/>
-      <c r="K90" s="85"/>
-      <c r="L90" s="84">
+      <c r="I90" s="64"/>
+      <c r="J90" s="64"/>
+      <c r="K90" s="64"/>
+      <c r="L90" s="63">
         <v>0.05</v>
       </c>
       <c r="Q90" s="32"/>
       <c r="R90" s="32"/>
     </row>
-    <row r="91" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B91" s="94"/>
-      <c r="C91" s="96"/>
-      <c r="D91" s="97"/>
-      <c r="E91" s="98"/>
-      <c r="F91" s="97"/>
-      <c r="G91" s="97"/>
-      <c r="H91" s="97"/>
-      <c r="I91" s="97"/>
-      <c r="J91" s="98"/>
-      <c r="K91" s="98"/>
-      <c r="L91" s="95"/>
-      <c r="Q91" s="93"/>
-      <c r="R91" s="93"/>
+    <row r="91" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B91" s="71"/>
+      <c r="C91" s="73"/>
+      <c r="D91" s="74"/>
+      <c r="E91" s="75"/>
+      <c r="F91" s="74"/>
+      <c r="G91" s="74"/>
+      <c r="H91" s="74"/>
+      <c r="I91" s="74"/>
+      <c r="J91" s="75"/>
+      <c r="K91" s="75"/>
+      <c r="L91" s="72"/>
+      <c r="Q91" s="32"/>
+      <c r="R91" s="32"/>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B92" s="75" t="s">
+      <c r="B92" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="C92" s="81" t="s">
+      <c r="C92" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D92" s="82">
+      <c r="D92" s="61">
         <v>10.196</v>
       </c>
-      <c r="E92" s="80"/>
-      <c r="F92" s="82">
+      <c r="E92" s="59"/>
+      <c r="F92" s="61">
         <v>10.212</v>
       </c>
-      <c r="G92" s="82">
+      <c r="G92" s="61">
         <v>10.228</v>
       </c>
-      <c r="H92" s="80">
+      <c r="H92" s="59">
         <v>10.208</v>
       </c>
-      <c r="I92" s="80"/>
-      <c r="J92" s="80"/>
-      <c r="K92" s="80"/>
-      <c r="L92" s="82">
+      <c r="I92" s="59"/>
+      <c r="J92" s="59"/>
+      <c r="K92" s="59"/>
+      <c r="L92" s="61">
         <v>10.19</v>
       </c>
       <c r="N92" s="38">
@@ -10939,60 +10972,60 @@
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B93" s="73"/>
-      <c r="C93" s="86" t="s">
+      <c r="B93" s="92"/>
+      <c r="C93" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D93" s="87">
+      <c r="D93" s="66">
         <v>10.196</v>
       </c>
-      <c r="E93" s="88"/>
-      <c r="F93" s="87">
+      <c r="E93" s="67"/>
+      <c r="F93" s="66">
         <f>G93-($F$1*Q92)</f>
         <v>10.215999999999999</v>
       </c>
-      <c r="G93" s="87">
+      <c r="G93" s="66">
         <v>10.25</v>
       </c>
-      <c r="H93" s="88">
+      <c r="H93" s="67">
         <f>G93-($H$1*R92)</f>
         <v>10.212</v>
       </c>
-      <c r="I93" s="88"/>
-      <c r="J93" s="88"/>
-      <c r="K93" s="88"/>
-      <c r="L93" s="87">
+      <c r="I93" s="67"/>
+      <c r="J93" s="67"/>
+      <c r="K93" s="67"/>
+      <c r="L93" s="66">
         <v>10.19</v>
       </c>
       <c r="Q93" s="32"/>
       <c r="R93" s="32"/>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B94" s="73"/>
-      <c r="C94" s="89" t="s">
+      <c r="B94" s="92"/>
+      <c r="C94" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D94" s="90">
+      <c r="D94" s="69">
         <f>D93-0.05</f>
         <v>10.145999999999999</v>
       </c>
-      <c r="E94" s="91"/>
-      <c r="F94" s="90">
+      <c r="E94" s="70"/>
+      <c r="F94" s="69">
         <f>F93-0.05</f>
         <v>10.165999999999999</v>
       </c>
-      <c r="G94" s="90">
+      <c r="G94" s="69">
         <f>G93-0.05</f>
         <v>10.199999999999999</v>
       </c>
-      <c r="H94" s="90">
+      <c r="H94" s="69">
         <f>H93-0.05</f>
         <v>10.161999999999999</v>
       </c>
-      <c r="I94" s="91"/>
-      <c r="J94" s="91"/>
-      <c r="K94" s="91"/>
-      <c r="L94" s="90">
+      <c r="I94" s="70"/>
+      <c r="J94" s="70"/>
+      <c r="K94" s="70"/>
+      <c r="L94" s="69">
         <f>L93-0.05</f>
         <v>10.139999999999999</v>
       </c>
@@ -11000,74 +11033,74 @@
       <c r="R94" s="32"/>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B95" s="74"/>
-      <c r="C95" s="83" t="s">
+      <c r="B95" s="93"/>
+      <c r="C95" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D95" s="84">
+      <c r="D95" s="63">
         <v>0.05</v>
       </c>
-      <c r="E95" s="85"/>
-      <c r="F95" s="84">
+      <c r="E95" s="64"/>
+      <c r="F95" s="63">
         <f>F92-F94</f>
         <v>4.6000000000001151E-2</v>
       </c>
-      <c r="G95" s="84">
+      <c r="G95" s="63">
         <f>G92-G94</f>
         <v>2.8000000000000469E-2</v>
       </c>
-      <c r="H95" s="84">
+      <c r="H95" s="63">
         <f>H92-H94</f>
         <v>4.6000000000001151E-2</v>
       </c>
-      <c r="I95" s="85"/>
-      <c r="J95" s="85"/>
-      <c r="K95" s="85"/>
-      <c r="L95" s="84">
+      <c r="I95" s="64"/>
+      <c r="J95" s="64"/>
+      <c r="K95" s="64"/>
+      <c r="L95" s="63">
         <v>0.05</v>
       </c>
       <c r="Q95" s="32"/>
       <c r="R95" s="32"/>
     </row>
-    <row r="96" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B96" s="94"/>
-      <c r="C96" s="96"/>
-      <c r="D96" s="97"/>
-      <c r="E96" s="98"/>
-      <c r="F96" s="97"/>
-      <c r="G96" s="97"/>
-      <c r="H96" s="97"/>
-      <c r="I96" s="97"/>
-      <c r="J96" s="98"/>
-      <c r="K96" s="98"/>
-      <c r="L96" s="95"/>
-      <c r="Q96" s="93"/>
-      <c r="R96" s="93"/>
+    <row r="96" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B96" s="71"/>
+      <c r="C96" s="73"/>
+      <c r="D96" s="74"/>
+      <c r="E96" s="75"/>
+      <c r="F96" s="74"/>
+      <c r="G96" s="74"/>
+      <c r="H96" s="74"/>
+      <c r="I96" s="74"/>
+      <c r="J96" s="75"/>
+      <c r="K96" s="75"/>
+      <c r="L96" s="72"/>
+      <c r="Q96" s="32"/>
+      <c r="R96" s="32"/>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B97" s="75" t="s">
+      <c r="B97" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="C97" s="81" t="s">
+      <c r="C97" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D97" s="82">
+      <c r="D97" s="61">
         <v>10.236000000000001</v>
       </c>
-      <c r="E97" s="80"/>
-      <c r="F97" s="82">
+      <c r="E97" s="59"/>
+      <c r="F97" s="61">
         <v>10.255000000000001</v>
       </c>
-      <c r="G97" s="82">
+      <c r="G97" s="61">
         <v>10.298999999999999</v>
       </c>
-      <c r="H97" s="80">
+      <c r="H97" s="59">
         <v>10.260999999999999</v>
       </c>
-      <c r="I97" s="80"/>
-      <c r="J97" s="80"/>
-      <c r="K97" s="80"/>
-      <c r="L97" s="80">
+      <c r="I97" s="59"/>
+      <c r="J97" s="59"/>
+      <c r="K97" s="59"/>
+      <c r="L97" s="59">
         <v>10.234</v>
       </c>
       <c r="N97" s="38">
@@ -11084,60 +11117,60 @@
       </c>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B98" s="73"/>
-      <c r="C98" s="86" t="s">
+      <c r="B98" s="92"/>
+      <c r="C98" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D98" s="87">
+      <c r="D98" s="66">
         <v>10.236000000000001</v>
       </c>
-      <c r="E98" s="88"/>
-      <c r="F98" s="87">
+      <c r="E98" s="67"/>
+      <c r="F98" s="66">
         <f>G98-($F$1*Q97)</f>
         <v>10.263</v>
       </c>
-      <c r="G98" s="87">
+      <c r="G98" s="66">
         <v>10.307</v>
       </c>
-      <c r="H98" s="88">
+      <c r="H98" s="67">
         <f>G98-($H$1*R97)</f>
         <v>10.261000000000001</v>
       </c>
-      <c r="I98" s="88"/>
-      <c r="J98" s="88"/>
-      <c r="K98" s="88"/>
-      <c r="L98" s="88">
+      <c r="I98" s="67"/>
+      <c r="J98" s="67"/>
+      <c r="K98" s="67"/>
+      <c r="L98" s="67">
         <v>10.234</v>
       </c>
       <c r="Q98" s="32"/>
       <c r="R98" s="32"/>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B99" s="73"/>
-      <c r="C99" s="89" t="s">
+      <c r="B99" s="92"/>
+      <c r="C99" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D99" s="90">
+      <c r="D99" s="69">
         <f>D98-0.05</f>
         <v>10.186</v>
       </c>
-      <c r="E99" s="91"/>
-      <c r="F99" s="90">
+      <c r="E99" s="70"/>
+      <c r="F99" s="69">
         <f>F98-0.05</f>
         <v>10.212999999999999</v>
       </c>
-      <c r="G99" s="90">
+      <c r="G99" s="69">
         <f>G98-0.05</f>
         <v>10.257</v>
       </c>
-      <c r="H99" s="90">
+      <c r="H99" s="69">
         <f>H98-0.05</f>
         <v>10.211</v>
       </c>
-      <c r="I99" s="91"/>
-      <c r="J99" s="91"/>
-      <c r="K99" s="91"/>
-      <c r="L99" s="90">
+      <c r="I99" s="70"/>
+      <c r="J99" s="70"/>
+      <c r="K99" s="70"/>
+      <c r="L99" s="69">
         <f>L98-0.05</f>
         <v>10.183999999999999</v>
       </c>
@@ -11145,74 +11178,74 @@
       <c r="R99" s="32"/>
     </row>
     <row r="100" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B100" s="74"/>
-      <c r="C100" s="83" t="s">
+      <c r="B100" s="93"/>
+      <c r="C100" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D100" s="84">
+      <c r="D100" s="63">
         <v>0.05</v>
       </c>
-      <c r="E100" s="85"/>
-      <c r="F100" s="84">
+      <c r="E100" s="64"/>
+      <c r="F100" s="63">
         <f>F97-F99</f>
         <v>4.2000000000001592E-2</v>
       </c>
-      <c r="G100" s="84">
+      <c r="G100" s="63">
         <f>G97-G99</f>
         <v>4.1999999999999815E-2</v>
       </c>
-      <c r="H100" s="84">
+      <c r="H100" s="63">
         <f>H97-H99</f>
         <v>4.9999999999998934E-2</v>
       </c>
-      <c r="I100" s="85"/>
-      <c r="J100" s="85"/>
-      <c r="K100" s="85"/>
-      <c r="L100" s="84">
+      <c r="I100" s="64"/>
+      <c r="J100" s="64"/>
+      <c r="K100" s="64"/>
+      <c r="L100" s="63">
         <v>0.05</v>
       </c>
       <c r="Q100" s="32"/>
       <c r="R100" s="32"/>
     </row>
-    <row r="101" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B101" s="94"/>
-      <c r="C101" s="96"/>
-      <c r="D101" s="97"/>
-      <c r="E101" s="98"/>
-      <c r="F101" s="97"/>
-      <c r="G101" s="97"/>
-      <c r="H101" s="97"/>
-      <c r="I101" s="97"/>
-      <c r="J101" s="98"/>
-      <c r="K101" s="98"/>
-      <c r="L101" s="95"/>
-      <c r="Q101" s="93"/>
-      <c r="R101" s="93"/>
+    <row r="101" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B101" s="71"/>
+      <c r="C101" s="73"/>
+      <c r="D101" s="74"/>
+      <c r="E101" s="75"/>
+      <c r="F101" s="74"/>
+      <c r="G101" s="74"/>
+      <c r="H101" s="74"/>
+      <c r="I101" s="74"/>
+      <c r="J101" s="75"/>
+      <c r="K101" s="75"/>
+      <c r="L101" s="72"/>
+      <c r="Q101" s="32"/>
+      <c r="R101" s="32"/>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B102" s="75" t="s">
+      <c r="B102" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="C102" s="81" t="s">
+      <c r="C102" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D102" s="82">
+      <c r="D102" s="61">
         <v>10.359</v>
       </c>
-      <c r="E102" s="80"/>
-      <c r="F102" s="82">
+      <c r="E102" s="59"/>
+      <c r="F102" s="61">
         <v>10.368</v>
       </c>
-      <c r="G102" s="82">
+      <c r="G102" s="61">
         <v>10.364000000000001</v>
       </c>
-      <c r="H102" s="80">
+      <c r="H102" s="59">
         <v>10.384</v>
       </c>
-      <c r="I102" s="80"/>
-      <c r="J102" s="80"/>
-      <c r="K102" s="80"/>
-      <c r="L102" s="80">
+      <c r="I102" s="59"/>
+      <c r="J102" s="59"/>
+      <c r="K102" s="59"/>
+      <c r="L102" s="59">
         <v>10.398999999999999</v>
       </c>
       <c r="N102" s="38">
@@ -11229,60 +11262,60 @@
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B103" s="73"/>
-      <c r="C103" s="86" t="s">
+      <c r="B103" s="92"/>
+      <c r="C103" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D103" s="87">
+      <c r="D103" s="66">
         <v>10.359</v>
       </c>
-      <c r="E103" s="88"/>
-      <c r="F103" s="87">
+      <c r="E103" s="67"/>
+      <c r="F103" s="66">
         <f>G103-($F$1*Q102)</f>
         <v>10.360000000000001</v>
       </c>
-      <c r="G103" s="87">
+      <c r="G103" s="66">
         <v>10.364000000000001</v>
       </c>
-      <c r="H103" s="88">
+      <c r="H103" s="67">
         <f>G103-($H$1*R102)</f>
         <v>10.386000000000001</v>
       </c>
-      <c r="I103" s="88"/>
-      <c r="J103" s="88"/>
-      <c r="K103" s="88"/>
-      <c r="L103" s="88">
+      <c r="I103" s="67"/>
+      <c r="J103" s="67"/>
+      <c r="K103" s="67"/>
+      <c r="L103" s="67">
         <v>10.398999999999999</v>
       </c>
       <c r="Q103" s="32"/>
       <c r="R103" s="32"/>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B104" s="73"/>
-      <c r="C104" s="89" t="s">
+      <c r="B104" s="92"/>
+      <c r="C104" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D104" s="90">
+      <c r="D104" s="69">
         <f>D103-0.05</f>
         <v>10.308999999999999</v>
       </c>
-      <c r="E104" s="91"/>
-      <c r="F104" s="90">
+      <c r="E104" s="70"/>
+      <c r="F104" s="69">
         <f>F103-0.05</f>
         <v>10.31</v>
       </c>
-      <c r="G104" s="90">
+      <c r="G104" s="69">
         <f>G103-0.05</f>
         <v>10.314</v>
       </c>
-      <c r="H104" s="90">
+      <c r="H104" s="69">
         <f>H103-0.05</f>
         <v>10.336</v>
       </c>
-      <c r="I104" s="91"/>
-      <c r="J104" s="91"/>
-      <c r="K104" s="91"/>
-      <c r="L104" s="90">
+      <c r="I104" s="70"/>
+      <c r="J104" s="70"/>
+      <c r="K104" s="70"/>
+      <c r="L104" s="69">
         <f>L103-0.05</f>
         <v>10.348999999999998</v>
       </c>
@@ -11290,74 +11323,74 @@
       <c r="R104" s="32"/>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B105" s="74"/>
-      <c r="C105" s="83" t="s">
+      <c r="B105" s="93"/>
+      <c r="C105" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D105" s="84">
+      <c r="D105" s="63">
         <v>0.05</v>
       </c>
-      <c r="E105" s="85"/>
-      <c r="F105" s="84">
+      <c r="E105" s="64"/>
+      <c r="F105" s="63">
         <f>F102-F104</f>
         <v>5.7999999999999829E-2</v>
       </c>
-      <c r="G105" s="84">
+      <c r="G105" s="63">
         <f>G102-G104</f>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="H105" s="84">
+      <c r="H105" s="63">
         <f>H102-H104</f>
         <v>4.8000000000000043E-2</v>
       </c>
-      <c r="I105" s="85"/>
-      <c r="J105" s="85"/>
-      <c r="K105" s="85"/>
-      <c r="L105" s="84">
+      <c r="I105" s="64"/>
+      <c r="J105" s="64"/>
+      <c r="K105" s="64"/>
+      <c r="L105" s="63">
         <v>0.05</v>
       </c>
       <c r="Q105" s="32"/>
       <c r="R105" s="32"/>
     </row>
-    <row r="106" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B106" s="94"/>
-      <c r="C106" s="96"/>
-      <c r="D106" s="97"/>
-      <c r="E106" s="98"/>
-      <c r="F106" s="97"/>
-      <c r="G106" s="97"/>
-      <c r="H106" s="97"/>
-      <c r="I106" s="97"/>
-      <c r="J106" s="98"/>
-      <c r="K106" s="98"/>
-      <c r="L106" s="95"/>
-      <c r="Q106" s="93"/>
-      <c r="R106" s="93"/>
+    <row r="106" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B106" s="71"/>
+      <c r="C106" s="73"/>
+      <c r="D106" s="74"/>
+      <c r="E106" s="75"/>
+      <c r="F106" s="74"/>
+      <c r="G106" s="74"/>
+      <c r="H106" s="74"/>
+      <c r="I106" s="74"/>
+      <c r="J106" s="75"/>
+      <c r="K106" s="75"/>
+      <c r="L106" s="72"/>
+      <c r="Q106" s="32"/>
+      <c r="R106" s="32"/>
     </row>
     <row r="107" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B107" s="76" t="s">
+      <c r="B107" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="C107" s="81" t="s">
+      <c r="C107" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D107" s="82">
+      <c r="D107" s="61">
         <v>10.372</v>
       </c>
-      <c r="E107" s="80"/>
-      <c r="F107" s="82">
+      <c r="E107" s="59"/>
+      <c r="F107" s="61">
         <v>10.371</v>
       </c>
-      <c r="G107" s="82">
+      <c r="G107" s="61">
         <v>10.375999999999999</v>
       </c>
-      <c r="H107" s="80">
+      <c r="H107" s="59">
         <v>10.388</v>
       </c>
-      <c r="I107" s="80"/>
-      <c r="J107" s="80"/>
-      <c r="K107" s="80"/>
-      <c r="L107" s="80">
+      <c r="I107" s="59"/>
+      <c r="J107" s="59"/>
+      <c r="K107" s="59"/>
+      <c r="L107" s="59">
         <v>10.385999999999999</v>
       </c>
       <c r="N107" s="38">
@@ -11374,60 +11407,60 @@
       </c>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B108" s="77"/>
-      <c r="C108" s="86" t="s">
+      <c r="B108" s="95"/>
+      <c r="C108" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D108" s="87">
+      <c r="D108" s="66">
         <v>10.372</v>
       </c>
-      <c r="E108" s="88"/>
-      <c r="F108" s="87">
+      <c r="E108" s="67"/>
+      <c r="F108" s="66">
         <f>G108-($F$1*Q107)</f>
         <v>10.375</v>
       </c>
-      <c r="G108" s="87">
+      <c r="G108" s="66">
         <v>10.379</v>
       </c>
-      <c r="H108" s="88">
+      <c r="H108" s="67">
         <f>G108-($H$1*R107)</f>
         <v>10.382999999999999</v>
       </c>
-      <c r="I108" s="88"/>
-      <c r="J108" s="88"/>
-      <c r="K108" s="88"/>
-      <c r="L108" s="88">
+      <c r="I108" s="67"/>
+      <c r="J108" s="67"/>
+      <c r="K108" s="67"/>
+      <c r="L108" s="67">
         <v>10.385999999999999</v>
       </c>
       <c r="Q108" s="32"/>
       <c r="R108" s="32"/>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B109" s="77"/>
-      <c r="C109" s="89" t="s">
+      <c r="B109" s="95"/>
+      <c r="C109" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D109" s="90">
+      <c r="D109" s="69">
         <f>D108-0.05</f>
         <v>10.321999999999999</v>
       </c>
-      <c r="E109" s="91"/>
-      <c r="F109" s="90">
+      <c r="E109" s="70"/>
+      <c r="F109" s="69">
         <f>F108-0.05</f>
         <v>10.324999999999999</v>
       </c>
-      <c r="G109" s="90">
+      <c r="G109" s="69">
         <f>G108-0.05</f>
         <v>10.328999999999999</v>
       </c>
-      <c r="H109" s="90">
+      <c r="H109" s="69">
         <f>H108-0.05</f>
         <v>10.332999999999998</v>
       </c>
-      <c r="I109" s="91"/>
-      <c r="J109" s="91"/>
-      <c r="K109" s="91"/>
-      <c r="L109" s="90">
+      <c r="I109" s="70"/>
+      <c r="J109" s="70"/>
+      <c r="K109" s="70"/>
+      <c r="L109" s="69">
         <f>L108-0.05</f>
         <v>10.335999999999999</v>
       </c>
@@ -11435,74 +11468,74 @@
       <c r="R109" s="32"/>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B110" s="78"/>
-      <c r="C110" s="83" t="s">
+      <c r="B110" s="96"/>
+      <c r="C110" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D110" s="84">
+      <c r="D110" s="63">
         <v>0.05</v>
       </c>
-      <c r="E110" s="85"/>
-      <c r="F110" s="84">
+      <c r="E110" s="64"/>
+      <c r="F110" s="63">
         <f>F107-F109</f>
         <v>4.6000000000001151E-2</v>
       </c>
-      <c r="G110" s="84">
+      <c r="G110" s="63">
         <f>G107-G109</f>
         <v>4.7000000000000597E-2</v>
       </c>
-      <c r="H110" s="84">
+      <c r="H110" s="63">
         <f>H107-H109</f>
         <v>5.5000000000001492E-2</v>
       </c>
-      <c r="I110" s="85"/>
-      <c r="J110" s="85"/>
-      <c r="K110" s="85"/>
-      <c r="L110" s="84">
+      <c r="I110" s="64"/>
+      <c r="J110" s="64"/>
+      <c r="K110" s="64"/>
+      <c r="L110" s="63">
         <v>0.05</v>
       </c>
       <c r="Q110" s="32"/>
       <c r="R110" s="32"/>
     </row>
-    <row r="111" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B111" s="94"/>
-      <c r="C111" s="96"/>
-      <c r="D111" s="97"/>
-      <c r="E111" s="98"/>
-      <c r="F111" s="97"/>
-      <c r="G111" s="97"/>
-      <c r="H111" s="97"/>
-      <c r="I111" s="97"/>
-      <c r="J111" s="98"/>
-      <c r="K111" s="98"/>
-      <c r="L111" s="95"/>
-      <c r="Q111" s="93"/>
-      <c r="R111" s="93"/>
+    <row r="111" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B111" s="71"/>
+      <c r="C111" s="73"/>
+      <c r="D111" s="74"/>
+      <c r="E111" s="75"/>
+      <c r="F111" s="74"/>
+      <c r="G111" s="74"/>
+      <c r="H111" s="74"/>
+      <c r="I111" s="74"/>
+      <c r="J111" s="75"/>
+      <c r="K111" s="75"/>
+      <c r="L111" s="72"/>
+      <c r="Q111" s="32"/>
+      <c r="R111" s="32"/>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B112" s="75" t="s">
+      <c r="B112" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="C112" s="81" t="s">
+      <c r="C112" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D112" s="82">
+      <c r="D112" s="61">
         <v>10.365</v>
       </c>
-      <c r="E112" s="80"/>
-      <c r="F112" s="82">
+      <c r="E112" s="59"/>
+      <c r="F112" s="61">
         <v>10.384</v>
       </c>
-      <c r="G112" s="82">
+      <c r="G112" s="61">
         <v>10.414</v>
       </c>
-      <c r="H112" s="80">
+      <c r="H112" s="59">
         <v>10.366</v>
       </c>
-      <c r="I112" s="80"/>
-      <c r="J112" s="80"/>
-      <c r="K112" s="80"/>
-      <c r="L112" s="80">
+      <c r="I112" s="59"/>
+      <c r="J112" s="59"/>
+      <c r="K112" s="59"/>
+      <c r="L112" s="59">
         <v>10.348000000000001</v>
       </c>
       <c r="N112" s="38">
@@ -11519,60 +11552,60 @@
       </c>
     </row>
     <row r="113" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B113" s="73"/>
-      <c r="C113" s="86" t="s">
+      <c r="B113" s="92"/>
+      <c r="C113" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D113" s="87">
+      <c r="D113" s="66">
         <v>10.365</v>
       </c>
-      <c r="E113" s="88"/>
-      <c r="F113" s="87">
+      <c r="E113" s="67"/>
+      <c r="F113" s="66">
         <f>G113-($F$1*Q112)</f>
         <v>10.388</v>
       </c>
-      <c r="G113" s="87">
+      <c r="G113" s="66">
         <v>10.426</v>
       </c>
-      <c r="H113" s="88">
+      <c r="H113" s="67">
         <f>G113-($H$1*R112)</f>
         <v>10.378</v>
       </c>
-      <c r="I113" s="88"/>
-      <c r="J113" s="88"/>
-      <c r="K113" s="88"/>
-      <c r="L113" s="88">
+      <c r="I113" s="67"/>
+      <c r="J113" s="67"/>
+      <c r="K113" s="67"/>
+      <c r="L113" s="67">
         <v>10.348000000000001</v>
       </c>
       <c r="Q113" s="32"/>
       <c r="R113" s="32"/>
     </row>
     <row r="114" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B114" s="73"/>
-      <c r="C114" s="89" t="s">
+      <c r="B114" s="92"/>
+      <c r="C114" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D114" s="90">
+      <c r="D114" s="69">
         <f>D113-0.05</f>
         <v>10.315</v>
       </c>
-      <c r="E114" s="91"/>
-      <c r="F114" s="90">
+      <c r="E114" s="70"/>
+      <c r="F114" s="69">
         <f>F113-0.05</f>
         <v>10.337999999999999</v>
       </c>
-      <c r="G114" s="90">
+      <c r="G114" s="69">
         <f>G113-0.05</f>
         <v>10.375999999999999</v>
       </c>
-      <c r="H114" s="90">
+      <c r="H114" s="69">
         <f>H113-0.05</f>
         <v>10.327999999999999</v>
       </c>
-      <c r="I114" s="91"/>
-      <c r="J114" s="91"/>
-      <c r="K114" s="91"/>
-      <c r="L114" s="90">
+      <c r="I114" s="70"/>
+      <c r="J114" s="70"/>
+      <c r="K114" s="70"/>
+      <c r="L114" s="69">
         <f>L113-0.05</f>
         <v>10.298</v>
       </c>
@@ -11580,74 +11613,74 @@
       <c r="R114" s="32"/>
     </row>
     <row r="115" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B115" s="74"/>
-      <c r="C115" s="83" t="s">
+      <c r="B115" s="93"/>
+      <c r="C115" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D115" s="84">
+      <c r="D115" s="63">
         <v>0.05</v>
       </c>
-      <c r="E115" s="85"/>
-      <c r="F115" s="84">
+      <c r="E115" s="64"/>
+      <c r="F115" s="63">
         <f>F112-F114</f>
         <v>4.6000000000001151E-2</v>
       </c>
-      <c r="G115" s="84">
+      <c r="G115" s="63">
         <f>G112-G114</f>
         <v>3.8000000000000256E-2</v>
       </c>
-      <c r="H115" s="84">
+      <c r="H115" s="63">
         <f>H112-H114</f>
         <v>3.8000000000000256E-2</v>
       </c>
-      <c r="I115" s="85"/>
-      <c r="J115" s="85"/>
-      <c r="K115" s="85"/>
-      <c r="L115" s="84">
+      <c r="I115" s="64"/>
+      <c r="J115" s="64"/>
+      <c r="K115" s="64"/>
+      <c r="L115" s="63">
         <v>0.05</v>
       </c>
       <c r="Q115" s="32"/>
       <c r="R115" s="32"/>
     </row>
-    <row r="116" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B116" s="94"/>
-      <c r="C116" s="96"/>
-      <c r="D116" s="97"/>
-      <c r="E116" s="98"/>
-      <c r="F116" s="97"/>
-      <c r="G116" s="97"/>
-      <c r="H116" s="97"/>
-      <c r="I116" s="97"/>
-      <c r="J116" s="98"/>
-      <c r="K116" s="98"/>
-      <c r="L116" s="95"/>
-      <c r="Q116" s="93"/>
-      <c r="R116" s="93"/>
+    <row r="116" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B116" s="71"/>
+      <c r="C116" s="73"/>
+      <c r="D116" s="74"/>
+      <c r="E116" s="75"/>
+      <c r="F116" s="74"/>
+      <c r="G116" s="74"/>
+      <c r="H116" s="74"/>
+      <c r="I116" s="74"/>
+      <c r="J116" s="75"/>
+      <c r="K116" s="75"/>
+      <c r="L116" s="72"/>
+      <c r="Q116" s="32"/>
+      <c r="R116" s="32"/>
     </row>
     <row r="117" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B117" s="75" t="s">
+      <c r="B117" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="C117" s="81" t="s">
+      <c r="C117" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D117" s="82">
+      <c r="D117" s="61">
         <v>10.404</v>
       </c>
-      <c r="E117" s="80"/>
-      <c r="F117" s="82">
+      <c r="E117" s="59"/>
+      <c r="F117" s="61">
         <v>10.435</v>
       </c>
-      <c r="G117" s="82">
+      <c r="G117" s="61">
         <v>10.465</v>
       </c>
-      <c r="H117" s="80">
+      <c r="H117" s="59">
         <v>10.433</v>
       </c>
-      <c r="I117" s="80"/>
-      <c r="J117" s="80"/>
-      <c r="K117" s="80"/>
-      <c r="L117" s="80">
+      <c r="I117" s="59"/>
+      <c r="J117" s="59"/>
+      <c r="K117" s="59"/>
+      <c r="L117" s="59">
         <v>10.419</v>
       </c>
       <c r="N117" s="38">
@@ -11664,60 +11697,60 @@
       </c>
     </row>
     <row r="118" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B118" s="73"/>
-      <c r="C118" s="86" t="s">
+      <c r="B118" s="92"/>
+      <c r="C118" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D118" s="87">
+      <c r="D118" s="66">
         <v>10.404</v>
       </c>
-      <c r="E118" s="88"/>
-      <c r="F118" s="87">
+      <c r="E118" s="67"/>
+      <c r="F118" s="66">
         <f>G118-($F$1*Q117)</f>
         <v>10.436</v>
       </c>
-      <c r="G118" s="87">
+      <c r="G118" s="66">
         <v>10.488</v>
       </c>
-      <c r="H118" s="88">
+      <c r="H118" s="67">
         <f>G118-($H$1*R117)</f>
         <v>10.443999999999999</v>
       </c>
-      <c r="I118" s="88"/>
-      <c r="J118" s="88"/>
-      <c r="K118" s="88"/>
-      <c r="L118" s="88">
+      <c r="I118" s="67"/>
+      <c r="J118" s="67"/>
+      <c r="K118" s="67"/>
+      <c r="L118" s="67">
         <v>10.419</v>
       </c>
       <c r="Q118" s="32"/>
       <c r="R118" s="32"/>
     </row>
     <row r="119" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B119" s="73"/>
-      <c r="C119" s="89" t="s">
+      <c r="B119" s="92"/>
+      <c r="C119" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D119" s="90">
+      <c r="D119" s="69">
         <f>D118-0.05</f>
         <v>10.353999999999999</v>
       </c>
-      <c r="E119" s="91"/>
-      <c r="F119" s="90">
+      <c r="E119" s="70"/>
+      <c r="F119" s="69">
         <f>F118-0.05</f>
         <v>10.385999999999999</v>
       </c>
-      <c r="G119" s="90">
+      <c r="G119" s="69">
         <f>G118-0.05</f>
         <v>10.437999999999999</v>
       </c>
-      <c r="H119" s="90">
+      <c r="H119" s="69">
         <f>H118-0.05</f>
         <v>10.393999999999998</v>
       </c>
-      <c r="I119" s="91"/>
-      <c r="J119" s="91"/>
-      <c r="K119" s="91"/>
-      <c r="L119" s="90">
+      <c r="I119" s="70"/>
+      <c r="J119" s="70"/>
+      <c r="K119" s="70"/>
+      <c r="L119" s="69">
         <f>L118-0.05</f>
         <v>10.369</v>
       </c>
@@ -11725,74 +11758,74 @@
       <c r="R119" s="32"/>
     </row>
     <row r="120" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B120" s="74"/>
-      <c r="C120" s="83" t="s">
+      <c r="B120" s="93"/>
+      <c r="C120" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D120" s="84">
+      <c r="D120" s="63">
         <v>0.05</v>
       </c>
-      <c r="E120" s="85"/>
-      <c r="F120" s="84">
+      <c r="E120" s="64"/>
+      <c r="F120" s="63">
         <f>F117-F119</f>
         <v>4.9000000000001265E-2</v>
       </c>
-      <c r="G120" s="84">
+      <c r="G120" s="63">
         <f>G117-G119</f>
         <v>2.7000000000001023E-2</v>
       </c>
-      <c r="H120" s="84">
+      <c r="H120" s="63">
         <f>H117-H119</f>
         <v>3.9000000000001478E-2</v>
       </c>
-      <c r="I120" s="85"/>
-      <c r="J120" s="85"/>
-      <c r="K120" s="85"/>
-      <c r="L120" s="84">
+      <c r="I120" s="64"/>
+      <c r="J120" s="64"/>
+      <c r="K120" s="64"/>
+      <c r="L120" s="63">
         <v>0.05</v>
       </c>
       <c r="Q120" s="32"/>
       <c r="R120" s="32"/>
     </row>
-    <row r="121" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B121" s="94"/>
-      <c r="C121" s="96"/>
-      <c r="D121" s="97"/>
-      <c r="E121" s="98"/>
-      <c r="F121" s="97"/>
-      <c r="G121" s="97"/>
-      <c r="H121" s="97"/>
-      <c r="I121" s="97"/>
-      <c r="J121" s="98"/>
-      <c r="K121" s="98"/>
-      <c r="L121" s="95"/>
-      <c r="Q121" s="93"/>
-      <c r="R121" s="93"/>
+    <row r="121" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B121" s="71"/>
+      <c r="C121" s="73"/>
+      <c r="D121" s="74"/>
+      <c r="E121" s="75"/>
+      <c r="F121" s="74"/>
+      <c r="G121" s="74"/>
+      <c r="H121" s="74"/>
+      <c r="I121" s="74"/>
+      <c r="J121" s="75"/>
+      <c r="K121" s="75"/>
+      <c r="L121" s="72"/>
+      <c r="Q121" s="32"/>
+      <c r="R121" s="32"/>
     </row>
     <row r="122" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B122" s="75" t="s">
+      <c r="B122" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="C122" s="81" t="s">
+      <c r="C122" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D122" s="82">
+      <c r="D122" s="61">
         <v>10.478</v>
       </c>
-      <c r="E122" s="80"/>
-      <c r="F122" s="82">
+      <c r="E122" s="59"/>
+      <c r="F122" s="61">
         <v>10.507</v>
       </c>
-      <c r="G122" s="82">
+      <c r="G122" s="61">
         <v>10.544</v>
       </c>
-      <c r="H122" s="80">
+      <c r="H122" s="59">
         <v>10.510999999999999</v>
       </c>
-      <c r="I122" s="80"/>
-      <c r="J122" s="80"/>
-      <c r="K122" s="80"/>
-      <c r="L122" s="80">
+      <c r="I122" s="59"/>
+      <c r="J122" s="59"/>
+      <c r="K122" s="59"/>
+      <c r="L122" s="59">
         <v>10.481999999999999</v>
       </c>
       <c r="N122" s="38">
@@ -11809,60 +11842,60 @@
       </c>
     </row>
     <row r="123" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B123" s="73"/>
-      <c r="C123" s="86" t="s">
+      <c r="B123" s="92"/>
+      <c r="C123" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D123" s="87">
+      <c r="D123" s="66">
         <v>10.478</v>
       </c>
-      <c r="E123" s="88"/>
-      <c r="F123" s="87">
+      <c r="E123" s="67"/>
+      <c r="F123" s="66">
         <f>G123-($F$1*Q122)</f>
         <v>10.504000000000001</v>
       </c>
-      <c r="G123" s="87">
+      <c r="G123" s="66">
         <v>10.55</v>
       </c>
-      <c r="H123" s="88">
+      <c r="H123" s="67">
         <f>G123-($H$1*R122)</f>
         <v>10.508000000000001</v>
       </c>
-      <c r="I123" s="88"/>
-      <c r="J123" s="88"/>
-      <c r="K123" s="88"/>
-      <c r="L123" s="88">
+      <c r="I123" s="67"/>
+      <c r="J123" s="67"/>
+      <c r="K123" s="67"/>
+      <c r="L123" s="67">
         <v>10.481999999999999</v>
       </c>
       <c r="Q123" s="32"/>
       <c r="R123" s="32"/>
     </row>
     <row r="124" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B124" s="73"/>
-      <c r="C124" s="89" t="s">
+      <c r="B124" s="92"/>
+      <c r="C124" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D124" s="90">
+      <c r="D124" s="69">
         <f>D123-0.05</f>
         <v>10.427999999999999</v>
       </c>
-      <c r="E124" s="91"/>
-      <c r="F124" s="90">
+      <c r="E124" s="70"/>
+      <c r="F124" s="69">
         <f>F123-0.05</f>
         <v>10.454000000000001</v>
       </c>
-      <c r="G124" s="90">
+      <c r="G124" s="69">
         <f>G123-0.05</f>
         <v>10.5</v>
       </c>
-      <c r="H124" s="90">
+      <c r="H124" s="69">
         <f>H123-0.05</f>
         <v>10.458</v>
       </c>
-      <c r="I124" s="91"/>
-      <c r="J124" s="91"/>
-      <c r="K124" s="91"/>
-      <c r="L124" s="90">
+      <c r="I124" s="70"/>
+      <c r="J124" s="70"/>
+      <c r="K124" s="70"/>
+      <c r="L124" s="69">
         <f>L123-0.05</f>
         <v>10.431999999999999</v>
       </c>
@@ -11870,74 +11903,74 @@
       <c r="R124" s="32"/>
     </row>
     <row r="125" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B125" s="74"/>
-      <c r="C125" s="83" t="s">
+      <c r="B125" s="93"/>
+      <c r="C125" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D125" s="84">
+      <c r="D125" s="63">
         <v>0.05</v>
       </c>
-      <c r="E125" s="85"/>
-      <c r="F125" s="84">
+      <c r="E125" s="64"/>
+      <c r="F125" s="63">
         <f>F122-F124</f>
         <v>5.2999999999999048E-2</v>
       </c>
-      <c r="G125" s="84">
+      <c r="G125" s="63">
         <f>G122-G124</f>
         <v>4.4000000000000483E-2</v>
       </c>
-      <c r="H125" s="84">
+      <c r="H125" s="63">
         <f>H122-H124</f>
         <v>5.2999999999999048E-2</v>
       </c>
-      <c r="I125" s="85"/>
-      <c r="J125" s="85"/>
-      <c r="K125" s="85"/>
-      <c r="L125" s="84">
+      <c r="I125" s="64"/>
+      <c r="J125" s="64"/>
+      <c r="K125" s="64"/>
+      <c r="L125" s="63">
         <v>0.05</v>
       </c>
       <c r="Q125" s="32"/>
       <c r="R125" s="32"/>
     </row>
-    <row r="126" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B126" s="94"/>
-      <c r="C126" s="96"/>
-      <c r="D126" s="97"/>
-      <c r="E126" s="98"/>
-      <c r="F126" s="97"/>
-      <c r="G126" s="97"/>
-      <c r="H126" s="97"/>
-      <c r="I126" s="97"/>
-      <c r="J126" s="98"/>
-      <c r="K126" s="98"/>
-      <c r="L126" s="95"/>
-      <c r="Q126" s="93"/>
-      <c r="R126" s="93"/>
+    <row r="126" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B126" s="71"/>
+      <c r="C126" s="73"/>
+      <c r="D126" s="74"/>
+      <c r="E126" s="75"/>
+      <c r="F126" s="74"/>
+      <c r="G126" s="74"/>
+      <c r="H126" s="74"/>
+      <c r="I126" s="74"/>
+      <c r="J126" s="75"/>
+      <c r="K126" s="75"/>
+      <c r="L126" s="72"/>
+      <c r="Q126" s="32"/>
+      <c r="R126" s="32"/>
     </row>
     <row r="127" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B127" s="76" t="s">
+      <c r="B127" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="C127" s="81" t="s">
+      <c r="C127" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D127" s="82">
+      <c r="D127" s="61">
         <v>10.510999999999999</v>
       </c>
-      <c r="E127" s="80"/>
-      <c r="F127" s="82">
+      <c r="E127" s="59"/>
+      <c r="F127" s="61">
         <v>10.54</v>
       </c>
-      <c r="G127" s="82">
+      <c r="G127" s="61">
         <v>10.589</v>
       </c>
-      <c r="H127" s="80">
+      <c r="H127" s="59">
         <v>10.534000000000001</v>
       </c>
-      <c r="I127" s="80"/>
-      <c r="J127" s="80"/>
-      <c r="K127" s="80"/>
-      <c r="L127" s="80">
+      <c r="I127" s="59"/>
+      <c r="J127" s="59"/>
+      <c r="K127" s="59"/>
+      <c r="L127" s="59">
         <v>10.510999999999999</v>
       </c>
       <c r="N127" s="38">
@@ -11954,60 +11987,60 @@
       </c>
     </row>
     <row r="128" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B128" s="77"/>
-      <c r="C128" s="86" t="s">
+      <c r="B128" s="95"/>
+      <c r="C128" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D128" s="87">
+      <c r="D128" s="66">
         <v>10.510999999999999</v>
       </c>
-      <c r="E128" s="88"/>
-      <c r="F128" s="87">
+      <c r="E128" s="67"/>
+      <c r="F128" s="66">
         <f>G128-($F$1*Q127)</f>
         <v>10.536</v>
       </c>
-      <c r="G128" s="87">
+      <c r="G128" s="66">
         <v>10.58</v>
       </c>
-      <c r="H128" s="88">
+      <c r="H128" s="67">
         <f>G128-($H$1*R127)</f>
         <v>10.536</v>
       </c>
-      <c r="I128" s="88"/>
-      <c r="J128" s="88"/>
-      <c r="K128" s="88"/>
-      <c r="L128" s="88">
+      <c r="I128" s="67"/>
+      <c r="J128" s="67"/>
+      <c r="K128" s="67"/>
+      <c r="L128" s="67">
         <v>10.510999999999999</v>
       </c>
       <c r="Q128" s="32"/>
       <c r="R128" s="32"/>
     </row>
     <row r="129" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B129" s="77"/>
-      <c r="C129" s="89" t="s">
+      <c r="B129" s="95"/>
+      <c r="C129" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D129" s="90">
+      <c r="D129" s="69">
         <f>D128-0.05</f>
         <v>10.460999999999999</v>
       </c>
-      <c r="E129" s="91"/>
-      <c r="F129" s="90">
+      <c r="E129" s="70"/>
+      <c r="F129" s="69">
         <f>F128-0.05</f>
         <v>10.485999999999999</v>
       </c>
-      <c r="G129" s="90">
+      <c r="G129" s="69">
         <f>G128-0.05</f>
         <v>10.53</v>
       </c>
-      <c r="H129" s="90">
+      <c r="H129" s="69">
         <f>H128-0.05</f>
         <v>10.485999999999999</v>
       </c>
-      <c r="I129" s="91"/>
-      <c r="J129" s="91"/>
-      <c r="K129" s="91"/>
-      <c r="L129" s="90">
+      <c r="I129" s="70"/>
+      <c r="J129" s="70"/>
+      <c r="K129" s="70"/>
+      <c r="L129" s="69">
         <f>L128-0.05</f>
         <v>10.460999999999999</v>
       </c>
@@ -12015,74 +12048,74 @@
       <c r="R129" s="32"/>
     </row>
     <row r="130" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B130" s="78"/>
-      <c r="C130" s="83" t="s">
+      <c r="B130" s="96"/>
+      <c r="C130" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D130" s="84">
+      <c r="D130" s="63">
         <v>0.05</v>
       </c>
-      <c r="E130" s="85"/>
-      <c r="F130" s="84">
+      <c r="E130" s="64"/>
+      <c r="F130" s="63">
         <f>F127-F129</f>
         <v>5.400000000000027E-2</v>
       </c>
-      <c r="G130" s="84">
+      <c r="G130" s="63">
         <f>G127-G129</f>
         <v>5.9000000000001052E-2</v>
       </c>
-      <c r="H130" s="84">
+      <c r="H130" s="63">
         <f>H127-H129</f>
         <v>4.8000000000001819E-2</v>
       </c>
-      <c r="I130" s="85"/>
-      <c r="J130" s="85"/>
-      <c r="K130" s="85"/>
-      <c r="L130" s="84">
+      <c r="I130" s="64"/>
+      <c r="J130" s="64"/>
+      <c r="K130" s="64"/>
+      <c r="L130" s="63">
         <v>0.05</v>
       </c>
       <c r="Q130" s="32"/>
       <c r="R130" s="32"/>
     </row>
-    <row r="131" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B131" s="94"/>
-      <c r="C131" s="96"/>
-      <c r="D131" s="97"/>
-      <c r="E131" s="98"/>
-      <c r="F131" s="97"/>
-      <c r="G131" s="97"/>
-      <c r="H131" s="97"/>
-      <c r="I131" s="97"/>
-      <c r="J131" s="98"/>
-      <c r="K131" s="98"/>
-      <c r="L131" s="95"/>
-      <c r="Q131" s="93"/>
-      <c r="R131" s="93"/>
+    <row r="131" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B131" s="71"/>
+      <c r="C131" s="73"/>
+      <c r="D131" s="74"/>
+      <c r="E131" s="75"/>
+      <c r="F131" s="74"/>
+      <c r="G131" s="74"/>
+      <c r="H131" s="74"/>
+      <c r="I131" s="74"/>
+      <c r="J131" s="75"/>
+      <c r="K131" s="75"/>
+      <c r="L131" s="72"/>
+      <c r="Q131" s="32"/>
+      <c r="R131" s="32"/>
     </row>
     <row r="132" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B132" s="75" t="s">
+      <c r="B132" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="C132" s="81" t="s">
+      <c r="C132" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D132" s="82">
+      <c r="D132" s="61">
         <v>10.548999999999999</v>
       </c>
-      <c r="E132" s="80"/>
-      <c r="F132" s="82">
+      <c r="E132" s="59"/>
+      <c r="F132" s="61">
         <v>10.569000000000001</v>
       </c>
-      <c r="G132" s="82">
+      <c r="G132" s="61">
         <v>10.598000000000001</v>
       </c>
-      <c r="H132" s="80">
+      <c r="H132" s="59">
         <v>10.567</v>
       </c>
-      <c r="I132" s="80"/>
-      <c r="J132" s="80"/>
-      <c r="K132" s="80"/>
-      <c r="L132" s="80">
+      <c r="I132" s="59"/>
+      <c r="J132" s="59"/>
+      <c r="K132" s="59"/>
+      <c r="L132" s="59">
         <v>10.547000000000001</v>
       </c>
       <c r="N132" s="38">
@@ -12099,60 +12132,60 @@
       </c>
     </row>
     <row r="133" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B133" s="73"/>
-      <c r="C133" s="86" t="s">
+      <c r="B133" s="92"/>
+      <c r="C133" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D133" s="87">
+      <c r="D133" s="66">
         <v>10.548999999999999</v>
       </c>
-      <c r="E133" s="88"/>
-      <c r="F133" s="87">
+      <c r="E133" s="67"/>
+      <c r="F133" s="66">
         <f>G133-($F$1*Q132)</f>
         <v>10.572000000000001</v>
       </c>
-      <c r="G133" s="87">
+      <c r="G133" s="66">
         <v>10.612</v>
       </c>
-      <c r="H133" s="88">
+      <c r="H133" s="67">
         <f>G133-($H$1*R132)</f>
         <v>10.572000000000001</v>
       </c>
-      <c r="I133" s="88"/>
-      <c r="J133" s="88"/>
-      <c r="K133" s="88"/>
-      <c r="L133" s="88">
+      <c r="I133" s="67"/>
+      <c r="J133" s="67"/>
+      <c r="K133" s="67"/>
+      <c r="L133" s="67">
         <v>10.547000000000001</v>
       </c>
       <c r="Q133" s="32"/>
       <c r="R133" s="32"/>
     </row>
     <row r="134" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B134" s="73"/>
-      <c r="C134" s="89" t="s">
+      <c r="B134" s="92"/>
+      <c r="C134" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D134" s="90">
+      <c r="D134" s="69">
         <f>D133-0.05</f>
         <v>10.498999999999999</v>
       </c>
-      <c r="E134" s="91"/>
-      <c r="F134" s="90">
+      <c r="E134" s="70"/>
+      <c r="F134" s="69">
         <f>F133-0.05</f>
         <v>10.522</v>
       </c>
-      <c r="G134" s="90">
+      <c r="G134" s="69">
         <f>G133-0.05</f>
         <v>10.561999999999999</v>
       </c>
-      <c r="H134" s="90">
+      <c r="H134" s="69">
         <f>H133-0.05</f>
         <v>10.522</v>
       </c>
-      <c r="I134" s="91"/>
-      <c r="J134" s="91"/>
-      <c r="K134" s="91"/>
-      <c r="L134" s="90">
+      <c r="I134" s="70"/>
+      <c r="J134" s="70"/>
+      <c r="K134" s="70"/>
+      <c r="L134" s="69">
         <f>L133-0.05</f>
         <v>10.497</v>
       </c>
@@ -12160,74 +12193,74 @@
       <c r="R134" s="32"/>
     </row>
     <row r="135" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B135" s="74"/>
-      <c r="C135" s="83" t="s">
+      <c r="B135" s="93"/>
+      <c r="C135" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D135" s="84">
+      <c r="D135" s="63">
         <v>0.05</v>
       </c>
-      <c r="E135" s="85"/>
-      <c r="F135" s="84">
+      <c r="E135" s="64"/>
+      <c r="F135" s="63">
         <f>F132-F134</f>
         <v>4.7000000000000597E-2</v>
       </c>
-      <c r="G135" s="84">
+      <c r="G135" s="63">
         <f>G132-G134</f>
         <v>3.6000000000001364E-2</v>
       </c>
-      <c r="H135" s="84">
+      <c r="H135" s="63">
         <f>H132-H134</f>
         <v>4.4999999999999929E-2</v>
       </c>
-      <c r="I135" s="85"/>
-      <c r="J135" s="85"/>
-      <c r="K135" s="85"/>
-      <c r="L135" s="84">
+      <c r="I135" s="64"/>
+      <c r="J135" s="64"/>
+      <c r="K135" s="64"/>
+      <c r="L135" s="63">
         <v>0.05</v>
       </c>
       <c r="Q135" s="32"/>
       <c r="R135" s="32"/>
     </row>
-    <row r="136" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B136" s="94"/>
-      <c r="C136" s="96"/>
-      <c r="D136" s="97"/>
-      <c r="E136" s="98"/>
-      <c r="F136" s="97"/>
-      <c r="G136" s="97"/>
-      <c r="H136" s="97"/>
-      <c r="I136" s="97"/>
-      <c r="J136" s="98"/>
-      <c r="K136" s="98"/>
-      <c r="L136" s="95"/>
-      <c r="Q136" s="93"/>
-      <c r="R136" s="93"/>
+    <row r="136" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B136" s="71"/>
+      <c r="C136" s="73"/>
+      <c r="D136" s="74"/>
+      <c r="E136" s="75"/>
+      <c r="F136" s="74"/>
+      <c r="G136" s="74"/>
+      <c r="H136" s="74"/>
+      <c r="I136" s="74"/>
+      <c r="J136" s="75"/>
+      <c r="K136" s="75"/>
+      <c r="L136" s="72"/>
+      <c r="Q136" s="32"/>
+      <c r="R136" s="32"/>
     </row>
     <row r="137" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B137" s="75" t="s">
+      <c r="B137" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="C137" s="81" t="s">
+      <c r="C137" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D137" s="82">
+      <c r="D137" s="61">
         <v>10.606999999999999</v>
       </c>
-      <c r="E137" s="80"/>
-      <c r="F137" s="82">
+      <c r="E137" s="59"/>
+      <c r="F137" s="61">
         <v>10.629</v>
       </c>
-      <c r="G137" s="82">
+      <c r="G137" s="61">
         <v>10.669</v>
       </c>
-      <c r="H137" s="80">
+      <c r="H137" s="59">
         <v>10.625999999999999</v>
       </c>
-      <c r="I137" s="80"/>
-      <c r="J137" s="80"/>
-      <c r="K137" s="80"/>
-      <c r="L137" s="80">
+      <c r="I137" s="59"/>
+      <c r="J137" s="59"/>
+      <c r="K137" s="59"/>
+      <c r="L137" s="59">
         <v>10.619</v>
       </c>
       <c r="N137" s="38">
@@ -12244,60 +12277,60 @@
       </c>
     </row>
     <row r="138" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B138" s="73"/>
-      <c r="C138" s="86" t="s">
+      <c r="B138" s="92"/>
+      <c r="C138" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D138" s="87">
+      <c r="D138" s="66">
         <v>10.606999999999999</v>
       </c>
-      <c r="E138" s="88"/>
-      <c r="F138" s="87">
+      <c r="E138" s="67"/>
+      <c r="F138" s="66">
         <f>G138-($F$1*Q137)</f>
         <v>10.632</v>
       </c>
-      <c r="G138" s="87">
+      <c r="G138" s="66">
         <v>10.673999999999999</v>
       </c>
-      <c r="H138" s="87">
+      <c r="H138" s="66">
         <f>G138-($H$1*R137)</f>
         <v>10.639999999999999</v>
       </c>
-      <c r="I138" s="88"/>
-      <c r="J138" s="88"/>
-      <c r="K138" s="88"/>
-      <c r="L138" s="88">
+      <c r="I138" s="67"/>
+      <c r="J138" s="67"/>
+      <c r="K138" s="67"/>
+      <c r="L138" s="67">
         <v>10.619</v>
       </c>
       <c r="Q138" s="32"/>
       <c r="R138" s="32"/>
     </row>
     <row r="139" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B139" s="73"/>
-      <c r="C139" s="89" t="s">
+      <c r="B139" s="92"/>
+      <c r="C139" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D139" s="90">
+      <c r="D139" s="69">
         <f>D138-0.05</f>
         <v>10.556999999999999</v>
       </c>
-      <c r="E139" s="91"/>
-      <c r="F139" s="90">
+      <c r="E139" s="70"/>
+      <c r="F139" s="69">
         <f>F138-0.05</f>
         <v>10.581999999999999</v>
       </c>
-      <c r="G139" s="90">
+      <c r="G139" s="69">
         <f>G138-0.05</f>
         <v>10.623999999999999</v>
       </c>
-      <c r="H139" s="90">
+      <c r="H139" s="69">
         <f>H138-0.05</f>
         <v>10.589999999999998</v>
       </c>
-      <c r="I139" s="91"/>
-      <c r="J139" s="91"/>
-      <c r="K139" s="91"/>
-      <c r="L139" s="90">
+      <c r="I139" s="70"/>
+      <c r="J139" s="70"/>
+      <c r="K139" s="70"/>
+      <c r="L139" s="69">
         <f>L138-0.05</f>
         <v>10.568999999999999</v>
       </c>
@@ -12305,74 +12338,74 @@
       <c r="R139" s="32"/>
     </row>
     <row r="140" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B140" s="74"/>
-      <c r="C140" s="83" t="s">
+      <c r="B140" s="93"/>
+      <c r="C140" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D140" s="84">
+      <c r="D140" s="63">
         <v>0.05</v>
       </c>
-      <c r="E140" s="85"/>
-      <c r="F140" s="84">
+      <c r="E140" s="64"/>
+      <c r="F140" s="63">
         <f>F137-F139</f>
         <v>4.7000000000000597E-2</v>
       </c>
-      <c r="G140" s="84">
+      <c r="G140" s="63">
         <f>G137-G139</f>
         <v>4.5000000000001705E-2</v>
       </c>
-      <c r="H140" s="84">
+      <c r="H140" s="63">
         <f>H137-H139</f>
         <v>3.6000000000001364E-2</v>
       </c>
-      <c r="I140" s="85"/>
-      <c r="J140" s="85"/>
-      <c r="K140" s="85"/>
-      <c r="L140" s="84">
+      <c r="I140" s="64"/>
+      <c r="J140" s="64"/>
+      <c r="K140" s="64"/>
+      <c r="L140" s="63">
         <v>0.05</v>
       </c>
       <c r="Q140" s="32"/>
       <c r="R140" s="32"/>
     </row>
-    <row r="141" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B141" s="94"/>
-      <c r="C141" s="96"/>
-      <c r="D141" s="97"/>
-      <c r="E141" s="98"/>
-      <c r="F141" s="97"/>
-      <c r="G141" s="97"/>
-      <c r="H141" s="97"/>
-      <c r="I141" s="97"/>
-      <c r="J141" s="98"/>
-      <c r="K141" s="98"/>
-      <c r="L141" s="95"/>
-      <c r="Q141" s="93"/>
-      <c r="R141" s="93"/>
+    <row r="141" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B141" s="71"/>
+      <c r="C141" s="73"/>
+      <c r="D141" s="74"/>
+      <c r="E141" s="75"/>
+      <c r="F141" s="74"/>
+      <c r="G141" s="74"/>
+      <c r="H141" s="74"/>
+      <c r="I141" s="74"/>
+      <c r="J141" s="75"/>
+      <c r="K141" s="75"/>
+      <c r="L141" s="72"/>
+      <c r="Q141" s="32"/>
+      <c r="R141" s="32"/>
     </row>
     <row r="142" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B142" s="75" t="s">
+      <c r="B142" s="91" t="s">
         <v>39</v>
       </c>
-      <c r="C142" s="81" t="s">
+      <c r="C142" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D142" s="82">
+      <c r="D142" s="61">
         <v>10.629</v>
       </c>
-      <c r="E142" s="80"/>
-      <c r="F142" s="82">
+      <c r="E142" s="59"/>
+      <c r="F142" s="61">
         <v>10.648</v>
       </c>
-      <c r="G142" s="82">
+      <c r="G142" s="61">
         <v>10.686</v>
       </c>
-      <c r="H142" s="80">
+      <c r="H142" s="59">
         <v>10.656000000000001</v>
       </c>
-      <c r="I142" s="80"/>
-      <c r="J142" s="80"/>
-      <c r="K142" s="80"/>
-      <c r="L142" s="80">
+      <c r="I142" s="59"/>
+      <c r="J142" s="59"/>
+      <c r="K142" s="59"/>
+      <c r="L142" s="59">
         <v>10.638999999999999</v>
       </c>
       <c r="N142" s="38">
@@ -12389,322 +12422,1146 @@
       </c>
     </row>
     <row r="143" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B143" s="73"/>
-      <c r="C143" s="86" t="s">
+      <c r="B143" s="92"/>
+      <c r="C143" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D143" s="87">
+      <c r="D143" s="66">
         <v>10.629</v>
       </c>
-      <c r="E143" s="88"/>
-      <c r="F143" s="87">
+      <c r="E143" s="67"/>
+      <c r="F143" s="66">
         <f>G143-($F$1*Q142)</f>
         <v>10.65</v>
       </c>
-      <c r="G143" s="87">
+      <c r="G143" s="66">
         <v>10.686</v>
       </c>
-      <c r="H143" s="88">
+      <c r="H143" s="67">
         <f>G143-($H$1*R142)</f>
         <v>10.656000000000001</v>
       </c>
-      <c r="I143" s="88"/>
-      <c r="J143" s="88"/>
-      <c r="K143" s="88"/>
-      <c r="L143" s="88">
+      <c r="I143" s="67"/>
+      <c r="J143" s="67"/>
+      <c r="K143" s="67"/>
+      <c r="L143" s="67">
         <v>10.638999999999999</v>
       </c>
     </row>
     <row r="144" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B144" s="73"/>
-      <c r="C144" s="89" t="s">
+      <c r="B144" s="92"/>
+      <c r="C144" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D144" s="90">
+      <c r="D144" s="69">
         <f>D143-0.05</f>
         <v>10.578999999999999</v>
       </c>
-      <c r="E144" s="91"/>
-      <c r="F144" s="90">
+      <c r="E144" s="70"/>
+      <c r="F144" s="69">
         <f>F143-0.05</f>
         <v>10.6</v>
       </c>
-      <c r="G144" s="90">
+      <c r="G144" s="69">
         <f>G143-0.05</f>
         <v>10.635999999999999</v>
       </c>
-      <c r="H144" s="90">
+      <c r="H144" s="69">
         <f>H143-0.05</f>
         <v>10.606</v>
       </c>
-      <c r="I144" s="91"/>
-      <c r="J144" s="91"/>
-      <c r="K144" s="91"/>
-      <c r="L144" s="90">
+      <c r="I144" s="70"/>
+      <c r="J144" s="70"/>
+      <c r="K144" s="70"/>
+      <c r="L144" s="69">
         <f>L143-0.05</f>
         <v>10.588999999999999</v>
       </c>
     </row>
     <row r="145" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B145" s="74"/>
-      <c r="C145" s="83" t="s">
+      <c r="B145" s="93"/>
+      <c r="C145" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D145" s="84">
+      <c r="D145" s="63">
         <v>0.05</v>
       </c>
-      <c r="E145" s="85"/>
-      <c r="F145" s="84">
+      <c r="E145" s="64"/>
+      <c r="F145" s="63">
         <f>F142-F144</f>
         <v>4.8000000000000043E-2</v>
       </c>
-      <c r="G145" s="84">
+      <c r="G145" s="63">
         <f>G142-G144</f>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="H145" s="84">
+      <c r="H145" s="63">
         <f>H142-H144</f>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="I145" s="85"/>
-      <c r="J145" s="85"/>
-      <c r="K145" s="85"/>
-      <c r="L145" s="84">
+      <c r="I145" s="64"/>
+      <c r="J145" s="64"/>
+      <c r="K145" s="64"/>
+      <c r="L145" s="63">
         <v>0.05</v>
       </c>
     </row>
-    <row r="146" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B146" s="94"/>
-      <c r="C146" s="96"/>
-      <c r="D146" s="97"/>
-      <c r="E146" s="98"/>
-      <c r="F146" s="97"/>
-      <c r="G146" s="97"/>
-      <c r="H146" s="97"/>
-      <c r="I146" s="97"/>
-      <c r="J146" s="98"/>
-      <c r="K146" s="98"/>
-      <c r="L146" s="95"/>
-      <c r="Q146" s="93"/>
-      <c r="R146" s="93"/>
+    <row r="146" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B146" s="71"/>
+      <c r="C146" s="73"/>
+      <c r="D146" s="74"/>
+      <c r="E146" s="75"/>
+      <c r="F146" s="74"/>
+      <c r="G146" s="74"/>
+      <c r="H146" s="74"/>
+      <c r="I146" s="74"/>
+      <c r="J146" s="75"/>
+      <c r="K146" s="75"/>
+      <c r="L146" s="72"/>
+      <c r="Q146" s="32"/>
+      <c r="R146" s="32"/>
     </row>
     <row r="147" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B147" s="75" t="s">
+      <c r="B147" s="91" t="s">
         <v>24</v>
       </c>
-      <c r="C147" s="81" t="s">
+      <c r="C147" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D147" s="82">
+      <c r="D147" s="61">
         <v>10.673999999999999</v>
       </c>
-      <c r="E147" s="80"/>
-      <c r="F147" s="82">
+      <c r="E147" s="59"/>
+      <c r="F147" s="61">
         <v>10.704000000000001</v>
       </c>
-      <c r="G147" s="82">
+      <c r="G147" s="61">
         <v>10.734999999999999</v>
       </c>
-      <c r="H147" s="80">
+      <c r="H147" s="59">
         <v>10.721</v>
       </c>
-      <c r="I147" s="80">
+      <c r="I147" s="59">
         <v>10.683999999999999</v>
       </c>
-      <c r="J147" s="80">
+      <c r="J147" s="59">
         <v>10.667999999999999</v>
       </c>
-      <c r="K147" s="80"/>
-      <c r="L147" s="80">
+      <c r="K147" s="59"/>
+      <c r="L147" s="59">
         <v>10.643000000000001</v>
       </c>
+      <c r="N147" s="97">
+        <v>3.1</v>
+      </c>
+      <c r="O147" s="97">
+        <v>8.6</v>
+      </c>
+      <c r="Q147" s="32">
+        <v>0.02</v>
+      </c>
+      <c r="R147" s="1">
+        <v>1.0999999999999999E-2</v>
+      </c>
     </row>
     <row r="148" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B148" s="73"/>
-      <c r="C148" s="86" t="s">
+      <c r="B148" s="92"/>
+      <c r="C148" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D148" s="87">
+      <c r="D148" s="66">
         <v>10.673999999999999</v>
       </c>
-      <c r="E148" s="88"/>
-      <c r="F148" s="87"/>
-      <c r="G148" s="87">
+      <c r="E148" s="67"/>
+      <c r="F148" s="66">
+        <f>G148-($F$1*Q147)</f>
+        <v>10.695</v>
+      </c>
+      <c r="G148" s="66">
         <v>10.734999999999999</v>
       </c>
-      <c r="H148" s="88"/>
-      <c r="I148" s="88"/>
-      <c r="J148" s="88"/>
-      <c r="K148" s="88"/>
-      <c r="L148" s="88">
+      <c r="H148" s="67">
+        <f>G148-($H$1*R147)</f>
+        <v>10.712999999999999</v>
+      </c>
+      <c r="I148" s="67">
+        <f>G148-($I$1*R147)</f>
+        <v>10.690999999999999</v>
+      </c>
+      <c r="J148" s="67">
+        <f>G148-($J$1*R147)</f>
+        <v>10.668999999999999</v>
+      </c>
+      <c r="K148" s="67"/>
+      <c r="L148" s="67">
         <v>10.643000000000001</v>
       </c>
     </row>
     <row r="149" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B149" s="73"/>
-      <c r="C149" s="89" t="s">
+      <c r="B149" s="92"/>
+      <c r="C149" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D149" s="90">
+      <c r="D149" s="69">
         <f>D148-0.05</f>
         <v>10.623999999999999</v>
       </c>
-      <c r="E149" s="91"/>
-      <c r="F149" s="90"/>
-      <c r="G149" s="90">
+      <c r="E149" s="70"/>
+      <c r="F149" s="69">
+        <f>F148-0.05</f>
+        <v>10.645</v>
+      </c>
+      <c r="G149" s="69">
         <f>G148-0.05</f>
         <v>10.684999999999999</v>
       </c>
-      <c r="H149" s="91"/>
-      <c r="I149" s="91"/>
-      <c r="J149" s="91"/>
-      <c r="K149" s="91"/>
-      <c r="L149" s="90">
+      <c r="H149" s="69">
+        <f>H148-0.05</f>
+        <v>10.662999999999998</v>
+      </c>
+      <c r="I149" s="69">
+        <f>I148-0.05</f>
+        <v>10.640999999999998</v>
+      </c>
+      <c r="J149" s="69">
+        <f>J148-0.05</f>
+        <v>10.618999999999998</v>
+      </c>
+      <c r="K149" s="70"/>
+      <c r="L149" s="69">
         <f>L148-0.05</f>
         <v>10.593</v>
       </c>
     </row>
     <row r="150" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B150" s="74"/>
-      <c r="C150" s="83" t="s">
+      <c r="B150" s="93"/>
+      <c r="C150" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D150" s="84">
+      <c r="D150" s="63">
         <v>0.05</v>
       </c>
-      <c r="E150" s="85"/>
-      <c r="F150" s="84"/>
-      <c r="G150" s="84">
+      <c r="E150" s="64"/>
+      <c r="F150" s="63">
+        <f>F147-F149</f>
+        <v>5.9000000000001052E-2</v>
+      </c>
+      <c r="G150" s="63">
         <f>G147-G149</f>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="H150" s="85"/>
-      <c r="I150" s="85"/>
-      <c r="J150" s="85"/>
-      <c r="K150" s="85"/>
-      <c r="L150" s="84">
+      <c r="H150" s="63">
+        <f>H147-H149</f>
+        <v>5.8000000000001606E-2</v>
+      </c>
+      <c r="I150" s="63">
+        <f>I147-I149</f>
+        <v>4.3000000000001037E-2</v>
+      </c>
+      <c r="J150" s="63">
+        <f>J147-J149</f>
+        <v>4.9000000000001265E-2</v>
+      </c>
+      <c r="K150" s="64"/>
+      <c r="L150" s="63">
         <v>0.05</v>
       </c>
     </row>
-    <row r="151" spans="2:18" s="92" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B151" s="94"/>
-      <c r="C151" s="96"/>
-      <c r="D151" s="97"/>
-      <c r="E151" s="98"/>
-      <c r="F151" s="97"/>
-      <c r="G151" s="97"/>
-      <c r="H151" s="97"/>
-      <c r="I151" s="97"/>
-      <c r="J151" s="98"/>
-      <c r="K151" s="98"/>
-      <c r="L151" s="95"/>
-      <c r="Q151" s="93"/>
-      <c r="R151" s="93"/>
+    <row r="151" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B151" s="71"/>
+      <c r="C151" s="73"/>
+      <c r="D151" s="74"/>
+      <c r="E151" s="75"/>
+      <c r="F151" s="74"/>
+      <c r="G151" s="74"/>
+      <c r="H151" s="74"/>
+      <c r="I151" s="74"/>
+      <c r="J151" s="75"/>
+      <c r="K151" s="75"/>
+      <c r="L151" s="72"/>
+      <c r="N151" s="98"/>
+      <c r="O151" s="98"/>
+      <c r="Q151" s="32"/>
+      <c r="R151" s="32"/>
     </row>
     <row r="152" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B152" s="75" t="s">
+      <c r="B152" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="C152" s="81" t="s">
+      <c r="C152" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D152" s="82">
+      <c r="D152" s="61">
         <v>10.631</v>
       </c>
-      <c r="E152" s="80">
+      <c r="E152" s="59">
         <v>10.654999999999999</v>
       </c>
-      <c r="F152" s="82">
+      <c r="F152" s="61">
         <v>10.676</v>
       </c>
-      <c r="G152" s="82">
+      <c r="G152" s="61">
         <v>10.693</v>
       </c>
-      <c r="H152" s="80">
+      <c r="H152" s="59">
         <v>10.682</v>
       </c>
-      <c r="I152" s="80">
+      <c r="I152" s="59">
         <v>10.683999999999999</v>
       </c>
-      <c r="J152" s="80">
+      <c r="J152" s="59">
         <v>10.683</v>
       </c>
-      <c r="K152" s="82">
+      <c r="K152" s="61">
         <v>10.65</v>
       </c>
-      <c r="L152" s="80">
+      <c r="L152" s="59">
         <v>10.643000000000001</v>
       </c>
+      <c r="N152" s="97">
+        <v>5</v>
+      </c>
+      <c r="O152" s="97">
+        <v>9</v>
+      </c>
+      <c r="Q152" s="1">
+        <v>1.7999999999999999E-2</v>
+      </c>
+      <c r="R152" s="1">
+        <v>8.9999999999999993E-3</v>
+      </c>
     </row>
     <row r="153" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B153" s="73"/>
-      <c r="C153" s="86" t="s">
+      <c r="B153" s="92"/>
+      <c r="C153" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="D153" s="87">
+      <c r="D153" s="66">
         <v>10.631</v>
       </c>
-      <c r="E153" s="88"/>
-      <c r="F153" s="87"/>
-      <c r="G153" s="87">
-        <v>10.693</v>
-      </c>
-      <c r="H153" s="88"/>
-      <c r="I153" s="88"/>
-      <c r="J153" s="88"/>
-      <c r="K153" s="88"/>
-      <c r="L153" s="88">
+      <c r="E153" s="66">
+        <f>G153-($E$1*Q152)</f>
+        <v>10.649000000000001</v>
+      </c>
+      <c r="F153" s="66">
+        <f>G153-($F$1*Q152)</f>
+        <v>10.685</v>
+      </c>
+      <c r="G153" s="66">
+        <v>10.721</v>
+      </c>
+      <c r="H153" s="67">
+        <f>G153-($H$1*R152)</f>
+        <v>10.702999999999999</v>
+      </c>
+      <c r="I153" s="67">
+        <f>G153-($I$1*R152)</f>
+        <v>10.685</v>
+      </c>
+      <c r="J153" s="67">
+        <f>G153-($J$1*R152)</f>
+        <v>10.667</v>
+      </c>
+      <c r="K153" s="67">
+        <f>G153-($K$1*R152)</f>
+        <v>10.649000000000001</v>
+      </c>
+      <c r="L153" s="67">
         <v>10.643000000000001</v>
       </c>
     </row>
     <row r="154" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B154" s="73"/>
-      <c r="C154" s="89" t="s">
+      <c r="B154" s="92"/>
+      <c r="C154" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="D154" s="90">
+      <c r="D154" s="69">
         <f>D153-0.05</f>
         <v>10.581</v>
       </c>
-      <c r="E154" s="91"/>
-      <c r="F154" s="90"/>
-      <c r="G154" s="90">
+      <c r="E154" s="69">
+        <f>E153-0.05</f>
+        <v>10.599</v>
+      </c>
+      <c r="F154" s="69">
+        <f>F153-0.05</f>
+        <v>10.635</v>
+      </c>
+      <c r="G154" s="69">
         <f>G153-0.05</f>
-        <v>10.642999999999999</v>
-      </c>
-      <c r="H154" s="91"/>
-      <c r="I154" s="91"/>
-      <c r="J154" s="91"/>
-      <c r="K154" s="91"/>
-      <c r="L154" s="90">
+        <v>10.670999999999999</v>
+      </c>
+      <c r="H154" s="69">
+        <f>H153-0.05</f>
+        <v>10.652999999999999</v>
+      </c>
+      <c r="I154" s="69">
+        <f>I153-0.05</f>
+        <v>10.635</v>
+      </c>
+      <c r="J154" s="69">
+        <f>J153-0.05</f>
+        <v>10.616999999999999</v>
+      </c>
+      <c r="K154" s="70"/>
+      <c r="L154" s="69">
         <f>L153-0.05</f>
         <v>10.593</v>
       </c>
     </row>
     <row r="155" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B155" s="74"/>
-      <c r="C155" s="83" t="s">
+      <c r="B155" s="93"/>
+      <c r="C155" s="62" t="s">
         <v>54</v>
       </c>
-      <c r="D155" s="84">
+      <c r="D155" s="63">
         <v>0.05</v>
       </c>
-      <c r="E155" s="85"/>
-      <c r="F155" s="84"/>
-      <c r="G155" s="84">
+      <c r="E155" s="63">
+        <f>E152-E154</f>
+        <v>5.5999999999999162E-2</v>
+      </c>
+      <c r="F155" s="63">
+        <f>F152-F154</f>
+        <v>4.1000000000000369E-2</v>
+      </c>
+      <c r="G155" s="63">
         <f>G152-G154</f>
+        <v>2.2000000000000242E-2</v>
+      </c>
+      <c r="H155" s="63">
+        <f>H152-H154</f>
+        <v>2.9000000000001691E-2</v>
+      </c>
+      <c r="I155" s="63">
+        <f>I152-I154</f>
+        <v>4.8999999999999488E-2</v>
+      </c>
+      <c r="J155" s="63">
+        <f>J152-J154</f>
+        <v>6.6000000000000725E-2</v>
+      </c>
+      <c r="K155" s="64"/>
+      <c r="L155" s="63">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="158" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B158" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="C158" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D158" s="61">
+        <v>10.64</v>
+      </c>
+      <c r="E158" s="59"/>
+      <c r="F158" s="61">
+        <v>10.663</v>
+      </c>
+      <c r="G158" s="61">
+        <v>10.669</v>
+      </c>
+      <c r="H158" s="59">
+        <v>10.608000000000001</v>
+      </c>
+      <c r="I158" s="59"/>
+      <c r="J158" s="59"/>
+      <c r="K158" s="59"/>
+      <c r="L158" s="61">
+        <v>10.56</v>
+      </c>
+      <c r="N158" s="97">
+        <v>3.26</v>
+      </c>
+      <c r="O158" s="97">
+        <v>3.09</v>
+      </c>
+      <c r="Q158" s="32">
+        <v>8.9999999999999993E-3</v>
+      </c>
+      <c r="R158" s="1">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="159" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B159" s="92"/>
+      <c r="C159" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="D159" s="66">
+        <v>10.64</v>
+      </c>
+      <c r="E159" s="67"/>
+      <c r="F159" s="66">
+        <v>10.663</v>
+      </c>
+      <c r="G159" s="66">
+        <v>10.669</v>
+      </c>
+      <c r="H159" s="67">
+        <v>10.608000000000001</v>
+      </c>
+      <c r="I159" s="67"/>
+      <c r="J159" s="67"/>
+      <c r="K159" s="67"/>
+      <c r="L159" s="66">
+        <v>10.56</v>
+      </c>
+    </row>
+    <row r="160" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B160" s="92"/>
+      <c r="C160" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="D160" s="69">
+        <f>D159-0.05</f>
+        <v>10.59</v>
+      </c>
+      <c r="E160" s="70"/>
+      <c r="F160" s="69">
+        <f>F159-0.05</f>
+        <v>10.613</v>
+      </c>
+      <c r="G160" s="69">
+        <f>G159-0.05</f>
+        <v>10.619</v>
+      </c>
+      <c r="H160" s="69">
+        <f>H159-0.05</f>
+        <v>10.558</v>
+      </c>
+      <c r="I160" s="69"/>
+      <c r="J160" s="69"/>
+      <c r="K160" s="70"/>
+      <c r="L160" s="69">
+        <f>L159-0.05</f>
+        <v>10.51</v>
+      </c>
+    </row>
+    <row r="161" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B161" s="93"/>
+      <c r="C161" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="D161" s="63">
+        <v>0.05</v>
+      </c>
+      <c r="E161" s="64"/>
+      <c r="F161" s="63">
+        <f>F158-F160</f>
         <v>5.0000000000000711E-2</v>
       </c>
-      <c r="H155" s="85"/>
-      <c r="I155" s="85"/>
-      <c r="J155" s="85"/>
-      <c r="K155" s="85"/>
-      <c r="L155" s="84">
+      <c r="G161" s="63">
+        <f>G158-G160</f>
+        <v>5.0000000000000711E-2</v>
+      </c>
+      <c r="H161" s="63">
+        <f>H158-H160</f>
+        <v>5.0000000000000711E-2</v>
+      </c>
+      <c r="I161" s="63"/>
+      <c r="J161" s="63"/>
+      <c r="K161" s="64"/>
+      <c r="L161" s="63">
         <v>0.05</v>
       </c>
     </row>
+    <row r="162" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B162" s="71"/>
+      <c r="C162" s="73"/>
+      <c r="D162" s="74"/>
+      <c r="E162" s="75"/>
+      <c r="F162" s="74"/>
+      <c r="G162" s="74"/>
+      <c r="H162" s="74"/>
+      <c r="I162" s="74"/>
+      <c r="J162" s="75"/>
+      <c r="K162" s="75"/>
+      <c r="L162" s="72"/>
+      <c r="N162" s="98"/>
+      <c r="O162" s="98"/>
+      <c r="Q162" s="32"/>
+      <c r="R162" s="32"/>
+    </row>
+    <row r="163" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B163" s="91" t="s">
+        <v>1</v>
+      </c>
+      <c r="C163" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D163" s="61">
+        <v>10.675000000000001</v>
+      </c>
+      <c r="E163" s="59"/>
+      <c r="F163" s="61">
+        <v>10.675000000000001</v>
+      </c>
+      <c r="G163" s="61">
+        <v>10.677</v>
+      </c>
+      <c r="H163" s="59">
+        <v>10.645</v>
+      </c>
+      <c r="I163" s="59"/>
+      <c r="J163" s="59"/>
+      <c r="K163" s="59"/>
+      <c r="L163" s="59">
+        <v>10.587999999999999</v>
+      </c>
+      <c r="N163" s="97">
+        <v>3.1</v>
+      </c>
+      <c r="O163" s="97">
+        <v>3.2</v>
+      </c>
+      <c r="Q163" s="32">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="R163" s="1">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B164" s="92"/>
+      <c r="C164" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="D164" s="66">
+        <v>10.675000000000001</v>
+      </c>
+      <c r="E164" s="67"/>
+      <c r="F164" s="66">
+        <f>G164-($F$1*Q163)</f>
+        <v>10.681000000000001</v>
+      </c>
+      <c r="G164" s="66">
+        <v>10.691000000000001</v>
+      </c>
+      <c r="H164" s="67">
+        <f>G164-($H$1*R163)</f>
+        <v>10.627000000000001</v>
+      </c>
+      <c r="I164" s="67"/>
+      <c r="J164" s="67"/>
+      <c r="K164" s="67"/>
+      <c r="L164" s="67">
+        <v>10.587999999999999</v>
+      </c>
+    </row>
+    <row r="165" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B165" s="92"/>
+      <c r="C165" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="D165" s="69">
+        <f>D164-0.05</f>
+        <v>10.625</v>
+      </c>
+      <c r="E165" s="70"/>
+      <c r="F165" s="69">
+        <f>F164-0.05</f>
+        <v>10.631</v>
+      </c>
+      <c r="G165" s="69">
+        <f>G164-0.05</f>
+        <v>10.641</v>
+      </c>
+      <c r="H165" s="69">
+        <f>H164-0.05</f>
+        <v>10.577</v>
+      </c>
+      <c r="I165" s="69"/>
+      <c r="J165" s="69"/>
+      <c r="K165" s="70"/>
+      <c r="L165" s="69">
+        <f>L164-0.05</f>
+        <v>10.537999999999998</v>
+      </c>
+    </row>
+    <row r="166" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B166" s="93"/>
+      <c r="C166" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="D166" s="63">
+        <v>0.05</v>
+      </c>
+      <c r="E166" s="64"/>
+      <c r="F166" s="63">
+        <f>F163-F165</f>
+        <v>4.4000000000000483E-2</v>
+      </c>
+      <c r="G166" s="63">
+        <f>G163-G165</f>
+        <v>3.5999999999999588E-2</v>
+      </c>
+      <c r="H166" s="63">
+        <f>H163-H165</f>
+        <v>6.7999999999999616E-2</v>
+      </c>
+      <c r="I166" s="63"/>
+      <c r="J166" s="63"/>
+      <c r="K166" s="64"/>
+      <c r="L166" s="63">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="167" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B167" s="71"/>
+      <c r="C167" s="73"/>
+      <c r="D167" s="74"/>
+      <c r="E167" s="75"/>
+      <c r="F167" s="74"/>
+      <c r="G167" s="74"/>
+      <c r="H167" s="74"/>
+      <c r="I167" s="74"/>
+      <c r="J167" s="75"/>
+      <c r="K167" s="75"/>
+      <c r="L167" s="72"/>
+      <c r="N167" s="98"/>
+      <c r="O167" s="98"/>
+      <c r="Q167" s="32"/>
+      <c r="R167" s="32"/>
+    </row>
+    <row r="168" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B168" s="91" t="s">
+        <v>41</v>
+      </c>
+      <c r="C168" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D168" s="61">
+        <v>10.688000000000001</v>
+      </c>
+      <c r="E168" s="59"/>
+      <c r="F168" s="61">
+        <v>10.69</v>
+      </c>
+      <c r="G168" s="61">
+        <v>10.702</v>
+      </c>
+      <c r="H168" s="59">
+        <v>10.645</v>
+      </c>
+      <c r="I168" s="59"/>
+      <c r="J168" s="59"/>
+      <c r="K168" s="59"/>
+      <c r="L168" s="59">
+        <v>10.603</v>
+      </c>
+      <c r="N168" s="97">
+        <v>3.02</v>
+      </c>
+      <c r="O168" s="97">
+        <v>3.13</v>
+      </c>
+      <c r="Q168" s="32">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="R168" s="1">
+        <v>3.2000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="169" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B169" s="92"/>
+      <c r="C169" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="D169" s="66">
+        <v>10.721</v>
+      </c>
+      <c r="E169" s="67"/>
+      <c r="F169" s="66">
+        <f>G169-($F$1*Q168)</f>
+        <v>10.692</v>
+      </c>
+      <c r="G169" s="66">
+        <v>10.702</v>
+      </c>
+      <c r="H169" s="67">
+        <f>G169-($H$1*R168)</f>
+        <v>10.638</v>
+      </c>
+      <c r="I169" s="67"/>
+      <c r="J169" s="67"/>
+      <c r="K169" s="67"/>
+      <c r="L169" s="67">
+        <v>10.603</v>
+      </c>
+    </row>
+    <row r="170" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B170" s="92"/>
+      <c r="C170" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="D170" s="69">
+        <f>D169-0.05</f>
+        <v>10.670999999999999</v>
+      </c>
+      <c r="E170" s="70"/>
+      <c r="F170" s="69">
+        <f>F169-0.05</f>
+        <v>10.641999999999999</v>
+      </c>
+      <c r="G170" s="69">
+        <f>G169-0.05</f>
+        <v>10.651999999999999</v>
+      </c>
+      <c r="H170" s="69">
+        <f>H169-0.05</f>
+        <v>10.587999999999999</v>
+      </c>
+      <c r="I170" s="69"/>
+      <c r="J170" s="69"/>
+      <c r="K170" s="70"/>
+      <c r="L170" s="69">
+        <f>L169-0.05</f>
+        <v>10.552999999999999</v>
+      </c>
+    </row>
+    <row r="171" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B171" s="93"/>
+      <c r="C171" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="D171" s="63">
+        <f>D168-D170</f>
+        <v>1.7000000000001236E-2</v>
+      </c>
+      <c r="E171" s="64"/>
+      <c r="F171" s="63">
+        <f>F168-F170</f>
+        <v>4.8000000000000043E-2</v>
+      </c>
+      <c r="G171" s="63">
+        <f>G168-G170</f>
+        <v>5.0000000000000711E-2</v>
+      </c>
+      <c r="H171" s="63">
+        <f>H168-H170</f>
+        <v>5.7000000000000384E-2</v>
+      </c>
+      <c r="I171" s="63"/>
+      <c r="J171" s="63"/>
+      <c r="K171" s="64"/>
+      <c r="L171" s="63">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="172" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B172" s="71"/>
+      <c r="C172" s="73"/>
+      <c r="D172" s="74"/>
+      <c r="E172" s="75"/>
+      <c r="F172" s="74"/>
+      <c r="G172" s="74"/>
+      <c r="H172" s="74"/>
+      <c r="I172" s="74"/>
+      <c r="J172" s="75"/>
+      <c r="K172" s="75"/>
+      <c r="L172" s="72"/>
+      <c r="N172" s="98"/>
+      <c r="O172" s="98"/>
+      <c r="Q172" s="32"/>
+      <c r="R172" s="32"/>
+    </row>
+    <row r="173" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B173" s="91" t="s">
+        <v>2</v>
+      </c>
+      <c r="C173" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D173" s="61">
+        <v>10.609</v>
+      </c>
+      <c r="E173" s="59"/>
+      <c r="F173" s="61">
+        <v>10.635999999999999</v>
+      </c>
+      <c r="G173" s="61">
+        <v>10.669</v>
+      </c>
+      <c r="H173" s="59">
+        <v>10.651999999999999</v>
+      </c>
+      <c r="I173" s="59"/>
+      <c r="J173" s="59"/>
+      <c r="K173" s="59"/>
+      <c r="L173" s="59">
+        <v>10.605</v>
+      </c>
+      <c r="N173" s="97">
+        <v>3.23</v>
+      </c>
+      <c r="O173" s="97">
+        <v>3.15</v>
+      </c>
+      <c r="Q173" s="32">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="R173" s="1">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="174" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B174" s="92"/>
+      <c r="C174" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="D174" s="66">
+        <v>10.609</v>
+      </c>
+      <c r="E174" s="67"/>
+      <c r="F174" s="66">
+        <f>G174-($F$1*Q173)</f>
+        <v>10.636000000000001</v>
+      </c>
+      <c r="G174" s="66">
+        <v>10.678000000000001</v>
+      </c>
+      <c r="H174" s="67">
+        <f>G174-($H$1*R173)</f>
+        <v>10.632000000000001</v>
+      </c>
+      <c r="I174" s="67"/>
+      <c r="J174" s="67"/>
+      <c r="K174" s="67"/>
+      <c r="L174" s="67">
+        <v>10.605</v>
+      </c>
+    </row>
+    <row r="175" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B175" s="92"/>
+      <c r="C175" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="D175" s="69">
+        <f>D174-0.05</f>
+        <v>10.558999999999999</v>
+      </c>
+      <c r="E175" s="70"/>
+      <c r="F175" s="69">
+        <f>F174-0.05</f>
+        <v>10.586</v>
+      </c>
+      <c r="G175" s="69">
+        <f>G174-0.05</f>
+        <v>10.628</v>
+      </c>
+      <c r="H175" s="69">
+        <f>H174-0.05</f>
+        <v>10.582000000000001</v>
+      </c>
+      <c r="I175" s="69"/>
+      <c r="J175" s="69"/>
+      <c r="K175" s="70"/>
+      <c r="L175" s="69">
+        <f>L174-0.05</f>
+        <v>10.555</v>
+      </c>
+    </row>
+    <row r="176" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B176" s="93"/>
+      <c r="C176" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="D176" s="63">
+        <v>0.05</v>
+      </c>
+      <c r="E176" s="64"/>
+      <c r="F176" s="63">
+        <f>F173-F175</f>
+        <v>4.9999999999998934E-2</v>
+      </c>
+      <c r="G176" s="63">
+        <f>G173-G175</f>
+        <v>4.1000000000000369E-2</v>
+      </c>
+      <c r="H176" s="63">
+        <f>H173-H175</f>
+        <v>6.9999999999998508E-2</v>
+      </c>
+      <c r="I176" s="63"/>
+      <c r="J176" s="63"/>
+      <c r="K176" s="64"/>
+      <c r="L176" s="63">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="177" spans="2:18" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B177" s="71"/>
+      <c r="C177" s="73"/>
+      <c r="D177" s="74"/>
+      <c r="E177" s="75"/>
+      <c r="F177" s="74"/>
+      <c r="G177" s="74"/>
+      <c r="H177" s="74"/>
+      <c r="I177" s="74"/>
+      <c r="J177" s="75"/>
+      <c r="K177" s="75"/>
+      <c r="L177" s="72"/>
+      <c r="N177" s="98"/>
+      <c r="O177" s="98"/>
+      <c r="Q177" s="32"/>
+      <c r="R177" s="32"/>
+    </row>
+    <row r="178" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B178" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="C178" s="60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D178" s="61">
+        <v>10.553000000000001</v>
+      </c>
+      <c r="E178" s="59"/>
+      <c r="F178" s="61">
+        <v>10.592000000000001</v>
+      </c>
+      <c r="G178" s="61">
+        <v>10.643000000000001</v>
+      </c>
+      <c r="H178" s="59">
+        <v>10.615</v>
+      </c>
+      <c r="I178" s="59"/>
+      <c r="J178" s="59"/>
+      <c r="K178" s="59"/>
+      <c r="L178" s="59">
+        <v>10.569000000000001</v>
+      </c>
+      <c r="N178" s="97">
+        <v>3.15</v>
+      </c>
+      <c r="O178" s="97">
+        <v>3.1</v>
+      </c>
+      <c r="Q178" s="32">
+        <v>2.9000000000000001E-2</v>
+      </c>
+      <c r="R178" s="1">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="179" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B179" s="92"/>
+      <c r="C179" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="D179" s="66">
+        <v>10.553000000000001</v>
+      </c>
+      <c r="E179" s="67"/>
+      <c r="F179" s="66">
+        <v>10.592000000000001</v>
+      </c>
+      <c r="G179" s="66">
+        <v>10.643000000000001</v>
+      </c>
+      <c r="H179" s="67">
+        <v>10.615</v>
+      </c>
+      <c r="I179" s="67"/>
+      <c r="J179" s="67"/>
+      <c r="K179" s="67"/>
+      <c r="L179" s="67">
+        <v>10.569000000000001</v>
+      </c>
+    </row>
+    <row r="180" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B180" s="92"/>
+      <c r="C180" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="D180" s="69">
+        <f>D179-0.05</f>
+        <v>10.503</v>
+      </c>
+      <c r="E180" s="70"/>
+      <c r="F180" s="69">
+        <f>F179-0.05</f>
+        <v>10.542</v>
+      </c>
+      <c r="G180" s="69">
+        <f>G179-0.05</f>
+        <v>10.593</v>
+      </c>
+      <c r="H180" s="69">
+        <f>H179-0.05</f>
+        <v>10.565</v>
+      </c>
+      <c r="I180" s="69"/>
+      <c r="J180" s="69"/>
+      <c r="K180" s="70"/>
+      <c r="L180" s="69">
+        <f>L179-0.05</f>
+        <v>10.519</v>
+      </c>
+    </row>
+    <row r="181" spans="2:18" x14ac:dyDescent="0.4">
+      <c r="B181" s="93"/>
+      <c r="C181" s="62" t="s">
+        <v>54</v>
+      </c>
+      <c r="D181" s="63">
+        <v>0.05</v>
+      </c>
+      <c r="E181" s="64"/>
+      <c r="F181" s="63">
+        <f>F178-F180</f>
+        <v>5.0000000000000711E-2</v>
+      </c>
+      <c r="G181" s="63">
+        <f>G178-G180</f>
+        <v>5.0000000000000711E-2</v>
+      </c>
+      <c r="H181" s="63">
+        <f>H178-H180</f>
+        <v>5.0000000000000711E-2</v>
+      </c>
+      <c r="I181" s="63"/>
+      <c r="J181" s="63"/>
+      <c r="K181" s="64"/>
+      <c r="L181" s="63">
+        <v>0.05</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="36">
+    <mergeCell ref="B163:B166"/>
+    <mergeCell ref="B168:B171"/>
+    <mergeCell ref="B173:B176"/>
+    <mergeCell ref="B178:B181"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B12:B15"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B158:B161"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B27:B30"/>
+    <mergeCell ref="B32:B35"/>
+    <mergeCell ref="B37:B40"/>
+    <mergeCell ref="B42:B45"/>
+    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="B52:B55"/>
+    <mergeCell ref="B57:B60"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="B77:B80"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="B87:B90"/>
+    <mergeCell ref="B92:B95"/>
+    <mergeCell ref="B97:B100"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="B107:B110"/>
+    <mergeCell ref="B112:B115"/>
+    <mergeCell ref="B117:B120"/>
     <mergeCell ref="B147:B150"/>
     <mergeCell ref="B152:B155"/>
     <mergeCell ref="B122:B125"/>
@@ -12712,30 +13569,6 @@
     <mergeCell ref="B132:B135"/>
     <mergeCell ref="B137:B140"/>
     <mergeCell ref="B142:B145"/>
-    <mergeCell ref="B97:B100"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="B107:B110"/>
-    <mergeCell ref="B112:B115"/>
-    <mergeCell ref="B117:B120"/>
-    <mergeCell ref="B72:B75"/>
-    <mergeCell ref="B77:B80"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="B87:B90"/>
-    <mergeCell ref="B92:B95"/>
-    <mergeCell ref="B47:B50"/>
-    <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B57:B60"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B27:B30"/>
-    <mergeCell ref="B32:B35"/>
-    <mergeCell ref="B37:B40"/>
-    <mergeCell ref="B42:B45"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B12:B15"/>
-    <mergeCell ref="B17:B20"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/計画.xlsx
+++ b/data/計画.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\〇市道 南千反畑町第１号線舗装補修工事\１０測量と設計照査\そういち担当\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C95C783A-FD16-4784-A306-F01A4E6CAF73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EE65DD-EE52-432F-A5C1-BFFCD9C0AF35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{9B8B15DF-CC4A-4363-BE7A-E60876B7E9DD}"/>
   </bookViews>
@@ -842,7 +842,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1071,6 +1071,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1081,21 +1084,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1110,11 +1098,32 @@
     <xf numFmtId="176" fontId="2" fillId="4" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1133,12 +1142,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2075,17 +2078,17 @@
       <c r="H34" s="2"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="76"/>
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
+      <c r="B35" s="77"/>
+      <c r="C35" s="77"/>
+      <c r="D35" s="77"/>
+      <c r="E35" s="77"/>
       <c r="H35" s="2"/>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B36" s="76"/>
-      <c r="C36" s="76"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="76"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="77"/>
       <c r="H36" s="2"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.4">
@@ -3152,12 +3155,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="2:13" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C2" s="78"/>
-      <c r="D2" s="78"/>
+      <c r="C2" s="79"/>
+      <c r="D2" s="79"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.4">
       <c r="B3" s="4"/>
@@ -3977,19 +3980,19 @@
       <c r="I35" s="2"/>
     </row>
     <row r="36" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B36" s="76"/>
-      <c r="C36" s="76"/>
-      <c r="D36" s="76"/>
-      <c r="E36" s="79"/>
-      <c r="F36" s="79"/>
+      <c r="B36" s="77"/>
+      <c r="C36" s="77"/>
+      <c r="D36" s="77"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
       <c r="I36" s="2"/>
     </row>
     <row r="37" spans="2:13" x14ac:dyDescent="0.4">
-      <c r="B37" s="76"/>
-      <c r="C37" s="76"/>
-      <c r="D37" s="76"/>
-      <c r="E37" s="79"/>
-      <c r="F37" s="79"/>
+      <c r="B37" s="77"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="77"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
       <c r="I37" s="2"/>
     </row>
     <row r="38" spans="2:13" x14ac:dyDescent="0.4">
@@ -5058,12 +5061,12 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B2" s="30"/>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="81"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="89"/>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.4">
@@ -5093,23 +5096,23 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B4" s="30"/>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="84"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="87"/>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="81" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="44">
         <v>9.7159999999999993</v>
       </c>
-      <c r="D5" s="87">
-        <v>9.81</v>
+      <c r="D5" s="83">
+        <v>9.8529999999999998</v>
       </c>
       <c r="E5" s="35"/>
       <c r="F5" s="49">
@@ -5117,37 +5120,37 @@
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="38">
-        <v>2.99</v>
+        <v>4.25</v>
       </c>
       <c r="I5" s="38">
-        <v>5.38</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="6" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="86"/>
+      <c r="B6" s="82"/>
       <c r="C6" s="45">
         <f>(D5-C5)/H5</f>
-        <v>3.1438127090301402E-2</v>
-      </c>
-      <c r="D6" s="88"/>
+        <v>3.2235294117647167E-2</v>
+      </c>
+      <c r="D6" s="84"/>
       <c r="E6" s="39"/>
       <c r="F6" s="50">
         <f>(D5-F5)/I5</f>
-        <v>2.3977695167286494E-2</v>
+        <v>4.195121951219527E-2</v>
       </c>
       <c r="G6" s="40"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="81" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="46">
         <v>9.8249999999999993</v>
       </c>
-      <c r="D7" s="87">
-        <v>9.8550000000000004</v>
+      <c r="D7" s="83">
+        <v>9.8510000000000009</v>
       </c>
       <c r="E7" s="35"/>
       <c r="F7" s="51">
@@ -5155,37 +5158,37 @@
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="38">
-        <v>2.97</v>
+        <v>4.24</v>
       </c>
       <c r="I7" s="38">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B8" s="86"/>
+      <c r="B8" s="82"/>
       <c r="C8" s="45">
         <f>(D7-C7)/H7</f>
-        <v>1.0101010101010484E-2</v>
-      </c>
-      <c r="D8" s="88"/>
+        <v>6.1320754716984848E-3</v>
+      </c>
+      <c r="D8" s="84"/>
       <c r="E8" s="39"/>
       <c r="F8" s="50">
         <f>(D7-F7)/I7</f>
-        <v>2.0740740740740757E-2</v>
+        <v>2.6150121065375433E-2</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="38"/>
       <c r="I8" s="38"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="81" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="46">
         <v>9.8689999999999998</v>
       </c>
-      <c r="D9" s="87">
-        <v>9.9009999999999998</v>
+      <c r="D9" s="83">
+        <v>9.9160000000000004</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="51">
@@ -5193,37 +5196,37 @@
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="38">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="I9" s="38">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B10" s="86"/>
+      <c r="B10" s="82"/>
       <c r="C10" s="45">
         <f>(D9-C9)/H9</f>
-        <v>1.0847457627118653E-2</v>
-      </c>
-      <c r="D10" s="88"/>
+        <v>1.1190476190476332E-2</v>
+      </c>
+      <c r="D10" s="84"/>
       <c r="E10" s="39"/>
       <c r="F10" s="50">
         <f>(D9-F9)/I9</f>
-        <v>1.2222222222222027E-2</v>
+        <v>1.9612590799031361E-2</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="38"/>
       <c r="I10" s="38"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="81" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="46">
         <v>9.8829999999999991</v>
       </c>
-      <c r="D11" s="87">
-        <v>9.9350000000000005</v>
+      <c r="D11" s="83">
+        <v>9.9420000000000002</v>
       </c>
       <c r="E11" s="35"/>
       <c r="F11" s="51">
@@ -5231,80 +5234,78 @@
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="38">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="I11" s="38">
-        <v>5.25</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B12" s="86"/>
+      <c r="B12" s="82"/>
       <c r="C12" s="45">
         <f>(D11-C11)/H11</f>
-        <v>1.7808219178082663E-2</v>
-      </c>
-      <c r="D12" s="88"/>
+        <v>1.4047619047619298E-2</v>
+      </c>
+      <c r="D12" s="84"/>
       <c r="E12" s="39"/>
       <c r="F12" s="50">
         <f>(D11-F11)/I11</f>
-        <v>1.085714285714293E-2</v>
+        <v>1.6080402010050267E-2</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="38"/>
       <c r="I12" s="38"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B13" s="89" t="s">
+      <c r="B13" s="90" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="46">
         <v>9.8719999999999999</v>
       </c>
-      <c r="D13" s="87">
-        <v>9.9450000000000003</v>
-      </c>
-      <c r="E13" s="36">
+      <c r="D13" s="92">
         <v>9.9550000000000001</v>
       </c>
+      <c r="E13" s="35"/>
       <c r="F13" s="51">
         <v>9.8729999999999993</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="38">
-        <v>2.93</v>
+        <v>4.18</v>
       </c>
       <c r="I13" s="38">
-        <v>5.13</v>
+        <v>3.9</v>
       </c>
       <c r="J13">
         <v>1.4</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B14" s="90"/>
+      <c r="B14" s="91"/>
       <c r="C14" s="45">
         <f>(D13-C13)/H13</f>
-        <v>2.4914675767918223E-2</v>
-      </c>
-      <c r="D14" s="88"/>
+        <v>1.9856459330143586E-2</v>
+      </c>
+      <c r="D14" s="93"/>
       <c r="E14" s="39"/>
       <c r="F14" s="50">
         <f>(D13-F13)/I13</f>
-        <v>1.4035087719298431E-2</v>
+        <v>2.1025641025641216E-2</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="38"/>
       <c r="I14" s="38"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B15" s="85" t="s">
+      <c r="B15" s="81" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="46">
         <v>9.9030000000000005</v>
       </c>
-      <c r="D15" s="87">
-        <v>9.9469999999999992</v>
+      <c r="D15" s="83">
+        <v>9.9600000000000009</v>
       </c>
       <c r="E15" s="35"/>
       <c r="F15" s="51">
@@ -5312,37 +5313,37 @@
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="38">
-        <v>3</v>
+        <v>4.26</v>
       </c>
       <c r="I15" s="38">
-        <v>4.97</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B16" s="86"/>
+      <c r="B16" s="82"/>
       <c r="C16" s="45">
         <f>(D15-C15)/H15</f>
-        <v>1.4666666666666236E-2</v>
-      </c>
-      <c r="D16" s="88"/>
+        <v>1.3380281690140937E-2</v>
+      </c>
+      <c r="D16" s="84"/>
       <c r="E16" s="39"/>
       <c r="F16" s="50">
         <f>(D15-F15)/I15</f>
-        <v>1.2676056338028293E-2</v>
+        <v>2.0540540540541156E-2</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="38"/>
       <c r="I16" s="38"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B17" s="85" t="s">
+      <c r="B17" s="81" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="46">
         <v>9.9260000000000002</v>
       </c>
-      <c r="D17" s="87">
-        <v>9.9870000000000001</v>
+      <c r="D17" s="83">
+        <v>9.9819999999999993</v>
       </c>
       <c r="E17" s="35"/>
       <c r="F17" s="51">
@@ -5350,36 +5351,36 @@
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="38">
-        <v>3.05</v>
+        <v>3.72</v>
       </c>
       <c r="I17" s="38">
-        <v>4.46</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B18" s="86"/>
+      <c r="B18" s="82"/>
       <c r="C18" s="45">
         <f>(D17-C17)/H17</f>
-        <v>1.9999999999999983E-2</v>
-      </c>
-      <c r="D18" s="88"/>
+        <v>1.5053763440859989E-2</v>
+      </c>
+      <c r="D18" s="84"/>
       <c r="E18" s="39"/>
       <c r="F18" s="50">
         <f>(D17-F17)/I17</f>
-        <v>1.6816143497757688E-2</v>
+        <v>1.8421052631578557E-2</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="38"/>
       <c r="I18" s="38"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B19" s="85" t="s">
+      <c r="B19" s="81" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="46">
         <v>10.038</v>
       </c>
-      <c r="D19" s="87">
+      <c r="D19" s="83">
         <v>10.050000000000001</v>
       </c>
       <c r="E19" s="35"/>
@@ -5395,12 +5396,12 @@
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B20" s="86"/>
+      <c r="B20" s="82"/>
       <c r="C20" s="45">
         <f>(D19-C19)/H19</f>
         <v>3.7500000000001421E-3</v>
       </c>
-      <c r="D20" s="88"/>
+      <c r="D20" s="84"/>
       <c r="E20" s="39"/>
       <c r="F20" s="50">
         <f>(D19-F19)/I19</f>
@@ -5411,13 +5412,13 @@
       <c r="I20" s="38"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="90" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="46">
         <v>10.052</v>
       </c>
-      <c r="D21" s="87">
+      <c r="D21" s="83">
         <v>10.054</v>
       </c>
       <c r="E21" s="36">
@@ -5438,12 +5439,12 @@
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B22" s="90"/>
+      <c r="B22" s="91"/>
       <c r="C22" s="45">
         <f>(D21-C21)/H21</f>
         <v>6.3694267515944836E-4</v>
       </c>
-      <c r="D22" s="88"/>
+      <c r="D22" s="84"/>
       <c r="E22" s="39"/>
       <c r="F22" s="50">
         <f>(D21-F21)/I21</f>
@@ -5454,13 +5455,13 @@
       <c r="I22" s="38"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="81" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="46">
         <v>10.002000000000001</v>
       </c>
-      <c r="D23" s="87">
+      <c r="D23" s="83">
         <v>10.045999999999999</v>
       </c>
       <c r="E23" s="35"/>
@@ -5476,12 +5477,12 @@
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B24" s="86"/>
+      <c r="B24" s="82"/>
       <c r="C24" s="45">
         <f>(D23-C23)/H23</f>
         <v>1.3836477987420976E-2</v>
       </c>
-      <c r="D24" s="88"/>
+      <c r="D24" s="84"/>
       <c r="E24" s="39"/>
       <c r="F24" s="50">
         <f>(D23-F23)/I23</f>
@@ -5492,13 +5493,13 @@
       <c r="I24" s="38"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B25" s="85" t="s">
+      <c r="B25" s="81" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="46">
         <v>9.9960000000000004</v>
       </c>
-      <c r="D25" s="87">
+      <c r="D25" s="83">
         <v>10.048999999999999</v>
       </c>
       <c r="E25" s="35"/>
@@ -5514,12 +5515,12 @@
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B26" s="86"/>
+      <c r="B26" s="82"/>
       <c r="C26" s="45">
         <f>(D25-C25)/H25</f>
         <v>1.6562499999999702E-2</v>
       </c>
-      <c r="D26" s="88"/>
+      <c r="D26" s="84"/>
       <c r="E26" s="39"/>
       <c r="F26" s="50">
         <f>(D25-F25)/I25</f>
@@ -5530,13 +5531,13 @@
       <c r="I26" s="38"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B27" s="85" t="s">
+      <c r="B27" s="81" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="46">
         <v>10.002000000000001</v>
       </c>
-      <c r="D27" s="87">
+      <c r="D27" s="83">
         <v>10.068</v>
       </c>
       <c r="E27" s="35"/>
@@ -5552,12 +5553,12 @@
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B28" s="86"/>
+      <c r="B28" s="82"/>
       <c r="C28" s="45">
         <f>(D27-C27)/H27</f>
         <v>2.0689655172413463E-2</v>
       </c>
-      <c r="D28" s="88"/>
+      <c r="D28" s="84"/>
       <c r="E28" s="39"/>
       <c r="F28" s="50">
         <f>(D27-F27)/I27</f>
@@ -5568,13 +5569,13 @@
       <c r="I28" s="38"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B29" s="85" t="s">
+      <c r="B29" s="81" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="46">
         <v>10.019</v>
       </c>
-      <c r="D29" s="87">
+      <c r="D29" s="83">
         <v>10.087999999999999</v>
       </c>
       <c r="E29" s="35"/>
@@ -5590,12 +5591,12 @@
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B30" s="86"/>
+      <c r="B30" s="82"/>
       <c r="C30" s="45">
         <f>(D29-C29)/H29</f>
         <v>2.1562499999999707E-2</v>
       </c>
-      <c r="D30" s="88"/>
+      <c r="D30" s="84"/>
       <c r="E30" s="39"/>
       <c r="F30" s="50">
         <f>(D29-F29)/I29</f>
@@ -5606,13 +5607,13 @@
       <c r="I30" s="38"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B31" s="85" t="s">
+      <c r="B31" s="81" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="46">
         <v>10.037000000000001</v>
       </c>
-      <c r="D31" s="87">
+      <c r="D31" s="83">
         <v>10.089</v>
       </c>
       <c r="E31" s="35"/>
@@ -5628,12 +5629,12 @@
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B32" s="86"/>
+      <c r="B32" s="82"/>
       <c r="C32" s="45">
         <f>(D31-C31)/H31</f>
         <v>1.635220125786151E-2</v>
       </c>
-      <c r="D32" s="88"/>
+      <c r="D32" s="84"/>
       <c r="E32" s="39"/>
       <c r="F32" s="50">
         <f>(D31-F31)/I31</f>
@@ -5644,13 +5645,13 @@
       <c r="I32" s="38"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B33" s="85" t="s">
+      <c r="B33" s="81" t="s">
         <v>13</v>
       </c>
       <c r="C33" s="46">
         <v>10.103</v>
       </c>
-      <c r="D33" s="87">
+      <c r="D33" s="83">
         <v>10.138</v>
       </c>
       <c r="E33" s="35"/>
@@ -5666,12 +5667,12 @@
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B34" s="86"/>
+      <c r="B34" s="82"/>
       <c r="C34" s="45">
         <f>(D33-C33)/H33</f>
         <v>1.0937500000000044E-2</v>
       </c>
-      <c r="D34" s="88"/>
+      <c r="D34" s="84"/>
       <c r="E34" s="39"/>
       <c r="F34" s="50">
         <f>(D33-F33)/I33</f>
@@ -5682,13 +5683,13 @@
       <c r="I34" s="38"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="89" t="s">
+      <c r="B35" s="90" t="s">
         <v>44</v>
       </c>
       <c r="C35" s="46">
         <v>10.132</v>
       </c>
-      <c r="D35" s="87">
+      <c r="D35" s="83">
         <v>10.153</v>
       </c>
       <c r="E35" s="36">
@@ -5709,12 +5710,12 @@
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B36" s="90"/>
+      <c r="B36" s="91"/>
       <c r="C36" s="45">
         <f>(D35-C35)/H35</f>
         <v>6.6037735849059104E-3</v>
       </c>
-      <c r="D36" s="88"/>
+      <c r="D36" s="84"/>
       <c r="E36" s="39"/>
       <c r="F36" s="50">
         <f>(D35-F35)/I35</f>
@@ -5725,13 +5726,13 @@
       <c r="I36" s="38"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B37" s="85" t="s">
+      <c r="B37" s="81" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="46">
         <v>10.108000000000001</v>
       </c>
-      <c r="D37" s="87">
+      <c r="D37" s="83">
         <v>10.154</v>
       </c>
       <c r="E37" s="35"/>
@@ -5747,12 +5748,12 @@
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B38" s="86"/>
+      <c r="B38" s="82"/>
       <c r="C38" s="45">
         <f>(D37-C37)/H37</f>
         <v>1.4465408805031249E-2</v>
       </c>
-      <c r="D38" s="88"/>
+      <c r="D38" s="84"/>
       <c r="E38" s="39"/>
       <c r="F38" s="50">
         <f>(D37-F37)/I37</f>
@@ -5763,13 +5764,13 @@
       <c r="I38" s="38"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B39" s="85" t="s">
+      <c r="B39" s="81" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="46">
         <v>10.14</v>
       </c>
-      <c r="D39" s="87">
+      <c r="D39" s="83">
         <v>10.192</v>
       </c>
       <c r="E39" s="35"/>
@@ -5785,12 +5786,12 @@
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B40" s="86"/>
+      <c r="B40" s="82"/>
       <c r="C40" s="45">
         <f>(D39-C39)/H39</f>
         <v>1.635220125786151E-2</v>
       </c>
-      <c r="D40" s="88"/>
+      <c r="D40" s="84"/>
       <c r="E40" s="39"/>
       <c r="F40" s="50">
         <f>(D39-F39)/I39</f>
@@ -5801,13 +5802,13 @@
       <c r="I40" s="38"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B41" s="85" t="s">
+      <c r="B41" s="81" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="46">
         <v>10.196</v>
       </c>
-      <c r="D41" s="87">
+      <c r="D41" s="83">
         <v>10.228</v>
       </c>
       <c r="E41" s="35"/>
@@ -5823,12 +5824,12 @@
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B42" s="86"/>
+      <c r="B42" s="82"/>
       <c r="C42" s="45">
         <f>(D41-C41)/H41</f>
         <v>1.0062893081761014E-2</v>
       </c>
-      <c r="D42" s="88"/>
+      <c r="D42" s="84"/>
       <c r="E42" s="39"/>
       <c r="F42" s="50">
         <f>(D41-F41)/I41</f>
@@ -5839,13 +5840,13 @@
       <c r="I42" s="38"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B43" s="85" t="s">
+      <c r="B43" s="81" t="s">
         <v>17</v>
       </c>
       <c r="C43" s="46">
         <v>10.236000000000001</v>
       </c>
-      <c r="D43" s="87">
+      <c r="D43" s="83">
         <v>10.298999999999999</v>
       </c>
       <c r="E43" s="35"/>
@@ -5861,12 +5862,12 @@
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B44" s="86"/>
+      <c r="B44" s="82"/>
       <c r="C44" s="45">
         <f>(D43-C43)/H43</f>
         <v>1.987381703469995E-2</v>
       </c>
-      <c r="D44" s="88"/>
+      <c r="D44" s="84"/>
       <c r="E44" s="39"/>
       <c r="F44" s="50">
         <f>(D43-F43)/I43</f>
@@ -5877,13 +5878,13 @@
       <c r="I44" s="38"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B45" s="85" t="s">
+      <c r="B45" s="81" t="s">
         <v>18</v>
       </c>
       <c r="C45" s="46">
         <v>10.359</v>
       </c>
-      <c r="D45" s="87">
+      <c r="D45" s="83">
         <v>10.364000000000001</v>
       </c>
       <c r="E45" s="35"/>
@@ -5899,12 +5900,12 @@
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B46" s="86"/>
+      <c r="B46" s="82"/>
       <c r="C46" s="45">
         <f>(D45-C45)/H45</f>
         <v>1.5625000000002442E-3</v>
       </c>
-      <c r="D46" s="88"/>
+      <c r="D46" s="84"/>
       <c r="E46" s="39"/>
       <c r="F46" s="50">
         <f>(D45-F45)/I45</f>
@@ -5915,13 +5916,13 @@
       <c r="I46" s="38"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B47" s="89" t="s">
+      <c r="B47" s="90" t="s">
         <v>37</v>
       </c>
       <c r="C47" s="46">
         <v>10.372</v>
       </c>
-      <c r="D47" s="87">
+      <c r="D47" s="83">
         <v>10.375999999999999</v>
       </c>
       <c r="E47" s="36">
@@ -5939,12 +5940,12 @@
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B48" s="90"/>
+      <c r="B48" s="91"/>
       <c r="C48" s="45">
         <f>(D47-C47)/H47</f>
         <v>1.2578616352199872E-3</v>
       </c>
-      <c r="D48" s="88"/>
+      <c r="D48" s="84"/>
       <c r="E48" s="39"/>
       <c r="F48" s="50">
         <f>(D47-F47)/I47</f>
@@ -5958,13 +5959,13 @@
       </c>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B49" s="85" t="s">
+      <c r="B49" s="81" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="46">
         <v>10.365</v>
       </c>
-      <c r="D49" s="87">
+      <c r="D49" s="83">
         <v>10.414</v>
       </c>
       <c r="E49" s="35"/>
@@ -5980,12 +5981,12 @@
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B50" s="86"/>
+      <c r="B50" s="82"/>
       <c r="C50" s="45">
         <f>(D49-C49)/H49</f>
         <v>1.5217391304347667E-2</v>
       </c>
-      <c r="D50" s="88"/>
+      <c r="D50" s="84"/>
       <c r="E50" s="39"/>
       <c r="F50" s="50">
         <f>(D49-F49)/I49</f>
@@ -5996,13 +5997,13 @@
       <c r="I50" s="38"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B51" s="85" t="s">
+      <c r="B51" s="81" t="s">
         <v>20</v>
       </c>
       <c r="C51" s="46">
         <v>10.404</v>
       </c>
-      <c r="D51" s="87">
+      <c r="D51" s="83">
         <v>10.465</v>
       </c>
       <c r="E51" s="35"/>
@@ -6018,12 +6019,12 @@
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B52" s="86"/>
+      <c r="B52" s="82"/>
       <c r="C52" s="45">
         <f>(D51-C51)/H51</f>
         <v>1.91823899371069E-2</v>
       </c>
-      <c r="D52" s="88"/>
+      <c r="D52" s="84"/>
       <c r="E52" s="39"/>
       <c r="F52" s="50">
         <f>(D51-F51)/I51</f>
@@ -6034,13 +6035,13 @@
       <c r="I52" s="38"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B53" s="85" t="s">
+      <c r="B53" s="81" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="46">
         <v>10.478</v>
       </c>
-      <c r="D53" s="87">
+      <c r="D53" s="83">
         <v>10.544</v>
       </c>
       <c r="E53" s="35"/>
@@ -6056,12 +6057,12 @@
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B54" s="86"/>
+      <c r="B54" s="82"/>
       <c r="C54" s="45">
         <f>(D53-C53)/H53</f>
         <v>2.0625000000000226E-2</v>
       </c>
-      <c r="D54" s="88"/>
+      <c r="D54" s="84"/>
       <c r="E54" s="39"/>
       <c r="F54" s="50">
         <f>(D53-F53)/I53</f>
@@ -6072,13 +6073,13 @@
       <c r="I54" s="38"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B55" s="89" t="s">
+      <c r="B55" s="90" t="s">
         <v>38</v>
       </c>
       <c r="C55" s="46">
         <v>10.510999999999999</v>
       </c>
-      <c r="D55" s="87">
+      <c r="D55" s="83">
         <v>10.589</v>
       </c>
       <c r="E55" s="36">
@@ -6096,12 +6097,12 @@
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B56" s="90"/>
+      <c r="B56" s="91"/>
       <c r="C56" s="45">
         <f>(D55-C55)/H55</f>
         <v>2.4528301886792822E-2</v>
       </c>
-      <c r="D56" s="88"/>
+      <c r="D56" s="84"/>
       <c r="E56" s="39"/>
       <c r="F56" s="50">
         <f>(D55-F55)/I55</f>
@@ -6115,13 +6116,13 @@
       </c>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B57" s="85" t="s">
+      <c r="B57" s="81" t="s">
         <v>22</v>
       </c>
       <c r="C57" s="46">
         <v>10.548999999999999</v>
       </c>
-      <c r="D57" s="87">
+      <c r="D57" s="83">
         <v>10.598000000000001</v>
       </c>
       <c r="E57" s="35"/>
@@ -6137,12 +6138,12 @@
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B58" s="86"/>
+      <c r="B58" s="82"/>
       <c r="C58" s="45">
         <f>(D57-C57)/H57</f>
         <v>1.5312500000000395E-2</v>
       </c>
-      <c r="D58" s="88"/>
+      <c r="D58" s="84"/>
       <c r="E58" s="39"/>
       <c r="F58" s="50">
         <f>(D57-F57)/I57</f>
@@ -6153,13 +6154,13 @@
       <c r="I58" s="38"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B59" s="85" t="s">
+      <c r="B59" s="81" t="s">
         <v>23</v>
       </c>
       <c r="C59" s="46">
         <v>10.606999999999999</v>
       </c>
-      <c r="D59" s="87">
+      <c r="D59" s="83">
         <v>10.669</v>
       </c>
       <c r="E59" s="35"/>
@@ -6175,12 +6176,12 @@
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B60" s="86"/>
+      <c r="B60" s="82"/>
       <c r="C60" s="45">
         <f>(D59-C59)/H59</f>
         <v>1.9375000000000364E-2</v>
       </c>
-      <c r="D60" s="88"/>
+      <c r="D60" s="84"/>
       <c r="E60" s="39"/>
       <c r="F60" s="50">
         <f>(D59-F59)/I59</f>
@@ -6191,13 +6192,13 @@
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B61" s="85" t="s">
+      <c r="B61" s="81" t="s">
         <v>39</v>
       </c>
       <c r="C61" s="46">
         <v>10.629</v>
       </c>
-      <c r="D61" s="87">
+      <c r="D61" s="83">
         <v>10.686</v>
       </c>
       <c r="E61" s="35"/>
@@ -6213,12 +6214,12 @@
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B62" s="86"/>
+      <c r="B62" s="82"/>
       <c r="C62" s="45">
         <f>(D61-C61)/H61</f>
         <v>1.786833855799385E-2</v>
       </c>
-      <c r="D62" s="88"/>
+      <c r="D62" s="84"/>
       <c r="E62" s="39"/>
       <c r="F62" s="50">
         <f>(D61-F61)/I61</f>
@@ -6229,13 +6230,13 @@
       <c r="I62" s="38"/>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B63" s="85" t="s">
+      <c r="B63" s="81" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="46">
         <v>10.673999999999999</v>
       </c>
-      <c r="D63" s="87">
+      <c r="D63" s="83">
         <v>10.734999999999999</v>
       </c>
       <c r="E63" s="35"/>
@@ -6247,9 +6248,9 @@
       <c r="I63" s="38"/>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B64" s="86"/>
+      <c r="B64" s="82"/>
       <c r="C64" s="45"/>
-      <c r="D64" s="88"/>
+      <c r="D64" s="84"/>
       <c r="E64" s="39"/>
       <c r="F64" s="50"/>
       <c r="G64" s="2"/>
@@ -6257,13 +6258,13 @@
       <c r="I64" s="38"/>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B65" s="85" t="s">
+      <c r="B65" s="81" t="s">
         <v>40</v>
       </c>
       <c r="C65" s="46">
         <v>10.631</v>
       </c>
-      <c r="D65" s="87">
+      <c r="D65" s="83">
         <v>10.693</v>
       </c>
       <c r="E65" s="35"/>
@@ -6275,9 +6276,9 @@
       <c r="I65" s="38"/>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B66" s="86"/>
+      <c r="B66" s="82"/>
       <c r="C66" s="45"/>
-      <c r="D66" s="88"/>
+      <c r="D66" s="84"/>
       <c r="E66" s="39"/>
       <c r="F66" s="50"/>
       <c r="G66" s="2"/>
@@ -6294,12 +6295,12 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B69" s="30"/>
-      <c r="C69" s="80" t="s">
+      <c r="C69" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="D69" s="80"/>
-      <c r="E69" s="80"/>
-      <c r="F69" s="81"/>
+      <c r="D69" s="88"/>
+      <c r="E69" s="88"/>
+      <c r="F69" s="89"/>
       <c r="H69" s="38"/>
       <c r="I69" s="38"/>
     </row>
@@ -6324,23 +6325,23 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B71" s="30"/>
-      <c r="C71" s="82" t="s">
+      <c r="C71" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="D71" s="83"/>
-      <c r="E71" s="83"/>
-      <c r="F71" s="84"/>
+      <c r="D71" s="86"/>
+      <c r="E71" s="86"/>
+      <c r="F71" s="87"/>
       <c r="H71" s="38"/>
       <c r="I71" s="38"/>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B72" s="85" t="s">
+      <c r="B72" s="81" t="s">
         <v>0</v>
       </c>
       <c r="C72" s="44">
         <v>10.64</v>
       </c>
-      <c r="D72" s="87">
+      <c r="D72" s="83">
         <v>10.669</v>
       </c>
       <c r="E72" s="35"/>
@@ -6355,12 +6356,12 @@
       </c>
     </row>
     <row r="73" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B73" s="86"/>
+      <c r="B73" s="82"/>
       <c r="C73" s="45">
         <f>(D72-C72)/H72</f>
         <v>8.8957055214723673E-3</v>
       </c>
-      <c r="D73" s="88"/>
+      <c r="D73" s="84"/>
       <c r="E73" s="39"/>
       <c r="F73" s="50">
         <f>(D72-F72)/I72</f>
@@ -6370,13 +6371,13 @@
       <c r="I73" s="42"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B74" s="85" t="s">
+      <c r="B74" s="81" t="s">
         <v>1</v>
       </c>
       <c r="C74" s="46">
         <v>10.675000000000001</v>
       </c>
-      <c r="D74" s="87">
+      <c r="D74" s="83">
         <v>10.677</v>
       </c>
       <c r="E74" s="35"/>
@@ -6391,12 +6392,12 @@
       </c>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B75" s="86"/>
+      <c r="B75" s="82"/>
       <c r="C75" s="45">
         <f>(D74-C74)/H74</f>
         <v>6.4516129032222307E-4</v>
       </c>
-      <c r="D75" s="88"/>
+      <c r="D75" s="84"/>
       <c r="E75" s="39"/>
       <c r="F75" s="50">
         <f>(D74-F74)/I74</f>
@@ -6406,13 +6407,13 @@
       <c r="I75" s="38"/>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B76" s="85" t="s">
+      <c r="B76" s="81" t="s">
         <v>41</v>
       </c>
       <c r="C76" s="46">
         <v>10.688000000000001</v>
       </c>
-      <c r="D76" s="87">
+      <c r="D76" s="83">
         <v>10.702</v>
       </c>
       <c r="E76" s="35"/>
@@ -6427,12 +6428,12 @@
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B77" s="86"/>
+      <c r="B77" s="82"/>
       <c r="C77" s="45">
         <f>(D76-C76)/H76</f>
         <v>4.6357615894037571E-3</v>
       </c>
-      <c r="D77" s="88"/>
+      <c r="D77" s="84"/>
       <c r="E77" s="39"/>
       <c r="F77" s="50">
         <f>(D76-F76)/I76</f>
@@ -6442,13 +6443,13 @@
       <c r="I77" s="38"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B78" s="85" t="s">
+      <c r="B78" s="81" t="s">
         <v>2</v>
       </c>
       <c r="C78" s="46">
         <v>10.609</v>
       </c>
-      <c r="D78" s="87">
+      <c r="D78" s="83">
         <v>10.669</v>
       </c>
       <c r="E78" s="35"/>
@@ -6463,12 +6464,12 @@
       </c>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B79" s="86"/>
+      <c r="B79" s="82"/>
       <c r="C79" s="45">
         <f>(D78-C78)/H78</f>
         <v>1.857585139318901E-2</v>
       </c>
-      <c r="D79" s="88"/>
+      <c r="D79" s="84"/>
       <c r="E79" s="39"/>
       <c r="F79" s="50">
         <f>(D78-F78)/I78</f>
@@ -6478,13 +6479,13 @@
       <c r="I79" s="38"/>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B80" s="85" t="s">
+      <c r="B80" s="81" t="s">
         <v>42</v>
       </c>
       <c r="C80" s="46">
         <v>10.553000000000001</v>
       </c>
-      <c r="D80" s="87">
+      <c r="D80" s="83">
         <v>10.643000000000001</v>
       </c>
       <c r="E80" s="35"/>
@@ -6499,12 +6500,12 @@
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B81" s="86"/>
+      <c r="B81" s="82"/>
       <c r="C81" s="45">
         <f>(D80-C80)/H80</f>
         <v>2.8571428571428525E-2</v>
       </c>
-      <c r="D81" s="88"/>
+      <c r="D81" s="84"/>
       <c r="E81" s="39"/>
       <c r="F81" s="50">
         <f>(D80-F80)/I80</f>
@@ -6515,16 +6516,60 @@
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="D80:D81"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="B76:B77"/>
-    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="D25:D26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="D51:D52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="D55:D56"/>
     <mergeCell ref="C71:F71"/>
     <mergeCell ref="B57:B58"/>
     <mergeCell ref="D57:D58"/>
@@ -6537,60 +6582,16 @@
     <mergeCell ref="B65:B66"/>
     <mergeCell ref="D65:D66"/>
     <mergeCell ref="C69:F69"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="D51:D52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="D25:D26"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="B76:B77"/>
+    <mergeCell ref="D76:D77"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -6615,12 +6616,12 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B2" s="30"/>
-      <c r="C2" s="80" t="s">
+      <c r="C2" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="81"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="89"/>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.4">
@@ -6650,23 +6651,23 @@
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B4" s="30"/>
-      <c r="C4" s="82" t="s">
+      <c r="C4" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="84"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="87"/>
       <c r="G4" s="1"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B5" s="85" t="s">
+      <c r="B5" s="81" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="44">
         <v>9.7159999999999993</v>
       </c>
-      <c r="D5" s="87">
-        <v>9.81</v>
+      <c r="D5" s="83">
+        <v>9.8529999999999998</v>
       </c>
       <c r="E5" s="35"/>
       <c r="F5" s="49">
@@ -6674,37 +6675,37 @@
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="38">
-        <v>2.99</v>
+        <v>4.25</v>
       </c>
       <c r="I5" s="38">
-        <v>5.38</v>
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="6" spans="2:10" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B6" s="86"/>
+      <c r="B6" s="82"/>
       <c r="C6" s="45">
         <f>(D5-C5)/H5</f>
-        <v>3.1438127090301402E-2</v>
-      </c>
-      <c r="D6" s="88"/>
+        <v>3.2235294117647167E-2</v>
+      </c>
+      <c r="D6" s="84"/>
       <c r="E6" s="39"/>
       <c r="F6" s="50">
         <f>(D5-F5)/I5</f>
-        <v>2.3977695167286494E-2</v>
+        <v>4.195121951219527E-2</v>
       </c>
       <c r="G6" s="40"/>
       <c r="H6" s="41"/>
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B7" s="85" t="s">
+      <c r="B7" s="81" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="46">
         <v>9.8249999999999993</v>
       </c>
-      <c r="D7" s="87">
-        <v>9.8510000000000009</v>
+      <c r="D7" s="83">
+        <v>9.8819999999999997</v>
       </c>
       <c r="E7" s="35"/>
       <c r="F7" s="51">
@@ -6712,37 +6713,37 @@
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="38">
-        <v>2.97</v>
+        <v>4.24</v>
       </c>
       <c r="I7" s="38">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B8" s="86"/>
+      <c r="B8" s="82"/>
       <c r="C8" s="45">
         <f>(D7-C7)/H7</f>
-        <v>8.7542087542092847E-3</v>
-      </c>
-      <c r="D8" s="88"/>
+        <v>1.3443396226415183E-2</v>
+      </c>
+      <c r="D8" s="84"/>
       <c r="E8" s="39"/>
       <c r="F8" s="50">
         <f>(D7-F7)/I7</f>
-        <v>2.0000000000000098E-2</v>
+        <v>3.3656174334140275E-2</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="38"/>
       <c r="I8" s="38"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="81" t="s">
         <v>2</v>
       </c>
       <c r="C9" s="46">
         <v>9.8689999999999998</v>
       </c>
-      <c r="D9" s="87">
-        <v>9.8919999999999995</v>
+      <c r="D9" s="83">
+        <v>9.9109999999999996</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="51">
@@ -6750,37 +6751,37 @@
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="38">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="I9" s="38">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B10" s="86"/>
+      <c r="B10" s="82"/>
       <c r="C10" s="45">
         <f>(D9-C9)/H9</f>
-        <v>7.796610169491419E-3</v>
-      </c>
-      <c r="D10" s="88"/>
+        <v>9.9999999999999551E-3</v>
+      </c>
+      <c r="D10" s="84"/>
       <c r="E10" s="39"/>
       <c r="F10" s="50">
         <f>(D9-F9)/I9</f>
-        <v>1.0555555555555297E-2</v>
+        <v>1.8401937046004537E-2</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="38"/>
       <c r="I10" s="38"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="81" t="s">
         <v>3</v>
       </c>
       <c r="C11" s="46">
         <v>9.8829999999999991</v>
       </c>
-      <c r="D11" s="87">
-        <v>9.9329999999999998</v>
+      <c r="D11" s="83">
+        <v>9.94</v>
       </c>
       <c r="E11" s="35"/>
       <c r="F11" s="51">
@@ -6788,83 +6789,78 @@
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="38">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="I11" s="38">
-        <v>5.25</v>
+        <v>3.98</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B12" s="86"/>
+      <c r="B12" s="82"/>
       <c r="C12" s="45">
         <f>(D11-C11)/H11</f>
-        <v>1.7123287671233122E-2</v>
-      </c>
-      <c r="D12" s="88"/>
+        <v>1.3571428571428663E-2</v>
+      </c>
+      <c r="D12" s="84"/>
       <c r="E12" s="39"/>
       <c r="F12" s="50">
         <f>(D11-F11)/I11</f>
-        <v>1.0476190476190422E-2</v>
+        <v>1.5577889447236027E-2</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="38"/>
       <c r="I12" s="38"/>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B13" s="89" t="s">
+      <c r="B13" s="90" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="46">
         <v>9.8719999999999999</v>
       </c>
-      <c r="D13" s="87">
-        <v>9.9559999999999995</v>
-      </c>
-      <c r="E13" s="36">
+      <c r="D13" s="92">
         <v>9.9550000000000001</v>
       </c>
+      <c r="E13" s="35"/>
       <c r="F13" s="51">
         <v>9.8729999999999993</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="38">
-        <v>2.93</v>
+        <v>4.18</v>
       </c>
       <c r="I13" s="38">
-        <v>5.13</v>
+        <v>3.9</v>
       </c>
       <c r="J13">
         <v>1.4</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B14" s="90"/>
+      <c r="B14" s="91"/>
       <c r="C14" s="45">
         <f>(D13-C13)/H13</f>
-        <v>2.8668941979522057E-2</v>
-      </c>
-      <c r="D14" s="88"/>
-      <c r="E14" s="39">
-        <f>D13-(F14*J13)</f>
-        <v>9.9333489278752438</v>
-      </c>
+        <v>1.9856459330143586E-2</v>
+      </c>
+      <c r="D14" s="93"/>
+      <c r="E14" s="39"/>
       <c r="F14" s="50">
         <f>(D13-F13)/I13</f>
-        <v>1.6179337231968849E-2</v>
+        <v>2.1025641025641216E-2</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="38"/>
       <c r="I14" s="38"/>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B15" s="85" t="s">
+      <c r="B15" s="81" t="s">
         <v>5</v>
       </c>
       <c r="C15" s="46">
         <v>9.9030000000000005</v>
       </c>
-      <c r="D15" s="87">
-        <v>9.9740000000000002</v>
+      <c r="D15" s="83">
+        <v>9.9730000000000008</v>
       </c>
       <c r="E15" s="35"/>
       <c r="F15" s="51">
@@ -6872,37 +6868,37 @@
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="38">
-        <v>3</v>
+        <v>4.26</v>
       </c>
       <c r="I15" s="38">
-        <v>4.97</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B16" s="86"/>
+      <c r="B16" s="82"/>
       <c r="C16" s="45">
         <f>(D15-C15)/H15</f>
-        <v>2.3666666666666576E-2</v>
-      </c>
-      <c r="D16" s="88"/>
+        <v>1.6431924882629175E-2</v>
+      </c>
+      <c r="D16" s="84"/>
       <c r="E16" s="39"/>
       <c r="F16" s="50">
         <f>(D15-F15)/I15</f>
-        <v>1.8108651911469143E-2</v>
+        <v>2.4054054054054645E-2</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="38"/>
       <c r="I16" s="38"/>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B17" s="85" t="s">
+      <c r="B17" s="81" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="46">
         <v>9.9260000000000002</v>
       </c>
-      <c r="D17" s="87">
-        <v>10.015000000000001</v>
+      <c r="D17" s="83">
+        <v>10.013999999999999</v>
       </c>
       <c r="E17" s="35"/>
       <c r="F17" s="51">
@@ -6910,36 +6906,36 @@
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="38">
-        <v>3.05</v>
+        <v>3.72</v>
       </c>
       <c r="I17" s="38">
-        <v>4.46</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B18" s="86"/>
+      <c r="B18" s="82"/>
       <c r="C18" s="45">
         <f>(D17-C17)/H17</f>
-        <v>2.9180327868852596E-2</v>
-      </c>
-      <c r="D18" s="88"/>
+        <v>2.3655913978494404E-2</v>
+      </c>
+      <c r="D18" s="84"/>
       <c r="E18" s="39"/>
       <c r="F18" s="50">
         <f>(D17-F17)/I17</f>
-        <v>2.309417040358739E-2</v>
+        <v>2.6842105263157511E-2</v>
       </c>
       <c r="G18" s="2"/>
       <c r="H18" s="38"/>
       <c r="I18" s="38"/>
     </row>
     <row r="19" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B19" s="85" t="s">
+      <c r="B19" s="81" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="46">
         <v>10.038</v>
       </c>
-      <c r="D19" s="87">
+      <c r="D19" s="83">
         <v>10.055</v>
       </c>
       <c r="E19" s="35"/>
@@ -6955,12 +6951,12 @@
       </c>
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B20" s="86"/>
+      <c r="B20" s="82"/>
       <c r="C20" s="45">
         <f>(D19-C19)/H19</f>
         <v>5.3124999999998312E-3</v>
       </c>
-      <c r="D20" s="88"/>
+      <c r="D20" s="84"/>
       <c r="E20" s="39"/>
       <c r="F20" s="50">
         <f>(D19-F19)/I19</f>
@@ -6971,13 +6967,13 @@
       <c r="I20" s="38"/>
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B21" s="89" t="s">
+      <c r="B21" s="90" t="s">
         <v>35</v>
       </c>
       <c r="C21" s="46">
         <v>10.052</v>
       </c>
-      <c r="D21" s="87">
+      <c r="D21" s="83">
         <v>10.055</v>
       </c>
       <c r="E21" s="36">
@@ -6998,12 +6994,12 @@
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B22" s="90"/>
+      <c r="B22" s="91"/>
       <c r="C22" s="45">
         <f>(D21-C21)/H21</f>
         <v>9.5541401273888972E-4</v>
       </c>
-      <c r="D22" s="88"/>
+      <c r="D22" s="84"/>
       <c r="E22" s="39">
         <f>D21-(F22*J21)</f>
         <v>10.02967018469657</v>
@@ -7017,13 +7013,13 @@
       <c r="I22" s="38"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="81" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="46">
         <v>10.002000000000001</v>
       </c>
-      <c r="D23" s="87">
+      <c r="D23" s="83">
         <v>10.055</v>
       </c>
       <c r="E23" s="35"/>
@@ -7039,12 +7035,12 @@
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B24" s="86"/>
+      <c r="B24" s="82"/>
       <c r="C24" s="45">
         <f>(D23-C23)/H23</f>
         <v>1.6666666666666368E-2</v>
       </c>
-      <c r="D24" s="88"/>
+      <c r="D24" s="84"/>
       <c r="E24" s="39"/>
       <c r="F24" s="50">
         <f>(D23-F23)/I23</f>
@@ -7055,13 +7051,13 @@
       <c r="I24" s="38"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B25" s="85" t="s">
+      <c r="B25" s="81" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="46">
         <v>9.9960000000000004</v>
       </c>
-      <c r="D25" s="87">
+      <c r="D25" s="83">
         <v>10.055</v>
       </c>
       <c r="E25" s="35"/>
@@ -7077,12 +7073,12 @@
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B26" s="86"/>
+      <c r="B26" s="82"/>
       <c r="C26" s="45">
         <f>(D25-C25)/H25</f>
         <v>1.8437499999999774E-2</v>
       </c>
-      <c r="D26" s="88"/>
+      <c r="D26" s="84"/>
       <c r="E26" s="39"/>
       <c r="F26" s="50">
         <f>(D25-F25)/I25</f>
@@ -7093,13 +7089,13 @@
       <c r="I26" s="38"/>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B27" s="85" t="s">
+      <c r="B27" s="81" t="s">
         <v>31</v>
       </c>
       <c r="C27" s="46">
         <v>10.002000000000001</v>
       </c>
-      <c r="D27" s="87">
+      <c r="D27" s="83">
         <v>10.076000000000001</v>
       </c>
       <c r="E27" s="35"/>
@@ -7115,12 +7111,12 @@
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B28" s="86"/>
+      <c r="B28" s="82"/>
       <c r="C28" s="45">
         <f>(D27-C27)/H27</f>
         <v>2.3197492163009356E-2</v>
       </c>
-      <c r="D28" s="88"/>
+      <c r="D28" s="84"/>
       <c r="E28" s="39"/>
       <c r="F28" s="50">
         <f>(D27-F27)/I27</f>
@@ -7131,13 +7127,13 @@
       <c r="I28" s="38"/>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B29" s="85" t="s">
+      <c r="B29" s="81" t="s">
         <v>11</v>
       </c>
       <c r="C29" s="46">
         <v>10.019</v>
       </c>
-      <c r="D29" s="87">
+      <c r="D29" s="83">
         <v>10.097</v>
       </c>
       <c r="E29" s="35"/>
@@ -7153,12 +7149,12 @@
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B30" s="86"/>
+      <c r="B30" s="82"/>
       <c r="C30" s="45">
         <f>(D29-C29)/H29</f>
         <v>2.4374999999999813E-2</v>
       </c>
-      <c r="D30" s="88"/>
+      <c r="D30" s="84"/>
       <c r="E30" s="39"/>
       <c r="F30" s="50">
         <f>(D29-F29)/I29</f>
@@ -7169,13 +7165,13 @@
       <c r="I30" s="38"/>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B31" s="85" t="s">
+      <c r="B31" s="81" t="s">
         <v>12</v>
       </c>
       <c r="C31" s="46">
         <v>10.037000000000001</v>
       </c>
-      <c r="D31" s="87">
+      <c r="D31" s="83">
         <v>10.118</v>
       </c>
       <c r="E31" s="35"/>
@@ -7191,12 +7187,12 @@
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B32" s="86"/>
+      <c r="B32" s="82"/>
       <c r="C32" s="45">
         <f>(D31-C31)/H31</f>
         <v>2.5471698113207392E-2</v>
       </c>
-      <c r="D32" s="88"/>
+      <c r="D32" s="84"/>
       <c r="E32" s="39"/>
       <c r="F32" s="50">
         <f>(D31-F31)/I31</f>
@@ -7207,13 +7203,13 @@
       <c r="I32" s="38"/>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B33" s="85" t="s">
+      <c r="B33" s="81" t="s">
         <v>13</v>
       </c>
       <c r="C33" s="46">
         <v>10.103</v>
       </c>
-      <c r="D33" s="87">
+      <c r="D33" s="83">
         <v>10.138999999999999</v>
       </c>
       <c r="E33" s="35"/>
@@ -7229,12 +7225,12 @@
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B34" s="86"/>
+      <c r="B34" s="82"/>
       <c r="C34" s="45">
         <f>(D33-C33)/H33</f>
         <v>1.1249999999999871E-2</v>
       </c>
-      <c r="D34" s="88"/>
+      <c r="D34" s="84"/>
       <c r="E34" s="39"/>
       <c r="F34" s="50">
         <f>(D33-F33)/I33</f>
@@ -7245,13 +7241,13 @@
       <c r="I34" s="38"/>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B35" s="89" t="s">
+      <c r="B35" s="90" t="s">
         <v>36</v>
       </c>
       <c r="C35" s="46">
         <v>10.132</v>
       </c>
-      <c r="D35" s="87">
+      <c r="D35" s="83">
         <v>10.15</v>
       </c>
       <c r="E35" s="36">
@@ -7272,12 +7268,12 @@
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B36" s="90"/>
+      <c r="B36" s="91"/>
       <c r="C36" s="45">
         <f>(D35-C35)/H35</f>
         <v>5.6603773584907799E-3</v>
       </c>
-      <c r="D36" s="88"/>
+      <c r="D36" s="84"/>
       <c r="E36" s="39">
         <f>D35-(F36*J35)</f>
         <v>10.130000000000001</v>
@@ -7291,13 +7287,13 @@
       <c r="I36" s="38"/>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B37" s="85" t="s">
+      <c r="B37" s="81" t="s">
         <v>14</v>
       </c>
       <c r="C37" s="46">
         <v>10.108000000000001</v>
       </c>
-      <c r="D37" s="87">
+      <c r="D37" s="83">
         <v>10.166</v>
       </c>
       <c r="E37" s="35"/>
@@ -7313,12 +7309,12 @@
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B38" s="86"/>
+      <c r="B38" s="82"/>
       <c r="C38" s="45">
         <f>(D37-C37)/H37</f>
         <v>1.8238993710691768E-2</v>
       </c>
-      <c r="D38" s="88"/>
+      <c r="D38" s="84"/>
       <c r="E38" s="39"/>
       <c r="F38" s="50">
         <f>(D37-F37)/I37</f>
@@ -7329,13 +7325,13 @@
       <c r="I38" s="38"/>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B39" s="85" t="s">
+      <c r="B39" s="81" t="s">
         <v>15</v>
       </c>
       <c r="C39" s="46">
         <v>10.14</v>
       </c>
-      <c r="D39" s="87">
+      <c r="D39" s="83">
         <v>10.193</v>
       </c>
       <c r="E39" s="35"/>
@@ -7351,12 +7347,12 @@
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B40" s="86"/>
+      <c r="B40" s="82"/>
       <c r="C40" s="45">
         <f>(D39-C39)/H39</f>
         <v>1.6666666666666368E-2</v>
       </c>
-      <c r="D40" s="88"/>
+      <c r="D40" s="84"/>
       <c r="E40" s="39"/>
       <c r="F40" s="50">
         <f>(D39-F39)/I39</f>
@@ -7367,13 +7363,13 @@
       <c r="I40" s="38"/>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B41" s="85" t="s">
+      <c r="B41" s="81" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="46">
         <v>10.196</v>
       </c>
-      <c r="D41" s="87">
+      <c r="D41" s="83">
         <v>10.25</v>
       </c>
       <c r="E41" s="35"/>
@@ -7389,12 +7385,12 @@
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B42" s="86"/>
+      <c r="B42" s="82"/>
       <c r="C42" s="45">
         <f>(D41-C41)/H41</f>
         <v>1.6981132075471781E-2</v>
       </c>
-      <c r="D42" s="88"/>
+      <c r="D42" s="84"/>
       <c r="E42" s="39"/>
       <c r="F42" s="50">
         <f>(D41-F41)/I41</f>
@@ -7405,13 +7401,13 @@
       <c r="I42" s="38"/>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B43" s="85" t="s">
+      <c r="B43" s="81" t="s">
         <v>17</v>
       </c>
       <c r="C43" s="46">
         <v>10.236000000000001</v>
       </c>
-      <c r="D43" s="87">
+      <c r="D43" s="83">
         <v>10.307</v>
       </c>
       <c r="E43" s="35"/>
@@ -7427,12 +7423,12 @@
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B44" s="86"/>
+      <c r="B44" s="82"/>
       <c r="C44" s="45">
         <f>(D43-C43)/H43</f>
         <v>2.239747634069392E-2</v>
       </c>
-      <c r="D44" s="88"/>
+      <c r="D44" s="84"/>
       <c r="E44" s="39"/>
       <c r="F44" s="50">
         <f>(D43-F43)/I43</f>
@@ -7443,13 +7439,13 @@
       <c r="I44" s="38"/>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B45" s="85" t="s">
+      <c r="B45" s="81" t="s">
         <v>18</v>
       </c>
       <c r="C45" s="46">
         <v>10.359</v>
       </c>
-      <c r="D45" s="87">
+      <c r="D45" s="83">
         <v>10.364000000000001</v>
       </c>
       <c r="E45" s="35"/>
@@ -7465,12 +7461,12 @@
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B46" s="86"/>
+      <c r="B46" s="82"/>
       <c r="C46" s="45">
         <f>(D45-C45)/H45</f>
         <v>1.5625000000002442E-3</v>
       </c>
-      <c r="D46" s="88"/>
+      <c r="D46" s="84"/>
       <c r="E46" s="39"/>
       <c r="F46" s="50">
         <f>(D45-F45)/I45</f>
@@ -7481,13 +7477,13 @@
       <c r="I46" s="38"/>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B47" s="89" t="s">
+      <c r="B47" s="90" t="s">
         <v>37</v>
       </c>
       <c r="C47" s="46">
         <v>10.372</v>
       </c>
-      <c r="D47" s="87">
+      <c r="D47" s="83">
         <v>10.379</v>
       </c>
       <c r="E47" s="36">
@@ -7508,12 +7504,12 @@
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B48" s="90"/>
+      <c r="B48" s="91"/>
       <c r="C48" s="45">
         <f>(D47-C47)/H47</f>
         <v>2.2012578616351173E-3</v>
       </c>
-      <c r="D48" s="88"/>
+      <c r="D48" s="84"/>
       <c r="E48" s="39">
         <f>D47-(F48*J47)</f>
         <v>10.380749999999999</v>
@@ -7527,13 +7523,13 @@
       <c r="I48" s="38"/>
     </row>
     <row r="49" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B49" s="85" t="s">
+      <c r="B49" s="81" t="s">
         <v>19</v>
       </c>
       <c r="C49" s="46">
         <v>10.365</v>
       </c>
-      <c r="D49" s="87">
+      <c r="D49" s="83">
         <v>10.426</v>
       </c>
       <c r="E49" s="35"/>
@@ -7549,12 +7545,12 @@
       </c>
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B50" s="86"/>
+      <c r="B50" s="82"/>
       <c r="C50" s="45">
         <f>(D49-C49)/H49</f>
         <v>1.894409937888197E-2</v>
       </c>
-      <c r="D50" s="88"/>
+      <c r="D50" s="84"/>
       <c r="E50" s="39"/>
       <c r="F50" s="50">
         <f>(D49-F49)/I49</f>
@@ -7565,13 +7561,13 @@
       <c r="I50" s="38"/>
     </row>
     <row r="51" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B51" s="85" t="s">
+      <c r="B51" s="81" t="s">
         <v>20</v>
       </c>
       <c r="C51" s="46">
         <v>10.404</v>
       </c>
-      <c r="D51" s="87">
+      <c r="D51" s="83">
         <v>10.488</v>
       </c>
       <c r="E51" s="35"/>
@@ -7587,12 +7583,12 @@
       </c>
     </row>
     <row r="52" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B52" s="86"/>
+      <c r="B52" s="82"/>
       <c r="C52" s="45">
         <f>(D51-C51)/H51</f>
         <v>2.6415094339622525E-2</v>
       </c>
-      <c r="D52" s="88"/>
+      <c r="D52" s="84"/>
       <c r="E52" s="39"/>
       <c r="F52" s="50">
         <f>(D51-F51)/I51</f>
@@ -7603,13 +7599,13 @@
       <c r="I52" s="38"/>
     </row>
     <row r="53" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B53" s="85" t="s">
+      <c r="B53" s="81" t="s">
         <v>21</v>
       </c>
       <c r="C53" s="46">
         <v>10.478</v>
       </c>
-      <c r="D53" s="87">
+      <c r="D53" s="83">
         <v>10.55</v>
       </c>
       <c r="E53" s="35"/>
@@ -7625,12 +7621,12 @@
       </c>
     </row>
     <row r="54" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B54" s="86"/>
+      <c r="B54" s="82"/>
       <c r="C54" s="45">
         <f>(D53-C53)/H53</f>
         <v>2.2500000000000298E-2</v>
       </c>
-      <c r="D54" s="88"/>
+      <c r="D54" s="84"/>
       <c r="E54" s="39"/>
       <c r="F54" s="50">
         <f>(D53-F53)/I53</f>
@@ -7641,13 +7637,13 @@
       <c r="I54" s="38"/>
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B55" s="89" t="s">
+      <c r="B55" s="90" t="s">
         <v>38</v>
       </c>
       <c r="C55" s="46">
         <v>10.510999999999999</v>
       </c>
-      <c r="D55" s="87">
+      <c r="D55" s="83">
         <v>10.58</v>
       </c>
       <c r="E55" s="36">
@@ -7668,12 +7664,12 @@
       </c>
     </row>
     <row r="56" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B56" s="90"/>
+      <c r="B56" s="91"/>
       <c r="C56" s="45">
         <f>(D55-C55)/H55</f>
         <v>2.1698113207547432E-2</v>
       </c>
-      <c r="D56" s="88"/>
+      <c r="D56" s="84"/>
       <c r="E56" s="39">
         <f>D55-(F56*J55)</f>
         <v>10.56490625</v>
@@ -7687,13 +7683,13 @@
       <c r="I56" s="38"/>
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B57" s="85" t="s">
+      <c r="B57" s="81" t="s">
         <v>22</v>
       </c>
       <c r="C57" s="46">
         <v>10.548999999999999</v>
       </c>
-      <c r="D57" s="87">
+      <c r="D57" s="83">
         <v>10.612</v>
       </c>
       <c r="E57" s="35"/>
@@ -7709,12 +7705,12 @@
       </c>
     </row>
     <row r="58" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B58" s="86"/>
+      <c r="B58" s="82"/>
       <c r="C58" s="45">
         <f>(D57-C57)/H57</f>
         <v>1.9687500000000191E-2</v>
       </c>
-      <c r="D58" s="88"/>
+      <c r="D58" s="84"/>
       <c r="E58" s="39"/>
       <c r="F58" s="50">
         <f>(D57-F57)/I57</f>
@@ -7725,13 +7721,13 @@
       <c r="I58" s="38"/>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B59" s="85" t="s">
+      <c r="B59" s="81" t="s">
         <v>23</v>
       </c>
       <c r="C59" s="46">
         <v>10.606999999999999</v>
       </c>
-      <c r="D59" s="87">
+      <c r="D59" s="83">
         <v>10.673999999999999</v>
       </c>
       <c r="E59" s="35"/>
@@ -7747,12 +7743,12 @@
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B60" s="86"/>
+      <c r="B60" s="82"/>
       <c r="C60" s="45">
         <f>(D59-C59)/H59</f>
         <v>2.0937500000000053E-2</v>
       </c>
-      <c r="D60" s="88"/>
+      <c r="D60" s="84"/>
       <c r="E60" s="39"/>
       <c r="F60" s="50">
         <f>(D59-F59)/I59</f>
@@ -7763,13 +7759,13 @@
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B61" s="85" t="s">
+      <c r="B61" s="81" t="s">
         <v>39</v>
       </c>
       <c r="C61" s="46">
         <v>10.629</v>
       </c>
-      <c r="D61" s="87">
+      <c r="D61" s="83">
         <v>10.686</v>
       </c>
       <c r="E61" s="35"/>
@@ -7785,12 +7781,12 @@
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B62" s="86"/>
+      <c r="B62" s="82"/>
       <c r="C62" s="45">
         <f>(D61-C61)/H61</f>
         <v>1.786833855799385E-2</v>
       </c>
-      <c r="D62" s="88"/>
+      <c r="D62" s="84"/>
       <c r="E62" s="39"/>
       <c r="F62" s="50">
         <f>(D61-F61)/I61</f>
@@ -7801,13 +7797,13 @@
       <c r="I62" s="38"/>
     </row>
     <row r="63" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B63" s="85" t="s">
+      <c r="B63" s="81" t="s">
         <v>24</v>
       </c>
       <c r="C63" s="46">
         <v>10.673999999999999</v>
       </c>
-      <c r="D63" s="87">
+      <c r="D63" s="83">
         <v>10.734999999999999</v>
       </c>
       <c r="E63" s="35"/>
@@ -7823,12 +7819,12 @@
       </c>
     </row>
     <row r="64" spans="2:10" x14ac:dyDescent="0.4">
-      <c r="B64" s="86"/>
+      <c r="B64" s="82"/>
       <c r="C64" s="45">
         <f>(D63-C63)/H63</f>
         <v>1.9677419354838691E-2</v>
       </c>
-      <c r="D64" s="88"/>
+      <c r="D64" s="84"/>
       <c r="E64" s="39"/>
       <c r="F64" s="50">
         <f>(D63-F63)/I63</f>
@@ -7839,13 +7835,13 @@
       <c r="I64" s="38"/>
     </row>
     <row r="65" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B65" s="85" t="s">
+      <c r="B65" s="81" t="s">
         <v>40</v>
       </c>
       <c r="C65" s="46">
         <v>10.631</v>
       </c>
-      <c r="D65" s="87">
+      <c r="D65" s="83">
         <v>10.721</v>
       </c>
       <c r="E65" s="35"/>
@@ -7861,12 +7857,12 @@
       </c>
     </row>
     <row r="66" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B66" s="86"/>
+      <c r="B66" s="82"/>
       <c r="C66" s="45">
         <f>(D65-C65)/H65</f>
         <v>1.7999999999999971E-2</v>
       </c>
-      <c r="D66" s="88"/>
+      <c r="D66" s="84"/>
       <c r="E66" s="39"/>
       <c r="F66" s="50">
         <f>(D65-F65)/I65</f>
@@ -7886,12 +7882,12 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B69" s="30"/>
-      <c r="C69" s="80" t="s">
+      <c r="C69" s="88" t="s">
         <v>30</v>
       </c>
-      <c r="D69" s="80"/>
-      <c r="E69" s="80"/>
-      <c r="F69" s="81"/>
+      <c r="D69" s="88"/>
+      <c r="E69" s="88"/>
+      <c r="F69" s="89"/>
       <c r="H69" s="38"/>
       <c r="I69" s="38"/>
     </row>
@@ -7916,23 +7912,23 @@
     </row>
     <row r="71" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B71" s="30"/>
-      <c r="C71" s="82" t="s">
+      <c r="C71" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="D71" s="83"/>
-      <c r="E71" s="83"/>
-      <c r="F71" s="84"/>
+      <c r="D71" s="86"/>
+      <c r="E71" s="86"/>
+      <c r="F71" s="87"/>
       <c r="H71" s="38"/>
       <c r="I71" s="38"/>
     </row>
     <row r="72" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B72" s="85" t="s">
+      <c r="B72" s="81" t="s">
         <v>0</v>
       </c>
       <c r="C72" s="44">
         <v>10.64</v>
       </c>
-      <c r="D72" s="87">
+      <c r="D72" s="83">
         <v>10.669</v>
       </c>
       <c r="E72" s="35"/>
@@ -7947,12 +7943,12 @@
       </c>
     </row>
     <row r="73" spans="2:9" s="8" customFormat="1" x14ac:dyDescent="0.4">
-      <c r="B73" s="86"/>
+      <c r="B73" s="82"/>
       <c r="C73" s="45">
         <f>(D72-C72)/H72</f>
         <v>8.8957055214723673E-3</v>
       </c>
-      <c r="D73" s="88"/>
+      <c r="D73" s="84"/>
       <c r="E73" s="39"/>
       <c r="F73" s="50">
         <f>(D72-F72)/I72</f>
@@ -7962,13 +7958,13 @@
       <c r="I73" s="42"/>
     </row>
     <row r="74" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B74" s="85" t="s">
+      <c r="B74" s="81" t="s">
         <v>1</v>
       </c>
       <c r="C74" s="46">
         <v>10.675000000000001</v>
       </c>
-      <c r="D74" s="87">
+      <c r="D74" s="83">
         <v>10.691000000000001</v>
       </c>
       <c r="E74" s="35"/>
@@ -7983,12 +7979,12 @@
       </c>
     </row>
     <row r="75" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B75" s="86"/>
+      <c r="B75" s="82"/>
       <c r="C75" s="45">
         <f>(D74-C74)/H74</f>
         <v>5.1612903225806495E-3</v>
       </c>
-      <c r="D75" s="88"/>
+      <c r="D75" s="84"/>
       <c r="E75" s="39"/>
       <c r="F75" s="50">
         <f>(D74-F74)/I74</f>
@@ -7998,13 +7994,13 @@
       <c r="I75" s="38"/>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B76" s="85" t="s">
+      <c r="B76" s="81" t="s">
         <v>41</v>
       </c>
       <c r="C76" s="46">
         <v>10.688000000000001</v>
       </c>
-      <c r="D76" s="87">
+      <c r="D76" s="83">
         <v>10.702</v>
       </c>
       <c r="E76" s="35"/>
@@ -8019,12 +8015,12 @@
       </c>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B77" s="86"/>
+      <c r="B77" s="82"/>
       <c r="C77" s="45">
         <f>(D76-C76)/H76</f>
         <v>4.6357615894037571E-3</v>
       </c>
-      <c r="D77" s="88"/>
+      <c r="D77" s="84"/>
       <c r="E77" s="39"/>
       <c r="F77" s="50">
         <f>(D76-F76)/I76</f>
@@ -8034,13 +8030,13 @@
       <c r="I77" s="38"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B78" s="85" t="s">
+      <c r="B78" s="81" t="s">
         <v>2</v>
       </c>
       <c r="C78" s="46">
         <v>10.609</v>
       </c>
-      <c r="D78" s="87">
+      <c r="D78" s="83">
         <v>10.678000000000001</v>
       </c>
       <c r="E78" s="35"/>
@@ -8055,12 +8051,12 @@
       </c>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B79" s="86"/>
+      <c r="B79" s="82"/>
       <c r="C79" s="45">
         <f>(D78-C78)/H78</f>
         <v>2.1362229102167441E-2</v>
       </c>
-      <c r="D79" s="88"/>
+      <c r="D79" s="84"/>
       <c r="E79" s="39"/>
       <c r="F79" s="50">
         <f>(D78-F78)/I78</f>
@@ -8070,13 +8066,13 @@
       <c r="I79" s="38"/>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B80" s="85" t="s">
+      <c r="B80" s="81" t="s">
         <v>42</v>
       </c>
       <c r="C80" s="46">
         <v>10.553000000000001</v>
       </c>
-      <c r="D80" s="87">
+      <c r="D80" s="83">
         <v>10.643000000000001</v>
       </c>
       <c r="E80" s="35"/>
@@ -8091,12 +8087,12 @@
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B81" s="86"/>
+      <c r="B81" s="82"/>
       <c r="C81" s="45">
         <f>(D80-C80)/H80</f>
         <v>2.8571428571428525E-2</v>
       </c>
-      <c r="D81" s="88"/>
+      <c r="D81" s="84"/>
       <c r="E81" s="39"/>
       <c r="F81" s="50">
         <f>(D80-F80)/I80</f>
@@ -8107,30 +8103,42 @@
     </row>
   </sheetData>
   <mergeCells count="76">
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="D45:D46"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="D49:D50"/>
-    <mergeCell ref="D74:D75"/>
-    <mergeCell ref="D53:D54"/>
-    <mergeCell ref="D55:D56"/>
-    <mergeCell ref="D57:D58"/>
-    <mergeCell ref="D59:D60"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="D63:D64"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D35:D36"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D39:D40"/>
-    <mergeCell ref="D41:D42"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="B80:B81"/>
-    <mergeCell ref="C71:F71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="D76:D77"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="C69:F69"/>
+    <mergeCell ref="D65:D66"/>
+    <mergeCell ref="B59:B60"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B57:B58"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="D27:D28"/>
@@ -8147,42 +8155,30 @@
     <mergeCell ref="D51:D52"/>
     <mergeCell ref="D29:D30"/>
     <mergeCell ref="D31:D32"/>
-    <mergeCell ref="B59:B60"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="B41:B42"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="C69:F69"/>
-    <mergeCell ref="D65:D66"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="B80:B81"/>
+    <mergeCell ref="C71:F71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="D76:D77"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="D80:D81"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D39:D40"/>
+    <mergeCell ref="D41:D42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="D45:D46"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="D49:D50"/>
+    <mergeCell ref="D74:D75"/>
+    <mergeCell ref="D53:D54"/>
+    <mergeCell ref="D55:D56"/>
+    <mergeCell ref="D57:D58"/>
+    <mergeCell ref="D59:D60"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="D63:D64"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -8247,7 +8243,7 @@
       </c>
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="95" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="60" t="s">
@@ -8258,37 +8254,35 @@
       </c>
       <c r="E2" s="61"/>
       <c r="F2" s="61">
-        <v>9.7609999999999992</v>
+        <v>9.782</v>
       </c>
       <c r="G2" s="61">
-        <v>9.81</v>
+        <v>9.8529999999999998</v>
       </c>
       <c r="H2" s="61">
-        <v>9.827</v>
-      </c>
-      <c r="I2" s="61">
-        <v>9.7420000000000009</v>
-      </c>
+        <v>9.782</v>
+      </c>
+      <c r="I2" s="61"/>
       <c r="J2" s="61"/>
       <c r="K2" s="61"/>
       <c r="L2" s="61">
         <v>9.6809999999999992</v>
       </c>
       <c r="N2" s="38">
-        <v>2.99</v>
+        <v>4.25</v>
       </c>
       <c r="O2" s="38">
-        <v>5.38</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="Q2" s="32">
-        <v>3.1E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="R2" s="32">
-        <v>2.4E-2</v>
+        <v>4.2000000000000003E-2</v>
       </c>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B3" s="92"/>
+      <c r="B3" s="95"/>
       <c r="C3" s="65" t="s">
         <v>52</v>
       </c>
@@ -8296,18 +8290,12 @@
         <v>9.7159999999999993</v>
       </c>
       <c r="E3" s="67"/>
-      <c r="F3" s="66">
-        <v>9.7609999999999992</v>
-      </c>
+      <c r="F3" s="66"/>
       <c r="G3" s="66">
-        <v>9.81</v>
-      </c>
-      <c r="H3" s="67">
-        <v>9.827</v>
-      </c>
-      <c r="I3" s="67">
-        <v>9.7420000000000009</v>
-      </c>
+        <v>9.8529999999999998</v>
+      </c>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
       <c r="J3" s="67"/>
       <c r="K3" s="67"/>
       <c r="L3" s="67">
@@ -8317,7 +8305,7 @@
       <c r="R3" s="32"/>
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B4" s="92"/>
+      <c r="B4" s="95"/>
       <c r="C4" s="68" t="s">
         <v>53</v>
       </c>
@@ -8328,20 +8316,17 @@
       <c r="E4" s="70"/>
       <c r="F4" s="69">
         <f>F3-0.05</f>
-        <v>9.7109999999999985</v>
+        <v>-0.05</v>
       </c>
       <c r="G4" s="69">
         <f>G3-0.05</f>
-        <v>9.76</v>
+        <v>9.802999999999999</v>
       </c>
       <c r="H4" s="69">
         <f>H3-0.05</f>
-        <v>9.7769999999999992</v>
-      </c>
-      <c r="I4" s="69">
-        <f>I3-0.05</f>
-        <v>9.6920000000000002</v>
-      </c>
+        <v>-0.05</v>
+      </c>
+      <c r="I4" s="69"/>
       <c r="J4" s="70"/>
       <c r="K4" s="70"/>
       <c r="L4" s="69">
@@ -8354,7 +8339,7 @@
       <c r="R4" s="32"/>
     </row>
     <row r="5" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B5" s="93"/>
+      <c r="B5" s="96"/>
       <c r="C5" s="62" t="s">
         <v>54</v>
       </c>
@@ -8364,7 +8349,7 @@
       <c r="E5" s="64"/>
       <c r="F5" s="63">
         <f>F2-F4</f>
-        <v>5.0000000000000711E-2</v>
+        <v>9.8320000000000007</v>
       </c>
       <c r="G5" s="63">
         <f>G2-G4</f>
@@ -8372,12 +8357,9 @@
       </c>
       <c r="H5" s="63">
         <f>H2-H4</f>
-        <v>5.0000000000000711E-2</v>
-      </c>
-      <c r="I5" s="63">
-        <f>I2-I4</f>
-        <v>5.0000000000000711E-2</v>
-      </c>
+        <v>9.8320000000000007</v>
+      </c>
+      <c r="I5" s="63"/>
       <c r="J5" s="64"/>
       <c r="K5" s="64"/>
       <c r="L5" s="63">
@@ -8402,7 +8384,7 @@
       <c r="R6" s="32"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B7" s="91" t="s">
+      <c r="B7" s="94" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="60" t="s">
@@ -8413,37 +8395,35 @@
       </c>
       <c r="E7" s="59"/>
       <c r="F7" s="61">
-        <v>9.8469999999999995</v>
+        <v>9.85</v>
       </c>
       <c r="G7" s="61">
-        <v>9.8550000000000004</v>
-      </c>
-      <c r="H7" s="59">
-        <v>9.8119999999999994</v>
-      </c>
-      <c r="I7" s="59">
-        <v>9.7829999999999995</v>
-      </c>
+        <v>9.8510000000000009</v>
+      </c>
+      <c r="H7" s="61">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="I7" s="59"/>
       <c r="J7" s="59"/>
       <c r="K7" s="59"/>
       <c r="L7" s="59">
         <v>9.7430000000000003</v>
       </c>
       <c r="N7" s="38">
-        <v>2.97</v>
+        <v>4.24</v>
       </c>
       <c r="O7" s="38">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
       <c r="Q7" s="32">
-        <v>8.9999999999999993E-3</v>
+        <v>1.2999999999999999E-2</v>
       </c>
       <c r="R7" s="32">
-        <v>0.02</v>
+        <v>3.4000000000000002E-2</v>
       </c>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B8" s="92"/>
+      <c r="B8" s="95"/>
       <c r="C8" s="65" t="s">
         <v>52</v>
       </c>
@@ -8451,21 +8431,12 @@
         <v>9.8249999999999993</v>
       </c>
       <c r="E8" s="67"/>
-      <c r="F8" s="66">
-        <f>G8-($F$1*Q7)</f>
-        <v>9.8330000000000002</v>
-      </c>
+      <c r="F8" s="66"/>
       <c r="G8" s="66">
-        <v>9.8510000000000009</v>
-      </c>
-      <c r="H8" s="67">
-        <f>G8-($H$1*R7)</f>
-        <v>9.8110000000000017</v>
-      </c>
-      <c r="I8" s="67">
-        <f>G8-($I$1*R7)</f>
-        <v>9.7710000000000008</v>
-      </c>
+        <v>9.8819999999999997</v>
+      </c>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
       <c r="J8" s="67"/>
       <c r="K8" s="67"/>
       <c r="L8" s="67">
@@ -8475,7 +8446,7 @@
       <c r="R8" s="32"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B9" s="92"/>
+      <c r="B9" s="95"/>
       <c r="C9" s="68" t="s">
         <v>53</v>
       </c>
@@ -8486,20 +8457,17 @@
       <c r="E9" s="70"/>
       <c r="F9" s="69">
         <f>F8-0.05</f>
-        <v>9.7829999999999995</v>
+        <v>-0.05</v>
       </c>
       <c r="G9" s="69">
         <f>G8-0.05</f>
-        <v>9.8010000000000002</v>
+        <v>9.831999999999999</v>
       </c>
       <c r="H9" s="69">
         <f>H8-0.05</f>
-        <v>9.761000000000001</v>
-      </c>
-      <c r="I9" s="69">
-        <f>I8-0.05</f>
-        <v>9.7210000000000001</v>
-      </c>
+        <v>-0.05</v>
+      </c>
+      <c r="I9" s="69"/>
       <c r="J9" s="70"/>
       <c r="K9" s="70"/>
       <c r="L9" s="69">
@@ -8510,7 +8478,7 @@
       <c r="R9" s="32"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B10" s="93"/>
+      <c r="B10" s="96"/>
       <c r="C10" s="62" t="s">
         <v>54</v>
       </c>
@@ -8520,20 +8488,17 @@
       <c r="E10" s="64"/>
       <c r="F10" s="63">
         <f>F7-F9</f>
-        <v>6.4000000000000057E-2</v>
+        <v>9.9</v>
       </c>
       <c r="G10" s="63">
         <f>G7-G9</f>
-        <v>5.400000000000027E-2</v>
+        <v>1.9000000000001904E-2</v>
       </c>
       <c r="H10" s="63">
         <f>H7-H9</f>
-        <v>5.099999999999838E-2</v>
-      </c>
-      <c r="I10" s="63">
-        <f>I7-I9</f>
-        <v>6.1999999999999389E-2</v>
-      </c>
+        <v>9.8500000000000014</v>
+      </c>
+      <c r="I10" s="63"/>
       <c r="J10" s="64"/>
       <c r="K10" s="64"/>
       <c r="L10" s="63">
@@ -8558,7 +8523,7 @@
       <c r="R11" s="32"/>
     </row>
     <row r="12" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B12" s="91" t="s">
+      <c r="B12" s="94" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="60" t="s">
@@ -8569,37 +8534,35 @@
       </c>
       <c r="E12" s="59"/>
       <c r="F12" s="61">
-        <v>9.8740000000000006</v>
+        <v>9.8919999999999995</v>
       </c>
       <c r="G12" s="61">
-        <v>9.9009999999999998</v>
+        <v>9.9160000000000004</v>
       </c>
       <c r="H12" s="59">
-        <v>9.8789999999999996</v>
-      </c>
-      <c r="I12" s="59">
-        <v>9.8650000000000002</v>
-      </c>
+        <v>9.8759999999999994</v>
+      </c>
+      <c r="I12" s="59"/>
       <c r="J12" s="59"/>
       <c r="K12" s="59"/>
       <c r="L12" s="59">
         <v>9.8350000000000009</v>
       </c>
       <c r="N12" s="38">
-        <v>2.95</v>
+        <v>4.2</v>
       </c>
       <c r="O12" s="38">
-        <v>5.4</v>
+        <v>4.13</v>
       </c>
       <c r="Q12" s="32">
-        <v>8.0000000000000002E-3</v>
+        <v>0.01</v>
       </c>
       <c r="R12" s="32">
-        <v>1.0999999999999999E-2</v>
+        <v>1.7999999999999999E-2</v>
       </c>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B13" s="92"/>
+      <c r="B13" s="95"/>
       <c r="C13" s="65" t="s">
         <v>52</v>
       </c>
@@ -8607,21 +8570,12 @@
         <v>9.8689999999999998</v>
       </c>
       <c r="E13" s="67"/>
-      <c r="F13" s="66">
-        <f>G13-($F$1*Q12)</f>
-        <v>9.8759999999999994</v>
-      </c>
+      <c r="F13" s="66"/>
       <c r="G13" s="66">
-        <v>9.8919999999999995</v>
-      </c>
-      <c r="H13" s="67">
-        <f>G13-($H$1*R12)</f>
-        <v>9.8699999999999992</v>
-      </c>
-      <c r="I13" s="67">
-        <f>G13-($I$1*R12)</f>
-        <v>9.847999999999999</v>
-      </c>
+        <v>9.9109999999999996</v>
+      </c>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
       <c r="J13" s="67"/>
       <c r="K13" s="67"/>
       <c r="L13" s="67">
@@ -8631,7 +8585,7 @@
       <c r="R13" s="32"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B14" s="92"/>
+      <c r="B14" s="95"/>
       <c r="C14" s="68" t="s">
         <v>53</v>
       </c>
@@ -8642,20 +8596,17 @@
       <c r="E14" s="70"/>
       <c r="F14" s="69">
         <f>F13-0.05</f>
-        <v>9.8259999999999987</v>
+        <v>-0.05</v>
       </c>
       <c r="G14" s="69">
         <f>G13-0.05</f>
-        <v>9.8419999999999987</v>
+        <v>9.8609999999999989</v>
       </c>
       <c r="H14" s="69">
         <f>H13-0.05</f>
-        <v>9.8199999999999985</v>
-      </c>
-      <c r="I14" s="69">
-        <f>I13-0.05</f>
-        <v>9.7979999999999983</v>
-      </c>
+        <v>-0.05</v>
+      </c>
+      <c r="I14" s="69"/>
       <c r="J14" s="70"/>
       <c r="K14" s="70"/>
       <c r="L14" s="69">
@@ -8666,7 +8617,7 @@
       <c r="R14" s="32"/>
     </row>
     <row r="15" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B15" s="93"/>
+      <c r="B15" s="96"/>
       <c r="C15" s="62" t="s">
         <v>54</v>
       </c>
@@ -8676,20 +8627,17 @@
       <c r="E15" s="64"/>
       <c r="F15" s="63">
         <f>F12-F14</f>
-        <v>4.8000000000001819E-2</v>
+        <v>9.9420000000000002</v>
       </c>
       <c r="G15" s="63">
         <f>G12-G14</f>
-        <v>5.9000000000001052E-2</v>
+        <v>5.5000000000001492E-2</v>
       </c>
       <c r="H15" s="63">
         <f>H12-H14</f>
-        <v>5.9000000000001052E-2</v>
-      </c>
-      <c r="I15" s="63">
-        <f>I12-I14</f>
-        <v>6.7000000000001947E-2</v>
-      </c>
+        <v>9.9260000000000002</v>
+      </c>
+      <c r="I15" s="63"/>
       <c r="J15" s="64"/>
       <c r="K15" s="64"/>
       <c r="L15" s="63">
@@ -8714,7 +8662,7 @@
       <c r="R16" s="32"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B17" s="91" t="s">
+      <c r="B17" s="94" t="s">
         <v>3</v>
       </c>
       <c r="C17" s="60" t="s">
@@ -8725,37 +8673,35 @@
       </c>
       <c r="E17" s="59"/>
       <c r="F17" s="61">
-        <v>9.9019999999999992</v>
+        <v>9.9269999999999996</v>
       </c>
       <c r="G17" s="61">
-        <v>9.9350000000000005</v>
+        <v>9.9420000000000002</v>
       </c>
       <c r="H17" s="59">
-        <v>9.9190000000000005</v>
-      </c>
-      <c r="I17" s="59">
-        <v>9.9019999999999992</v>
-      </c>
+        <v>9.9120000000000008</v>
+      </c>
+      <c r="I17" s="59"/>
       <c r="J17" s="59"/>
       <c r="K17" s="59"/>
       <c r="L17" s="59">
         <v>9.8780000000000001</v>
       </c>
       <c r="N17" s="38">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="O17" s="38">
-        <v>5.25</v>
+        <v>3.98</v>
       </c>
       <c r="Q17" s="32">
-        <v>1.7000000000000001E-2</v>
+        <v>1.4E-2</v>
       </c>
       <c r="R17" s="32">
-        <v>0.01</v>
+        <v>1.6E-2</v>
       </c>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B18" s="92"/>
+      <c r="B18" s="95"/>
       <c r="C18" s="65" t="s">
         <v>52</v>
       </c>
@@ -8763,21 +8709,12 @@
         <v>9.8829999999999991</v>
       </c>
       <c r="E18" s="67"/>
-      <c r="F18" s="66">
-        <f>G18-($F$1*Q17)</f>
-        <v>9.8989999999999991</v>
-      </c>
+      <c r="F18" s="66"/>
       <c r="G18" s="66">
-        <v>9.9329999999999998</v>
-      </c>
-      <c r="H18" s="67">
-        <f>G18-($H$1*R17)</f>
-        <v>9.9130000000000003</v>
-      </c>
-      <c r="I18" s="67">
-        <f>G18-($I$1*R17)</f>
-        <v>9.8930000000000007</v>
-      </c>
+        <v>9.94</v>
+      </c>
+      <c r="H18" s="67"/>
+      <c r="I18" s="67"/>
       <c r="J18" s="67"/>
       <c r="K18" s="67"/>
       <c r="L18" s="67">
@@ -8787,7 +8724,7 @@
       <c r="R18" s="32"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B19" s="92"/>
+      <c r="B19" s="95"/>
       <c r="C19" s="68" t="s">
         <v>53</v>
       </c>
@@ -8798,20 +8735,17 @@
       <c r="E19" s="70"/>
       <c r="F19" s="69">
         <f>F18-0.05</f>
-        <v>9.8489999999999984</v>
+        <v>-0.05</v>
       </c>
       <c r="G19" s="69">
         <f>G18-0.05</f>
-        <v>9.8829999999999991</v>
+        <v>9.8899999999999988</v>
       </c>
       <c r="H19" s="69">
         <f>H18-0.05</f>
-        <v>9.8629999999999995</v>
-      </c>
-      <c r="I19" s="69">
-        <f>I18-0.05</f>
-        <v>9.843</v>
-      </c>
+        <v>-0.05</v>
+      </c>
+      <c r="I19" s="69"/>
       <c r="J19" s="70"/>
       <c r="K19" s="70"/>
       <c r="L19" s="69">
@@ -8822,7 +8756,7 @@
       <c r="R19" s="32"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B20" s="93"/>
+      <c r="B20" s="96"/>
       <c r="C20" s="62" t="s">
         <v>54</v>
       </c>
@@ -8832,7 +8766,7 @@
       <c r="E20" s="64"/>
       <c r="F20" s="63">
         <f>F17-F19</f>
-        <v>5.3000000000000824E-2</v>
+        <v>9.9770000000000003</v>
       </c>
       <c r="G20" s="63">
         <f>G17-G19</f>
@@ -8840,12 +8774,9 @@
       </c>
       <c r="H20" s="63">
         <f>H17-H19</f>
-        <v>5.6000000000000938E-2</v>
-      </c>
-      <c r="I20" s="63">
-        <f>I17-I19</f>
-        <v>5.8999999999999275E-2</v>
-      </c>
+        <v>9.9620000000000015</v>
+      </c>
+      <c r="I20" s="63"/>
       <c r="J20" s="64"/>
       <c r="K20" s="64"/>
       <c r="L20" s="63">
@@ -8870,7 +8801,7 @@
       <c r="R21" s="32"/>
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B22" s="94" t="s">
+      <c r="B22" s="97" t="s">
         <v>34</v>
       </c>
       <c r="C22" s="60" t="s">
@@ -8881,37 +8812,35 @@
       </c>
       <c r="E22" s="59"/>
       <c r="F22" s="61">
-        <v>9.8930000000000007</v>
+        <v>9.9169999999999998</v>
       </c>
       <c r="G22" s="61">
-        <v>9.9450000000000003</v>
+        <v>9.9550000000000001</v>
       </c>
       <c r="H22" s="59">
-        <v>9.9160000000000004</v>
-      </c>
-      <c r="I22" s="59">
-        <v>9.8960000000000008</v>
-      </c>
+        <v>9.9049999999999994</v>
+      </c>
+      <c r="I22" s="59"/>
       <c r="J22" s="59"/>
       <c r="K22" s="59"/>
       <c r="L22" s="59">
         <v>9.8729999999999993</v>
       </c>
       <c r="N22" s="38">
-        <v>2.93</v>
+        <v>4.18</v>
       </c>
       <c r="O22" s="38">
-        <v>5.13</v>
+        <v>3.9</v>
       </c>
       <c r="Q22" s="32">
-        <v>2.9000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="R22" s="32">
-        <v>1.6E-2</v>
+        <v>2.1000000000000001E-2</v>
       </c>
     </row>
     <row r="23" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B23" s="95"/>
+      <c r="B23" s="98"/>
       <c r="C23" s="65" t="s">
         <v>52</v>
       </c>
@@ -8919,21 +8848,12 @@
         <v>9.8719999999999999</v>
       </c>
       <c r="E23" s="67"/>
-      <c r="F23" s="66">
-        <f>G23-($F$1*Q22)</f>
-        <v>9.8979999999999997</v>
-      </c>
+      <c r="F23" s="66"/>
       <c r="G23" s="66">
-        <v>9.9559999999999995</v>
-      </c>
-      <c r="H23" s="67">
-        <f>G23-($H$1*R22)</f>
-        <v>9.9239999999999995</v>
-      </c>
-      <c r="I23" s="67">
-        <f>G23-($I$1*R22)</f>
-        <v>9.8919999999999995</v>
-      </c>
+        <v>9.9550000000000001</v>
+      </c>
+      <c r="H23" s="67"/>
+      <c r="I23" s="67"/>
       <c r="J23" s="67"/>
       <c r="K23" s="67"/>
       <c r="L23" s="67">
@@ -8943,7 +8863,7 @@
       <c r="R23" s="32"/>
     </row>
     <row r="24" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B24" s="95"/>
+      <c r="B24" s="98"/>
       <c r="C24" s="68" t="s">
         <v>53</v>
       </c>
@@ -8954,20 +8874,17 @@
       <c r="E24" s="70"/>
       <c r="F24" s="69">
         <f>F23-0.05</f>
-        <v>9.847999999999999</v>
+        <v>-0.05</v>
       </c>
       <c r="G24" s="69">
         <f>G23-0.05</f>
-        <v>9.9059999999999988</v>
+        <v>9.9049999999999994</v>
       </c>
       <c r="H24" s="69">
         <f>H23-0.05</f>
-        <v>9.8739999999999988</v>
-      </c>
-      <c r="I24" s="69">
-        <f>I23-0.05</f>
-        <v>9.8419999999999987</v>
-      </c>
+        <v>-0.05</v>
+      </c>
+      <c r="I24" s="69"/>
       <c r="J24" s="70"/>
       <c r="K24" s="70"/>
       <c r="L24" s="69">
@@ -8978,7 +8895,7 @@
       <c r="R24" s="32"/>
     </row>
     <row r="25" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B25" s="96"/>
+      <c r="B25" s="99"/>
       <c r="C25" s="62" t="s">
         <v>54</v>
       </c>
@@ -8988,20 +8905,17 @@
       <c r="E25" s="64"/>
       <c r="F25" s="63">
         <f>F22-F24</f>
-        <v>4.5000000000001705E-2</v>
+        <v>9.9670000000000005</v>
       </c>
       <c r="G25" s="63">
         <f>G22-G24</f>
-        <v>3.9000000000001478E-2</v>
+        <v>5.0000000000000711E-2</v>
       </c>
       <c r="H25" s="63">
         <f>H22-H24</f>
-        <v>4.2000000000001592E-2</v>
-      </c>
-      <c r="I25" s="63">
-        <f>I22-I24</f>
-        <v>5.4000000000002046E-2</v>
-      </c>
+        <v>9.9550000000000001</v>
+      </c>
+      <c r="I25" s="63"/>
       <c r="J25" s="64"/>
       <c r="K25" s="64"/>
       <c r="L25" s="63">
@@ -9026,7 +8940,7 @@
       <c r="R26" s="32"/>
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B27" s="91" t="s">
+      <c r="B27" s="94" t="s">
         <v>5</v>
       </c>
       <c r="C27" s="60" t="s">
@@ -9037,37 +8951,35 @@
       </c>
       <c r="E27" s="59"/>
       <c r="F27" s="61">
-        <v>9.9169999999999998</v>
+        <v>9.9380000000000006</v>
       </c>
       <c r="G27" s="61">
-        <v>9.9469999999999992</v>
+        <v>9.9600000000000009</v>
       </c>
       <c r="H27" s="59">
-        <v>9.9469999999999992</v>
-      </c>
-      <c r="I27" s="59">
-        <v>9.9149999999999991</v>
-      </c>
+        <v>9.9260000000000002</v>
+      </c>
+      <c r="I27" s="59"/>
       <c r="J27" s="59"/>
       <c r="K27" s="59"/>
       <c r="L27" s="59">
         <v>9.8839999999999986</v>
       </c>
       <c r="N27" s="38">
-        <v>3</v>
+        <v>4.26</v>
       </c>
       <c r="O27" s="38">
-        <v>4.97</v>
+        <v>3.7</v>
       </c>
       <c r="Q27" s="32">
+        <v>1.6E-2</v>
+      </c>
+      <c r="R27" s="32">
         <v>2.4E-2</v>
       </c>
-      <c r="R27" s="32">
-        <v>1.7999999999999999E-2</v>
-      </c>
     </row>
     <row r="28" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B28" s="92"/>
+      <c r="B28" s="95"/>
       <c r="C28" s="65" t="s">
         <v>52</v>
       </c>
@@ -9075,21 +8987,12 @@
         <v>9.9030000000000005</v>
       </c>
       <c r="E28" s="67"/>
-      <c r="F28" s="66">
-        <f>G28-($F$1*Q27)</f>
-        <v>9.9260000000000002</v>
-      </c>
+      <c r="F28" s="66"/>
       <c r="G28" s="66">
-        <v>9.9740000000000002</v>
-      </c>
-      <c r="H28" s="67">
-        <f>G28-($H$1*R27)</f>
-        <v>9.9380000000000006</v>
-      </c>
-      <c r="I28" s="67">
-        <f>G28-($I$1*R27)</f>
-        <v>9.902000000000001</v>
-      </c>
+        <v>9.9730000000000008</v>
+      </c>
+      <c r="H28" s="67"/>
+      <c r="I28" s="67"/>
       <c r="J28" s="67"/>
       <c r="K28" s="67"/>
       <c r="L28" s="67">
@@ -9099,7 +9002,7 @@
       <c r="R28" s="32"/>
     </row>
     <row r="29" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B29" s="92"/>
+      <c r="B29" s="95"/>
       <c r="C29" s="68" t="s">
         <v>53</v>
       </c>
@@ -9110,20 +9013,17 @@
       <c r="E29" s="70"/>
       <c r="F29" s="69">
         <f>F28-0.05</f>
-        <v>9.8759999999999994</v>
+        <v>-0.05</v>
       </c>
       <c r="G29" s="69">
         <f>G28-0.05</f>
-        <v>9.9239999999999995</v>
+        <v>9.923</v>
       </c>
       <c r="H29" s="69">
         <f>H28-0.05</f>
-        <v>9.8879999999999999</v>
-      </c>
-      <c r="I29" s="69">
-        <f>I28-0.05</f>
-        <v>9.8520000000000003</v>
-      </c>
+        <v>-0.05</v>
+      </c>
+      <c r="I29" s="69"/>
       <c r="J29" s="70"/>
       <c r="K29" s="70"/>
       <c r="L29" s="69">
@@ -9134,7 +9034,7 @@
       <c r="R29" s="32"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B30" s="93"/>
+      <c r="B30" s="96"/>
       <c r="C30" s="62" t="s">
         <v>54</v>
       </c>
@@ -9144,20 +9044,17 @@
       <c r="E30" s="64"/>
       <c r="F30" s="63">
         <f>F27-F29</f>
-        <v>4.1000000000000369E-2</v>
+        <v>9.9880000000000013</v>
       </c>
       <c r="G30" s="63">
         <f>G27-G29</f>
-        <v>2.2999999999999687E-2</v>
+        <v>3.700000000000081E-2</v>
       </c>
       <c r="H30" s="63">
         <f>H27-H29</f>
-        <v>5.8999999999999275E-2</v>
-      </c>
-      <c r="I30" s="63">
-        <f>I27-I29</f>
-        <v>6.2999999999998835E-2</v>
-      </c>
+        <v>9.9760000000000009</v>
+      </c>
+      <c r="I30" s="63"/>
       <c r="J30" s="64"/>
       <c r="K30" s="64"/>
       <c r="L30" s="63">
@@ -9182,7 +9079,7 @@
       <c r="R31" s="32"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B32" s="91" t="s">
+      <c r="B32" s="94" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="60" t="s">
@@ -9193,37 +9090,35 @@
       </c>
       <c r="E32" s="59"/>
       <c r="F32" s="61">
-        <v>9.9440000000000008</v>
+        <v>9.9610000000000003</v>
       </c>
       <c r="G32" s="61">
-        <v>9.9870000000000001</v>
+        <v>9.9819999999999993</v>
       </c>
       <c r="H32" s="61">
-        <v>9.9600000000000009</v>
-      </c>
-      <c r="I32" s="59">
-        <v>9.9280000000000008</v>
-      </c>
+        <v>9.9499999999999993</v>
+      </c>
+      <c r="I32" s="59"/>
       <c r="J32" s="59"/>
       <c r="K32" s="59"/>
       <c r="L32" s="59">
         <v>9.9120000000000008</v>
       </c>
       <c r="N32" s="38">
-        <v>3.05</v>
+        <v>3.72</v>
       </c>
       <c r="O32" s="38">
-        <v>4.46</v>
+        <v>3.8</v>
       </c>
       <c r="Q32" s="32">
-        <v>2.9000000000000001E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="R32" s="32">
-        <v>2.3E-2</v>
+        <v>2.7E-2</v>
       </c>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B33" s="92"/>
+      <c r="B33" s="95"/>
       <c r="C33" s="65" t="s">
         <v>52</v>
       </c>
@@ -9231,21 +9126,12 @@
         <v>9.9260000000000002</v>
       </c>
       <c r="E33" s="67"/>
-      <c r="F33" s="66">
-        <f>G33-($F$1*Q32)</f>
-        <v>9.9570000000000007</v>
-      </c>
+      <c r="F33" s="66"/>
       <c r="G33" s="66">
-        <v>10.015000000000001</v>
-      </c>
-      <c r="H33" s="67">
-        <f>G33-($H$1*R32)</f>
-        <v>9.9690000000000012</v>
-      </c>
-      <c r="I33" s="67">
-        <f>G33-($I$1*R32)</f>
-        <v>9.923</v>
-      </c>
+        <v>10.013999999999999</v>
+      </c>
+      <c r="H33" s="67"/>
+      <c r="I33" s="67"/>
       <c r="J33" s="67"/>
       <c r="K33" s="67"/>
       <c r="L33" s="67">
@@ -9255,7 +9141,7 @@
       <c r="R33" s="32"/>
     </row>
     <row r="34" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B34" s="92"/>
+      <c r="B34" s="95"/>
       <c r="C34" s="68" t="s">
         <v>53</v>
       </c>
@@ -9266,20 +9152,17 @@
       <c r="E34" s="70"/>
       <c r="F34" s="69">
         <f>F33-0.05</f>
-        <v>9.907</v>
+        <v>-0.05</v>
       </c>
       <c r="G34" s="69">
         <f>G33-0.05</f>
-        <v>9.9649999999999999</v>
+        <v>9.9639999999999986</v>
       </c>
       <c r="H34" s="69">
         <f>H33-0.05</f>
-        <v>9.9190000000000005</v>
-      </c>
-      <c r="I34" s="69">
-        <f>I33-0.05</f>
-        <v>9.8729999999999993</v>
-      </c>
+        <v>-0.05</v>
+      </c>
+      <c r="I34" s="69"/>
       <c r="J34" s="70"/>
       <c r="K34" s="70"/>
       <c r="L34" s="69">
@@ -9290,7 +9173,7 @@
       <c r="R34" s="32"/>
     </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B35" s="93"/>
+      <c r="B35" s="96"/>
       <c r="C35" s="62" t="s">
         <v>54</v>
       </c>
@@ -9300,20 +9183,17 @@
       <c r="E35" s="64"/>
       <c r="F35" s="63">
         <f>F32-F34</f>
-        <v>3.700000000000081E-2</v>
+        <v>10.011000000000001</v>
       </c>
       <c r="G35" s="63">
         <f>G32-G34</f>
-        <v>2.2000000000000242E-2</v>
+        <v>1.8000000000000682E-2</v>
       </c>
       <c r="H35" s="63">
         <f>H32-H34</f>
-        <v>4.1000000000000369E-2</v>
-      </c>
-      <c r="I35" s="63">
-        <f>I32-I34</f>
-        <v>5.5000000000001492E-2</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="I35" s="63"/>
       <c r="J35" s="64"/>
       <c r="K35" s="64"/>
       <c r="L35" s="63">
@@ -9338,7 +9218,7 @@
       <c r="R36" s="32"/>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B37" s="91" t="s">
+      <c r="B37" s="94" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="60" t="s">
@@ -9377,7 +9257,7 @@
       </c>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B38" s="92"/>
+      <c r="B38" s="95"/>
       <c r="C38" s="65" t="s">
         <v>52</v>
       </c>
@@ -9406,7 +9286,7 @@
       <c r="R38" s="32"/>
     </row>
     <row r="39" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B39" s="92"/>
+      <c r="B39" s="95"/>
       <c r="C39" s="68" t="s">
         <v>53</v>
       </c>
@@ -9438,7 +9318,7 @@
       <c r="R39" s="32"/>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B40" s="93"/>
+      <c r="B40" s="96"/>
       <c r="C40" s="62" t="s">
         <v>54</v>
       </c>
@@ -9483,7 +9363,7 @@
       <c r="R41" s="32"/>
     </row>
     <row r="42" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B42" s="94" t="s">
+      <c r="B42" s="97" t="s">
         <v>35</v>
       </c>
       <c r="C42" s="60" t="s">
@@ -9522,7 +9402,7 @@
       </c>
     </row>
     <row r="43" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B43" s="95"/>
+      <c r="B43" s="98"/>
       <c r="C43" s="65" t="s">
         <v>52</v>
       </c>
@@ -9551,7 +9431,7 @@
       <c r="R43" s="32"/>
     </row>
     <row r="44" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B44" s="95"/>
+      <c r="B44" s="98"/>
       <c r="C44" s="68" t="s">
         <v>53</v>
       </c>
@@ -9583,7 +9463,7 @@
       <c r="R44" s="32"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B45" s="96"/>
+      <c r="B45" s="99"/>
       <c r="C45" s="62" t="s">
         <v>54</v>
       </c>
@@ -9628,7 +9508,7 @@
       <c r="R46" s="32"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B47" s="91" t="s">
+      <c r="B47" s="94" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="60" t="s">
@@ -9667,7 +9547,7 @@
       </c>
     </row>
     <row r="48" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B48" s="92"/>
+      <c r="B48" s="95"/>
       <c r="C48" s="65" t="s">
         <v>52</v>
       </c>
@@ -9696,7 +9576,7 @@
       <c r="R48" s="32"/>
     </row>
     <row r="49" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B49" s="92"/>
+      <c r="B49" s="95"/>
       <c r="C49" s="68" t="s">
         <v>53</v>
       </c>
@@ -9728,7 +9608,7 @@
       <c r="R49" s="32"/>
     </row>
     <row r="50" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B50" s="93"/>
+      <c r="B50" s="96"/>
       <c r="C50" s="62" t="s">
         <v>54</v>
       </c>
@@ -9773,7 +9653,7 @@
       <c r="R51" s="32"/>
     </row>
     <row r="52" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B52" s="91" t="s">
+      <c r="B52" s="94" t="s">
         <v>9</v>
       </c>
       <c r="C52" s="60" t="s">
@@ -9812,7 +9692,7 @@
       </c>
     </row>
     <row r="53" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B53" s="92"/>
+      <c r="B53" s="95"/>
       <c r="C53" s="65" t="s">
         <v>52</v>
       </c>
@@ -9841,7 +9721,7 @@
       <c r="R53" s="32"/>
     </row>
     <row r="54" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B54" s="92"/>
+      <c r="B54" s="95"/>
       <c r="C54" s="68" t="s">
         <v>53</v>
       </c>
@@ -9873,7 +9753,7 @@
       <c r="R54" s="32"/>
     </row>
     <row r="55" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B55" s="93"/>
+      <c r="B55" s="96"/>
       <c r="C55" s="62" t="s">
         <v>54</v>
       </c>
@@ -9918,7 +9798,7 @@
       <c r="R56" s="32"/>
     </row>
     <row r="57" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B57" s="91" t="s">
+      <c r="B57" s="94" t="s">
         <v>31</v>
       </c>
       <c r="C57" s="60" t="s">
@@ -9957,7 +9837,7 @@
       </c>
     </row>
     <row r="58" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B58" s="92"/>
+      <c r="B58" s="95"/>
       <c r="C58" s="65" t="s">
         <v>52</v>
       </c>
@@ -9986,7 +9866,7 @@
       <c r="R58" s="32"/>
     </row>
     <row r="59" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B59" s="92"/>
+      <c r="B59" s="95"/>
       <c r="C59" s="68" t="s">
         <v>53</v>
       </c>
@@ -10018,7 +9898,7 @@
       <c r="R59" s="32"/>
     </row>
     <row r="60" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B60" s="93"/>
+      <c r="B60" s="96"/>
       <c r="C60" s="62" t="s">
         <v>54</v>
       </c>
@@ -10063,7 +9943,7 @@
       <c r="R61" s="32"/>
     </row>
     <row r="62" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B62" s="91" t="s">
+      <c r="B62" s="94" t="s">
         <v>11</v>
       </c>
       <c r="C62" s="60" t="s">
@@ -10102,7 +9982,7 @@
       </c>
     </row>
     <row r="63" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B63" s="92"/>
+      <c r="B63" s="95"/>
       <c r="C63" s="65" t="s">
         <v>52</v>
       </c>
@@ -10131,7 +10011,7 @@
       <c r="R63" s="32"/>
     </row>
     <row r="64" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B64" s="92"/>
+      <c r="B64" s="95"/>
       <c r="C64" s="68" t="s">
         <v>53</v>
       </c>
@@ -10163,7 +10043,7 @@
       <c r="R64" s="32"/>
     </row>
     <row r="65" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B65" s="93"/>
+      <c r="B65" s="96"/>
       <c r="C65" s="62" t="s">
         <v>54</v>
       </c>
@@ -10208,7 +10088,7 @@
       <c r="R66" s="32"/>
     </row>
     <row r="67" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B67" s="91" t="s">
+      <c r="B67" s="94" t="s">
         <v>12</v>
       </c>
       <c r="C67" s="60" t="s">
@@ -10247,7 +10127,7 @@
       </c>
     </row>
     <row r="68" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B68" s="92"/>
+      <c r="B68" s="95"/>
       <c r="C68" s="65" t="s">
         <v>52</v>
       </c>
@@ -10276,7 +10156,7 @@
       <c r="R68" s="32"/>
     </row>
     <row r="69" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B69" s="92"/>
+      <c r="B69" s="95"/>
       <c r="C69" s="68" t="s">
         <v>53</v>
       </c>
@@ -10308,7 +10188,7 @@
       <c r="R69" s="32"/>
     </row>
     <row r="70" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B70" s="93"/>
+      <c r="B70" s="96"/>
       <c r="C70" s="62" t="s">
         <v>54</v>
       </c>
@@ -10353,7 +10233,7 @@
       <c r="R71" s="32"/>
     </row>
     <row r="72" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B72" s="91" t="s">
+      <c r="B72" s="94" t="s">
         <v>13</v>
       </c>
       <c r="C72" s="60" t="s">
@@ -10392,7 +10272,7 @@
       </c>
     </row>
     <row r="73" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B73" s="92"/>
+      <c r="B73" s="95"/>
       <c r="C73" s="65" t="s">
         <v>52</v>
       </c>
@@ -10421,7 +10301,7 @@
       <c r="R73" s="32"/>
     </row>
     <row r="74" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B74" s="92"/>
+      <c r="B74" s="95"/>
       <c r="C74" s="68" t="s">
         <v>53</v>
       </c>
@@ -10453,7 +10333,7 @@
       <c r="R74" s="32"/>
     </row>
     <row r="75" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B75" s="93"/>
+      <c r="B75" s="96"/>
       <c r="C75" s="62" t="s">
         <v>54</v>
       </c>
@@ -10498,7 +10378,7 @@
       <c r="R76" s="32"/>
     </row>
     <row r="77" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B77" s="94" t="s">
+      <c r="B77" s="97" t="s">
         <v>44</v>
       </c>
       <c r="C77" s="60" t="s">
@@ -10537,7 +10417,7 @@
       </c>
     </row>
     <row r="78" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B78" s="95"/>
+      <c r="B78" s="98"/>
       <c r="C78" s="65" t="s">
         <v>52</v>
       </c>
@@ -10566,7 +10446,7 @@
       <c r="R78" s="32"/>
     </row>
     <row r="79" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B79" s="95"/>
+      <c r="B79" s="98"/>
       <c r="C79" s="68" t="s">
         <v>53</v>
       </c>
@@ -10598,7 +10478,7 @@
       <c r="R79" s="32"/>
     </row>
     <row r="80" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B80" s="96"/>
+      <c r="B80" s="99"/>
       <c r="C80" s="62" t="s">
         <v>54</v>
       </c>
@@ -10643,7 +10523,7 @@
       <c r="R81" s="32"/>
     </row>
     <row r="82" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B82" s="91" t="s">
+      <c r="B82" s="94" t="s">
         <v>14</v>
       </c>
       <c r="C82" s="60" t="s">
@@ -10682,7 +10562,7 @@
       </c>
     </row>
     <row r="83" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B83" s="92"/>
+      <c r="B83" s="95"/>
       <c r="C83" s="65" t="s">
         <v>52</v>
       </c>
@@ -10711,7 +10591,7 @@
       <c r="R83" s="32"/>
     </row>
     <row r="84" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B84" s="92"/>
+      <c r="B84" s="95"/>
       <c r="C84" s="68" t="s">
         <v>53</v>
       </c>
@@ -10743,7 +10623,7 @@
       <c r="R84" s="32"/>
     </row>
     <row r="85" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B85" s="93"/>
+      <c r="B85" s="96"/>
       <c r="C85" s="62" t="s">
         <v>54</v>
       </c>
@@ -10788,7 +10668,7 @@
       <c r="R86" s="32"/>
     </row>
     <row r="87" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B87" s="91" t="s">
+      <c r="B87" s="94" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="60" t="s">
@@ -10827,7 +10707,7 @@
       </c>
     </row>
     <row r="88" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B88" s="92"/>
+      <c r="B88" s="95"/>
       <c r="C88" s="65" t="s">
         <v>52</v>
       </c>
@@ -10856,7 +10736,7 @@
       <c r="R88" s="32"/>
     </row>
     <row r="89" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B89" s="92"/>
+      <c r="B89" s="95"/>
       <c r="C89" s="68" t="s">
         <v>53</v>
       </c>
@@ -10888,7 +10768,7 @@
       <c r="R89" s="32"/>
     </row>
     <row r="90" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B90" s="93"/>
+      <c r="B90" s="96"/>
       <c r="C90" s="62" t="s">
         <v>54</v>
       </c>
@@ -10933,7 +10813,7 @@
       <c r="R91" s="32"/>
     </row>
     <row r="92" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B92" s="91" t="s">
+      <c r="B92" s="94" t="s">
         <v>16</v>
       </c>
       <c r="C92" s="60" t="s">
@@ -10972,7 +10852,7 @@
       </c>
     </row>
     <row r="93" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B93" s="92"/>
+      <c r="B93" s="95"/>
       <c r="C93" s="65" t="s">
         <v>52</v>
       </c>
@@ -11001,7 +10881,7 @@
       <c r="R93" s="32"/>
     </row>
     <row r="94" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B94" s="92"/>
+      <c r="B94" s="95"/>
       <c r="C94" s="68" t="s">
         <v>53</v>
       </c>
@@ -11033,7 +10913,7 @@
       <c r="R94" s="32"/>
     </row>
     <row r="95" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B95" s="93"/>
+      <c r="B95" s="96"/>
       <c r="C95" s="62" t="s">
         <v>54</v>
       </c>
@@ -11078,7 +10958,7 @@
       <c r="R96" s="32"/>
     </row>
     <row r="97" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B97" s="91" t="s">
+      <c r="B97" s="94" t="s">
         <v>17</v>
       </c>
       <c r="C97" s="60" t="s">
@@ -11117,7 +10997,7 @@
       </c>
     </row>
     <row r="98" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B98" s="92"/>
+      <c r="B98" s="95"/>
       <c r="C98" s="65" t="s">
         <v>52</v>
       </c>
@@ -11146,7 +11026,7 @@
       <c r="R98" s="32"/>
     </row>
     <row r="99" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B99" s="92"/>
+      <c r="B99" s="95"/>
       <c r="C99" s="68" t="s">
         <v>53</v>
       </c>
@@ -11178,7 +11058,7 @@
       <c r="R99" s="32"/>
     </row>
     <row r="100" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B100" s="93"/>
+      <c r="B100" s="96"/>
       <c r="C100" s="62" t="s">
         <v>54</v>
       </c>
@@ -11223,7 +11103,7 @@
       <c r="R101" s="32"/>
     </row>
     <row r="102" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B102" s="91" t="s">
+      <c r="B102" s="94" t="s">
         <v>18</v>
       </c>
       <c r="C102" s="60" t="s">
@@ -11262,7 +11142,7 @@
       </c>
     </row>
     <row r="103" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B103" s="92"/>
+      <c r="B103" s="95"/>
       <c r="C103" s="65" t="s">
         <v>52</v>
       </c>
@@ -11291,7 +11171,7 @@
       <c r="R103" s="32"/>
     </row>
     <row r="104" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B104" s="92"/>
+      <c r="B104" s="95"/>
       <c r="C104" s="68" t="s">
         <v>53</v>
       </c>
@@ -11323,7 +11203,7 @@
       <c r="R104" s="32"/>
     </row>
     <row r="105" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B105" s="93"/>
+      <c r="B105" s="96"/>
       <c r="C105" s="62" t="s">
         <v>54</v>
       </c>
@@ -11368,7 +11248,7 @@
       <c r="R106" s="32"/>
     </row>
     <row r="107" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B107" s="94" t="s">
+      <c r="B107" s="97" t="s">
         <v>37</v>
       </c>
       <c r="C107" s="60" t="s">
@@ -11407,7 +11287,7 @@
       </c>
     </row>
     <row r="108" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B108" s="95"/>
+      <c r="B108" s="98"/>
       <c r="C108" s="65" t="s">
         <v>52</v>
       </c>
@@ -11436,7 +11316,7 @@
       <c r="R108" s="32"/>
     </row>
     <row r="109" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B109" s="95"/>
+      <c r="B109" s="98"/>
       <c r="C109" s="68" t="s">
         <v>53</v>
       </c>
@@ -11468,7 +11348,7 @@
       <c r="R109" s="32"/>
     </row>
     <row r="110" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B110" s="96"/>
+      <c r="B110" s="99"/>
       <c r="C110" s="62" t="s">
         <v>54</v>
       </c>
@@ -11513,7 +11393,7 @@
       <c r="R111" s="32"/>
     </row>
     <row r="112" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B112" s="91" t="s">
+      <c r="B112" s="94" t="s">
         <v>19</v>
       </c>
       <c r="C112" s="60" t="s">
@@ -11552,7 +11432,7 @@
       </c>
     </row>
     <row r="113" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B113" s="92"/>
+      <c r="B113" s="95"/>
       <c r="C113" s="65" t="s">
         <v>52</v>
       </c>
@@ -11581,7 +11461,7 @@
       <c r="R113" s="32"/>
     </row>
     <row r="114" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B114" s="92"/>
+      <c r="B114" s="95"/>
       <c r="C114" s="68" t="s">
         <v>53</v>
       </c>
@@ -11613,7 +11493,7 @@
       <c r="R114" s="32"/>
     </row>
     <row r="115" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B115" s="93"/>
+      <c r="B115" s="96"/>
       <c r="C115" s="62" t="s">
         <v>54</v>
       </c>
@@ -11658,7 +11538,7 @@
       <c r="R116" s="32"/>
     </row>
     <row r="117" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B117" s="91" t="s">
+      <c r="B117" s="94" t="s">
         <v>20</v>
       </c>
       <c r="C117" s="60" t="s">
@@ -11697,7 +11577,7 @@
       </c>
     </row>
     <row r="118" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B118" s="92"/>
+      <c r="B118" s="95"/>
       <c r="C118" s="65" t="s">
         <v>52</v>
       </c>
@@ -11726,7 +11606,7 @@
       <c r="R118" s="32"/>
     </row>
     <row r="119" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B119" s="92"/>
+      <c r="B119" s="95"/>
       <c r="C119" s="68" t="s">
         <v>53</v>
       </c>
@@ -11758,7 +11638,7 @@
       <c r="R119" s="32"/>
     </row>
     <row r="120" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B120" s="93"/>
+      <c r="B120" s="96"/>
       <c r="C120" s="62" t="s">
         <v>54</v>
       </c>
@@ -11803,7 +11683,7 @@
       <c r="R121" s="32"/>
     </row>
     <row r="122" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B122" s="91" t="s">
+      <c r="B122" s="94" t="s">
         <v>21</v>
       </c>
       <c r="C122" s="60" t="s">
@@ -11842,7 +11722,7 @@
       </c>
     </row>
     <row r="123" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B123" s="92"/>
+      <c r="B123" s="95"/>
       <c r="C123" s="65" t="s">
         <v>52</v>
       </c>
@@ -11871,7 +11751,7 @@
       <c r="R123" s="32"/>
     </row>
     <row r="124" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B124" s="92"/>
+      <c r="B124" s="95"/>
       <c r="C124" s="68" t="s">
         <v>53</v>
       </c>
@@ -11903,7 +11783,7 @@
       <c r="R124" s="32"/>
     </row>
     <row r="125" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B125" s="93"/>
+      <c r="B125" s="96"/>
       <c r="C125" s="62" t="s">
         <v>54</v>
       </c>
@@ -11948,7 +11828,7 @@
       <c r="R126" s="32"/>
     </row>
     <row r="127" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B127" s="94" t="s">
+      <c r="B127" s="97" t="s">
         <v>38</v>
       </c>
       <c r="C127" s="60" t="s">
@@ -11987,7 +11867,7 @@
       </c>
     </row>
     <row r="128" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B128" s="95"/>
+      <c r="B128" s="98"/>
       <c r="C128" s="65" t="s">
         <v>52</v>
       </c>
@@ -12016,7 +11896,7 @@
       <c r="R128" s="32"/>
     </row>
     <row r="129" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B129" s="95"/>
+      <c r="B129" s="98"/>
       <c r="C129" s="68" t="s">
         <v>53</v>
       </c>
@@ -12048,7 +11928,7 @@
       <c r="R129" s="32"/>
     </row>
     <row r="130" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B130" s="96"/>
+      <c r="B130" s="99"/>
       <c r="C130" s="62" t="s">
         <v>54</v>
       </c>
@@ -12093,7 +11973,7 @@
       <c r="R131" s="32"/>
     </row>
     <row r="132" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B132" s="91" t="s">
+      <c r="B132" s="94" t="s">
         <v>22</v>
       </c>
       <c r="C132" s="60" t="s">
@@ -12132,7 +12012,7 @@
       </c>
     </row>
     <row r="133" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B133" s="92"/>
+      <c r="B133" s="95"/>
       <c r="C133" s="65" t="s">
         <v>52</v>
       </c>
@@ -12161,7 +12041,7 @@
       <c r="R133" s="32"/>
     </row>
     <row r="134" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B134" s="92"/>
+      <c r="B134" s="95"/>
       <c r="C134" s="68" t="s">
         <v>53</v>
       </c>
@@ -12193,7 +12073,7 @@
       <c r="R134" s="32"/>
     </row>
     <row r="135" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B135" s="93"/>
+      <c r="B135" s="96"/>
       <c r="C135" s="62" t="s">
         <v>54</v>
       </c>
@@ -12238,7 +12118,7 @@
       <c r="R136" s="32"/>
     </row>
     <row r="137" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B137" s="91" t="s">
+      <c r="B137" s="94" t="s">
         <v>23</v>
       </c>
       <c r="C137" s="60" t="s">
@@ -12277,7 +12157,7 @@
       </c>
     </row>
     <row r="138" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B138" s="92"/>
+      <c r="B138" s="95"/>
       <c r="C138" s="65" t="s">
         <v>52</v>
       </c>
@@ -12306,7 +12186,7 @@
       <c r="R138" s="32"/>
     </row>
     <row r="139" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B139" s="92"/>
+      <c r="B139" s="95"/>
       <c r="C139" s="68" t="s">
         <v>53</v>
       </c>
@@ -12338,7 +12218,7 @@
       <c r="R139" s="32"/>
     </row>
     <row r="140" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B140" s="93"/>
+      <c r="B140" s="96"/>
       <c r="C140" s="62" t="s">
         <v>54</v>
       </c>
@@ -12383,7 +12263,7 @@
       <c r="R141" s="32"/>
     </row>
     <row r="142" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B142" s="91" t="s">
+      <c r="B142" s="94" t="s">
         <v>39</v>
       </c>
       <c r="C142" s="60" t="s">
@@ -12422,7 +12302,7 @@
       </c>
     </row>
     <row r="143" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B143" s="92"/>
+      <c r="B143" s="95"/>
       <c r="C143" s="65" t="s">
         <v>52</v>
       </c>
@@ -12449,7 +12329,7 @@
       </c>
     </row>
     <row r="144" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B144" s="92"/>
+      <c r="B144" s="95"/>
       <c r="C144" s="68" t="s">
         <v>53</v>
       </c>
@@ -12479,7 +12359,7 @@
       </c>
     </row>
     <row r="145" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B145" s="93"/>
+      <c r="B145" s="96"/>
       <c r="C145" s="62" t="s">
         <v>54</v>
       </c>
@@ -12522,7 +12402,7 @@
       <c r="R146" s="32"/>
     </row>
     <row r="147" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B147" s="91" t="s">
+      <c r="B147" s="94" t="s">
         <v>24</v>
       </c>
       <c r="C147" s="60" t="s">
@@ -12551,10 +12431,10 @@
       <c r="L147" s="59">
         <v>10.643000000000001</v>
       </c>
-      <c r="N147" s="97">
+      <c r="N147" s="38">
         <v>3.1</v>
       </c>
-      <c r="O147" s="97">
+      <c r="O147" s="38">
         <v>8.6</v>
       </c>
       <c r="Q147" s="32">
@@ -12565,7 +12445,7 @@
       </c>
     </row>
     <row r="148" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B148" s="92"/>
+      <c r="B148" s="95"/>
       <c r="C148" s="65" t="s">
         <v>52</v>
       </c>
@@ -12598,7 +12478,7 @@
       </c>
     </row>
     <row r="149" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B149" s="92"/>
+      <c r="B149" s="95"/>
       <c r="C149" s="68" t="s">
         <v>53</v>
       </c>
@@ -12634,7 +12514,7 @@
       </c>
     </row>
     <row r="150" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B150" s="93"/>
+      <c r="B150" s="96"/>
       <c r="C150" s="62" t="s">
         <v>54</v>
       </c>
@@ -12679,13 +12559,13 @@
       <c r="J151" s="75"/>
       <c r="K151" s="75"/>
       <c r="L151" s="72"/>
-      <c r="N151" s="98"/>
-      <c r="O151" s="98"/>
+      <c r="N151" s="76"/>
+      <c r="O151" s="76"/>
       <c r="Q151" s="32"/>
       <c r="R151" s="32"/>
     </row>
     <row r="152" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B152" s="91" t="s">
+      <c r="B152" s="94" t="s">
         <v>40</v>
       </c>
       <c r="C152" s="60" t="s">
@@ -12718,10 +12598,10 @@
       <c r="L152" s="59">
         <v>10.643000000000001</v>
       </c>
-      <c r="N152" s="97">
+      <c r="N152" s="38">
         <v>5</v>
       </c>
-      <c r="O152" s="97">
+      <c r="O152" s="38">
         <v>9</v>
       </c>
       <c r="Q152" s="1">
@@ -12732,7 +12612,7 @@
       </c>
     </row>
     <row r="153" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B153" s="92"/>
+      <c r="B153" s="95"/>
       <c r="C153" s="65" t="s">
         <v>52</v>
       </c>
@@ -12771,36 +12651,36 @@
       </c>
     </row>
     <row r="154" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B154" s="92"/>
+      <c r="B154" s="95"/>
       <c r="C154" s="68" t="s">
         <v>53</v>
       </c>
       <c r="D154" s="69">
-        <f>D153-0.05</f>
+        <f t="shared" ref="D154:J154" si="0">D153-0.05</f>
         <v>10.581</v>
       </c>
       <c r="E154" s="69">
-        <f>E153-0.05</f>
+        <f t="shared" si="0"/>
         <v>10.599</v>
       </c>
       <c r="F154" s="69">
-        <f>F153-0.05</f>
+        <f t="shared" si="0"/>
         <v>10.635</v>
       </c>
       <c r="G154" s="69">
-        <f>G153-0.05</f>
+        <f t="shared" si="0"/>
         <v>10.670999999999999</v>
       </c>
       <c r="H154" s="69">
-        <f>H153-0.05</f>
+        <f t="shared" si="0"/>
         <v>10.652999999999999</v>
       </c>
       <c r="I154" s="69">
-        <f>I153-0.05</f>
+        <f t="shared" si="0"/>
         <v>10.635</v>
       </c>
       <c r="J154" s="69">
-        <f>J153-0.05</f>
+        <f t="shared" si="0"/>
         <v>10.616999999999999</v>
       </c>
       <c r="K154" s="70"/>
@@ -12810,7 +12690,7 @@
       </c>
     </row>
     <row r="155" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B155" s="93"/>
+      <c r="B155" s="96"/>
       <c r="C155" s="62" t="s">
         <v>54</v>
       </c>
@@ -12818,27 +12698,27 @@
         <v>0.05</v>
       </c>
       <c r="E155" s="63">
-        <f>E152-E154</f>
+        <f t="shared" ref="E155:J155" si="1">E152-E154</f>
         <v>5.5999999999999162E-2</v>
       </c>
       <c r="F155" s="63">
-        <f>F152-F154</f>
+        <f t="shared" si="1"/>
         <v>4.1000000000000369E-2</v>
       </c>
       <c r="G155" s="63">
-        <f>G152-G154</f>
+        <f t="shared" si="1"/>
         <v>2.2000000000000242E-2</v>
       </c>
       <c r="H155" s="63">
-        <f>H152-H154</f>
+        <f t="shared" si="1"/>
         <v>2.9000000000001691E-2</v>
       </c>
       <c r="I155" s="63">
-        <f>I152-I154</f>
+        <f t="shared" si="1"/>
         <v>4.8999999999999488E-2</v>
       </c>
       <c r="J155" s="63">
-        <f>J152-J154</f>
+        <f t="shared" si="1"/>
         <v>6.6000000000000725E-2</v>
       </c>
       <c r="K155" s="64"/>
@@ -12847,7 +12727,7 @@
       </c>
     </row>
     <row r="158" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B158" s="91" t="s">
+      <c r="B158" s="94" t="s">
         <v>0</v>
       </c>
       <c r="C158" s="60" t="s">
@@ -12872,10 +12752,10 @@
       <c r="L158" s="61">
         <v>10.56</v>
       </c>
-      <c r="N158" s="97">
+      <c r="N158" s="38">
         <v>3.26</v>
       </c>
-      <c r="O158" s="97">
+      <c r="O158" s="38">
         <v>3.09</v>
       </c>
       <c r="Q158" s="32">
@@ -12886,7 +12766,7 @@
       </c>
     </row>
     <row r="159" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B159" s="92"/>
+      <c r="B159" s="95"/>
       <c r="C159" s="65" t="s">
         <v>52</v>
       </c>
@@ -12911,7 +12791,7 @@
       </c>
     </row>
     <row r="160" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B160" s="92"/>
+      <c r="B160" s="95"/>
       <c r="C160" s="68" t="s">
         <v>53</v>
       </c>
@@ -12941,7 +12821,7 @@
       </c>
     </row>
     <row r="161" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B161" s="93"/>
+      <c r="B161" s="96"/>
       <c r="C161" s="62" t="s">
         <v>54</v>
       </c>
@@ -12980,13 +12860,13 @@
       <c r="J162" s="75"/>
       <c r="K162" s="75"/>
       <c r="L162" s="72"/>
-      <c r="N162" s="98"/>
-      <c r="O162" s="98"/>
+      <c r="N162" s="76"/>
+      <c r="O162" s="76"/>
       <c r="Q162" s="32"/>
       <c r="R162" s="32"/>
     </row>
     <row r="163" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B163" s="91" t="s">
+      <c r="B163" s="94" t="s">
         <v>1</v>
       </c>
       <c r="C163" s="60" t="s">
@@ -13011,10 +12891,10 @@
       <c r="L163" s="59">
         <v>10.587999999999999</v>
       </c>
-      <c r="N163" s="97">
+      <c r="N163" s="38">
         <v>3.1</v>
       </c>
-      <c r="O163" s="97">
+      <c r="O163" s="38">
         <v>3.2</v>
       </c>
       <c r="Q163" s="32">
@@ -13025,7 +12905,7 @@
       </c>
     </row>
     <row r="164" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B164" s="92"/>
+      <c r="B164" s="95"/>
       <c r="C164" s="65" t="s">
         <v>52</v>
       </c>
@@ -13052,7 +12932,7 @@
       </c>
     </row>
     <row r="165" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B165" s="92"/>
+      <c r="B165" s="95"/>
       <c r="C165" s="68" t="s">
         <v>53</v>
       </c>
@@ -13082,7 +12962,7 @@
       </c>
     </row>
     <row r="166" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B166" s="93"/>
+      <c r="B166" s="96"/>
       <c r="C166" s="62" t="s">
         <v>54</v>
       </c>
@@ -13121,13 +13001,13 @@
       <c r="J167" s="75"/>
       <c r="K167" s="75"/>
       <c r="L167" s="72"/>
-      <c r="N167" s="98"/>
-      <c r="O167" s="98"/>
+      <c r="N167" s="76"/>
+      <c r="O167" s="76"/>
       <c r="Q167" s="32"/>
       <c r="R167" s="32"/>
     </row>
     <row r="168" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B168" s="91" t="s">
+      <c r="B168" s="94" t="s">
         <v>41</v>
       </c>
       <c r="C168" s="60" t="s">
@@ -13152,10 +13032,10 @@
       <c r="L168" s="59">
         <v>10.603</v>
       </c>
-      <c r="N168" s="97">
+      <c r="N168" s="38">
         <v>3.02</v>
       </c>
-      <c r="O168" s="97">
+      <c r="O168" s="38">
         <v>3.13</v>
       </c>
       <c r="Q168" s="32">
@@ -13166,7 +13046,7 @@
       </c>
     </row>
     <row r="169" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B169" s="92"/>
+      <c r="B169" s="95"/>
       <c r="C169" s="65" t="s">
         <v>52</v>
       </c>
@@ -13193,7 +13073,7 @@
       </c>
     </row>
     <row r="170" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B170" s="92"/>
+      <c r="B170" s="95"/>
       <c r="C170" s="68" t="s">
         <v>53</v>
       </c>
@@ -13223,7 +13103,7 @@
       </c>
     </row>
     <row r="171" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B171" s="93"/>
+      <c r="B171" s="96"/>
       <c r="C171" s="62" t="s">
         <v>54</v>
       </c>
@@ -13263,13 +13143,13 @@
       <c r="J172" s="75"/>
       <c r="K172" s="75"/>
       <c r="L172" s="72"/>
-      <c r="N172" s="98"/>
-      <c r="O172" s="98"/>
+      <c r="N172" s="76"/>
+      <c r="O172" s="76"/>
       <c r="Q172" s="32"/>
       <c r="R172" s="32"/>
     </row>
     <row r="173" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B173" s="91" t="s">
+      <c r="B173" s="94" t="s">
         <v>2</v>
       </c>
       <c r="C173" s="60" t="s">
@@ -13294,10 +13174,10 @@
       <c r="L173" s="59">
         <v>10.605</v>
       </c>
-      <c r="N173" s="97">
+      <c r="N173" s="38">
         <v>3.23</v>
       </c>
-      <c r="O173" s="97">
+      <c r="O173" s="38">
         <v>3.15</v>
       </c>
       <c r="Q173" s="32">
@@ -13308,7 +13188,7 @@
       </c>
     </row>
     <row r="174" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B174" s="92"/>
+      <c r="B174" s="95"/>
       <c r="C174" s="65" t="s">
         <v>52</v>
       </c>
@@ -13335,7 +13215,7 @@
       </c>
     </row>
     <row r="175" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B175" s="92"/>
+      <c r="B175" s="95"/>
       <c r="C175" s="68" t="s">
         <v>53</v>
       </c>
@@ -13365,7 +13245,7 @@
       </c>
     </row>
     <row r="176" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B176" s="93"/>
+      <c r="B176" s="96"/>
       <c r="C176" s="62" t="s">
         <v>54</v>
       </c>
@@ -13404,13 +13284,13 @@
       <c r="J177" s="75"/>
       <c r="K177" s="75"/>
       <c r="L177" s="72"/>
-      <c r="N177" s="98"/>
-      <c r="O177" s="98"/>
+      <c r="N177" s="76"/>
+      <c r="O177" s="76"/>
       <c r="Q177" s="32"/>
       <c r="R177" s="32"/>
     </row>
     <row r="178" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B178" s="91" t="s">
+      <c r="B178" s="94" t="s">
         <v>42</v>
       </c>
       <c r="C178" s="60" t="s">
@@ -13435,10 +13315,10 @@
       <c r="L178" s="59">
         <v>10.569000000000001</v>
       </c>
-      <c r="N178" s="97">
+      <c r="N178" s="38">
         <v>3.15</v>
       </c>
-      <c r="O178" s="97">
+      <c r="O178" s="38">
         <v>3.1</v>
       </c>
       <c r="Q178" s="32">
@@ -13449,7 +13329,7 @@
       </c>
     </row>
     <row r="179" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B179" s="92"/>
+      <c r="B179" s="95"/>
       <c r="C179" s="65" t="s">
         <v>52</v>
       </c>
@@ -13474,7 +13354,7 @@
       </c>
     </row>
     <row r="180" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B180" s="92"/>
+      <c r="B180" s="95"/>
       <c r="C180" s="68" t="s">
         <v>53</v>
       </c>
@@ -13504,7 +13384,7 @@
       </c>
     </row>
     <row r="181" spans="2:18" x14ac:dyDescent="0.4">
-      <c r="B181" s="93"/>
+      <c r="B181" s="96"/>
       <c r="C181" s="62" t="s">
         <v>54</v>
       </c>
@@ -13533,6 +13413,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="B107:B110"/>
+    <mergeCell ref="B112:B115"/>
+    <mergeCell ref="B117:B120"/>
+    <mergeCell ref="B147:B150"/>
+    <mergeCell ref="B152:B155"/>
+    <mergeCell ref="B122:B125"/>
+    <mergeCell ref="B127:B130"/>
+    <mergeCell ref="B132:B135"/>
+    <mergeCell ref="B137:B140"/>
+    <mergeCell ref="B142:B145"/>
+    <mergeCell ref="B82:B85"/>
+    <mergeCell ref="B87:B90"/>
+    <mergeCell ref="B92:B95"/>
+    <mergeCell ref="B97:B100"/>
+    <mergeCell ref="B102:B105"/>
+    <mergeCell ref="B57:B60"/>
+    <mergeCell ref="B62:B65"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="B72:B75"/>
+    <mergeCell ref="B77:B80"/>
     <mergeCell ref="B163:B166"/>
     <mergeCell ref="B168:B171"/>
     <mergeCell ref="B173:B176"/>
@@ -13549,26 +13449,6 @@
     <mergeCell ref="B42:B45"/>
     <mergeCell ref="B47:B50"/>
     <mergeCell ref="B52:B55"/>
-    <mergeCell ref="B57:B60"/>
-    <mergeCell ref="B62:B65"/>
-    <mergeCell ref="B67:B70"/>
-    <mergeCell ref="B72:B75"/>
-    <mergeCell ref="B77:B80"/>
-    <mergeCell ref="B82:B85"/>
-    <mergeCell ref="B87:B90"/>
-    <mergeCell ref="B92:B95"/>
-    <mergeCell ref="B97:B100"/>
-    <mergeCell ref="B102:B105"/>
-    <mergeCell ref="B107:B110"/>
-    <mergeCell ref="B112:B115"/>
-    <mergeCell ref="B117:B120"/>
-    <mergeCell ref="B147:B150"/>
-    <mergeCell ref="B152:B155"/>
-    <mergeCell ref="B122:B125"/>
-    <mergeCell ref="B127:B130"/>
-    <mergeCell ref="B132:B135"/>
-    <mergeCell ref="B137:B140"/>
-    <mergeCell ref="B142:B145"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
